--- a/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
+++ b/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fptsk-my.sharepoint.com/personal/david_badin_fpt_sk/Documents/Dropbox/Public/davidbadin.github.io/PD2026_app/temp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fptsk-my.sharepoint.com/personal/david_badin_fpt_sk/Documents/Dropbox/Public/davidbadin.github.io/PD2026_app/app/src/main/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD8FFB5F-CF8C-4FD4-B6A9-444E52B4AC52}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BE22FC4-6C6C-4C3C-ABC8-1F7A65A572E5}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>7Mvv3CqJw2QzjZElmBmlWw</t>
+  </si>
+  <si>
+    <t>bilbo</t>
   </si>
 </sst>
 </file>
@@ -609,6 +612,18 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -619,18 +634,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,10 +651,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1240,7 +1239,7 @@
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -1302,7 +1301,7 @@
       <c r="L10" s="13"/>
       <c r="M10" s="13"/>
     </row>
-    <row r="11" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -1395,7 +1394,7 @@
       <c r="L13" s="13"/>
       <c r="M13" s="13"/>
     </row>
-    <row r="14" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -1426,7 +1425,7 @@
       <c r="L14" s="13"/>
       <c r="M14" s="13"/>
     </row>
-    <row r="15" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -1457,7 +1456,7 @@
       <c r="L15" s="13"/>
       <c r="M15" s="13"/>
     </row>
-    <row r="16" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -1550,7 +1549,7 @@
       <c r="L18" s="13"/>
       <c r="M18" s="13"/>
     </row>
-    <row r="19" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
         <v>18</v>
       </c>
@@ -1641,7 +1640,7 @@
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
     </row>
-    <row r="22" spans="1:13" ht="215.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>21</v>
       </c>
@@ -1864,7 +1863,7 @@
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23">
         <v>28</v>
       </c>
@@ -1880,10 +1879,10 @@
       <c r="E29" s="25">
         <v>0.78819444444444442</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="43"/>
+      <c r="G29" s="47"/>
       <c r="H29" s="26" t="s">
         <v>41</v>
       </c>
@@ -1893,7 +1892,9 @@
       <c r="J29" s="27"/>
       <c r="K29" s="27"/>
       <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
+      <c r="M29" s="27" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="30" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23">
@@ -1911,10 +1912,10 @@
       <c r="E30" s="25">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="43"/>
+      <c r="G30" s="47"/>
       <c r="H30" s="26" t="s">
         <v>41</v>
       </c>
@@ -1957,7 +1958,7 @@
       <c r="L31" s="27"/>
       <c r="M31" s="27"/>
     </row>
-    <row r="32" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23">
         <v>31</v>
       </c>
@@ -1973,10 +1974,10 @@
       <c r="E32" s="25">
         <v>0.97222222222222221</v>
       </c>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="43"/>
+      <c r="G32" s="47"/>
       <c r="H32" s="26" t="s">
         <v>41</v>
       </c>
@@ -2035,10 +2036,10 @@
       <c r="E34" s="31">
         <v>0.57638888888888884</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="45"/>
+      <c r="G34" s="49"/>
       <c r="H34" s="32" t="s">
         <v>41</v>
       </c>
@@ -2064,10 +2065,10 @@
       <c r="E35" s="31">
         <v>0.65972222222222221</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="45"/>
+      <c r="G35" s="49"/>
       <c r="H35" s="32" t="s">
         <v>41</v>
       </c>
@@ -2093,10 +2094,10 @@
       <c r="E36" s="31">
         <v>0.73611111111111116</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F36" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="45"/>
+      <c r="G36" s="49"/>
       <c r="H36" s="32" t="s">
         <v>41</v>
       </c>
@@ -2106,7 +2107,7 @@
       <c r="L36" s="33"/>
       <c r="M36" s="33"/>
     </row>
-    <row r="37" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="29">
         <v>36</v>
       </c>
@@ -2275,10 +2276,10 @@
       <c r="E42" s="37">
         <v>0.53472222222222221</v>
       </c>
-      <c r="F42" s="46" t="s">
+      <c r="F42" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="47"/>
+      <c r="G42" s="43"/>
       <c r="H42" s="38" t="s">
         <v>41</v>
       </c>
@@ -2304,10 +2305,10 @@
       <c r="E43" s="37">
         <v>0.61805555555555558</v>
       </c>
-      <c r="F43" s="46" t="s">
+      <c r="F43" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G43" s="47"/>
+      <c r="G43" s="43"/>
       <c r="H43" s="38" t="s">
         <v>41</v>
       </c>
@@ -2333,10 +2334,10 @@
       <c r="E44" s="37">
         <v>0.6875</v>
       </c>
-      <c r="F44" s="46" t="s">
+      <c r="F44" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="47"/>
+      <c r="G44" s="43"/>
       <c r="H44" s="38" t="s">
         <v>41</v>
       </c>
@@ -2362,10 +2363,10 @@
       <c r="E45" s="40">
         <v>0.72916666666666663</v>
       </c>
-      <c r="F45" s="48" t="s">
+      <c r="F45" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="G45" s="49"/>
+      <c r="G45" s="45"/>
       <c r="H45" s="38" t="s">
         <v>41</v>
       </c>
@@ -2377,7 +2378,7 @@
       <c r="L45" s="39"/>
       <c r="M45" s="39"/>
     </row>
-    <row r="46" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
         <v>45</v>
       </c>
@@ -2393,10 +2394,10 @@
       <c r="E46" s="37">
         <v>0.78472222222222221</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="G46" s="49"/>
+      <c r="G46" s="45"/>
       <c r="H46" s="38" t="s">
         <v>41</v>
       </c>
@@ -2408,7 +2409,7 @@
       <c r="L46" s="39"/>
       <c r="M46" s="39"/>
     </row>
-    <row r="47" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
         <v>46</v>
       </c>
@@ -2439,7 +2440,7 @@
       <c r="L47" s="39"/>
       <c r="M47" s="39"/>
     </row>
-    <row r="48" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
         <v>47</v>
       </c>
@@ -2470,7 +2471,7 @@
       <c r="L48" s="39"/>
       <c r="M48" s="39"/>
     </row>
-    <row r="49" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
         <v>48</v>
       </c>
@@ -2532,17 +2533,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
+++ b/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fptsk-my.sharepoint.com/personal/david_badin_fpt_sk/Documents/Dropbox/Public/davidbadin.github.io/PD2026_app/app/src/main/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BE22FC4-6C6C-4C3C-ABC8-1F7A65A572E5}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E6BD8A-4D18-495C-9832-6BABE9161938}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="158">
   <si>
     <t>ID</t>
   </si>
@@ -250,18 +250,9 @@
     <t>1Jrodi5WbL1r2z1LZN2dkw</t>
   </si>
   <si>
-    <t>Subcultural beat, alebo jednoducho povedané mix sympatického smradu, hluku a drsnosti doplnený o romantický náhľad na svet, kamarátstvo, držanie party a množstvo spomienok. Vitaj v rock ´n´ rollovom svete brnenských pardálov.🎸😎</t>
-  </si>
-  <si>
     <t>3QZJ3UhOA7Q5XoIuDfL4S3</t>
   </si>
   <si>
-    <t>punk ´n´ roll</t>
-  </si>
-  <si>
-    <t>tamgasti-cz</t>
-  </si>
-  <si>
     <t>4IF4ihSoCuOxzIUNaSqxmX</t>
   </si>
   <si>
@@ -329,13 +320,187 @@
   </si>
   <si>
     <t>bilbo</t>
+  </si>
+  <si>
+    <t>me-against-all</t>
+  </si>
+  <si>
+    <t>true-reason</t>
+  </si>
+  <si>
+    <t>grobiani</t>
+  </si>
+  <si>
+    <t>punkreas</t>
+  </si>
+  <si>
+    <t>hoten-toten</t>
+  </si>
+  <si>
+    <t>total-chaos</t>
+  </si>
+  <si>
+    <t>rumkicks</t>
+  </si>
+  <si>
+    <t>agata</t>
+  </si>
+  <si>
+    <t>cybo</t>
+  </si>
+  <si>
+    <t>marno</t>
+  </si>
+  <si>
+    <t>upside-down</t>
+  </si>
+  <si>
+    <t>covers-for-lovers</t>
+  </si>
+  <si>
+    <t>sitnan</t>
+  </si>
+  <si>
+    <t>vvu</t>
+  </si>
+  <si>
+    <t>nezfales</t>
+  </si>
+  <si>
+    <t>fialky</t>
+  </si>
+  <si>
+    <t>punk-floid</t>
+  </si>
+  <si>
+    <t>zotrwacnost</t>
+  </si>
+  <si>
+    <t>mental-tension</t>
+  </si>
+  <si>
+    <t>crossczech</t>
+  </si>
+  <si>
+    <t>stamgasti</t>
+  </si>
+  <si>
+    <t>vision-days</t>
+  </si>
+  <si>
+    <t>tragedis</t>
+  </si>
+  <si>
+    <t>saints-sinners</t>
+  </si>
+  <si>
+    <t>banane-metalik</t>
+  </si>
+  <si>
+    <t>perkele</t>
+  </si>
+  <si>
+    <t>booze-glory</t>
+  </si>
+  <si>
+    <t>dafy-the-rafters</t>
+  </si>
+  <si>
+    <t>springless</t>
+  </si>
+  <si>
+    <t>ska-petarda</t>
+  </si>
+  <si>
+    <t>proti-smeru</t>
+  </si>
+  <si>
+    <t>dimenzia-x</t>
+  </si>
+  <si>
+    <t>curlies</t>
+  </si>
+  <si>
+    <t>fail-together</t>
+  </si>
+  <si>
+    <t>stara-puska</t>
+  </si>
+  <si>
+    <t>supertesla</t>
+  </si>
+  <si>
+    <t>driak</t>
+  </si>
+  <si>
+    <t>plus-minus</t>
+  </si>
+  <si>
+    <t>hardcore</t>
+  </si>
+  <si>
+    <t>punk rock</t>
+  </si>
+  <si>
+    <t>hardcore punk</t>
+  </si>
+  <si>
+    <t>crust / black metal</t>
+  </si>
+  <si>
+    <t>punk / trash</t>
+  </si>
+  <si>
+    <t>hardcore / punk</t>
+  </si>
+  <si>
+    <t>power oi!</t>
+  </si>
+  <si>
+    <t>subcultural beat</t>
+  </si>
+  <si>
+    <t>oi!</t>
+  </si>
+  <si>
+    <t>gore'n'roll</t>
+  </si>
+  <si>
+    <t>street punk / oi!</t>
+  </si>
+  <si>
+    <t>antipunk</t>
+  </si>
+  <si>
+    <t>ska</t>
+  </si>
+  <si>
+    <t>folk punk</t>
+  </si>
+  <si>
+    <t>punk / folk</t>
+  </si>
+  <si>
+    <t>heartland punk</t>
+  </si>
+  <si>
+    <t>O koncertný zážitok, množstvo dobre známych peciek i náladu máš teda postarané, už sa len stačí zariadiť tak, že to nepremeškáš.🖤😏</t>
+  </si>
+  <si>
+    <t>Na Punkáči deťom 2026 vystúpi aj brnenská parta nazvaná Štamgasti. Subcultural beat, srdce a melodický set sú mixom, ktorý baví. 👊🎸</t>
+  </si>
+  <si>
+    <t>Bilbo, známy z viacerých projektov, si tentoraz hodí koncertný set sám, resp. bez zvyšných členov kapely Marhule. Prítomné teda bude invenčné hovorené slovo, texty rovnako tak, pričom netreba zabúdať na zrejmý odkaz - Šír lásku ...🖤🎸</t>
+  </si>
+  <si>
+    <t>Nádych Škótska, dynamický punk-rock doplnený o gajdy a hlavne výborný zážitok. Z Česka príde na 15. ročník Punkáči deťom aj kapela Curlies, a to s jasným odkazom.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +554,18 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1E1E26"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -434,7 +611,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -470,24 +647,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -615,25 +779,70 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,6 +860,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -970,11 +1183,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M999"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="6" width="20.7109375" customWidth="1"/>
+    <col min="2" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="34.28515625" customWidth="1"/>
     <col min="7" max="7" width="66.42578125" customWidth="1"/>
     <col min="8" max="8" width="20.7109375" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
@@ -1022,7 +1236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1048,12 +1262,18 @@
       <c r="I2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="J2" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" s="56">
+        <v>800</v>
+      </c>
       <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M2" s="46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1079,12 +1299,18 @@
       <c r="I3" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="J3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="56">
+        <v>800</v>
+      </c>
       <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1110,12 +1336,18 @@
       <c r="I4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="J4" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K4" s="56">
+        <v>800</v>
+      </c>
       <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M4" s="46" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1141,12 +1373,18 @@
       <c r="I5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="J5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K5" s="56">
+        <v>200</v>
+      </c>
       <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-    </row>
-    <row r="6" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1172,12 +1410,18 @@
       <c r="I6" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="J6" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="56">
+        <v>110</v>
+      </c>
       <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="46" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -1203,12 +1447,18 @@
       <c r="I7" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="56">
+        <v>40</v>
+      </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-    </row>
-    <row r="8" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="46" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1234,10 +1484,16 @@
       <c r="I8" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="J8" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" s="56">
+        <v>50</v>
+      </c>
       <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
+      <c r="M8" s="46" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
@@ -1265,12 +1521,18 @@
       <c r="I9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="57">
+        <v>800</v>
+      </c>
       <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-    </row>
-    <row r="10" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -1296,10 +1558,16 @@
       <c r="I10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
+      <c r="J10" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="57">
+        <v>800</v>
+      </c>
       <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="M10" s="48" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
@@ -1327,12 +1595,18 @@
       <c r="I11" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
+      <c r="J11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K11" s="57">
+        <v>800</v>
+      </c>
       <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-    </row>
-    <row r="12" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -1358,12 +1632,18 @@
       <c r="I12" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
+      <c r="J12" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K12" s="57">
+        <v>800</v>
+      </c>
       <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-    </row>
-    <row r="13" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" s="47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -1389,10 +1669,16 @@
       <c r="I13" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
+      <c r="J13" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="57">
+        <v>800</v>
+      </c>
       <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="M13" s="47" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
@@ -1420,10 +1706,16 @@
       <c r="I14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
+      <c r="J14" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="57">
+        <v>500</v>
+      </c>
       <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+      <c r="M14" s="47" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
@@ -1451,10 +1743,16 @@
       <c r="I15" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="J15" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K15" s="57">
+        <v>500</v>
+      </c>
       <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+      <c r="M15" s="48" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
@@ -1482,12 +1780,18 @@
       <c r="I16" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
+      <c r="J16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="57">
+        <v>130</v>
+      </c>
       <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-    </row>
-    <row r="17" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -1513,12 +1817,18 @@
       <c r="I17" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
+      <c r="J17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" s="57">
+        <v>120</v>
+      </c>
       <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-    </row>
-    <row r="18" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -1537,17 +1847,25 @@
       <c r="F18" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="13"/>
+      <c r="G18" s="62" t="s">
+        <v>154</v>
+      </c>
       <c r="H18" s="12" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
+      <c r="J18" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="K18" s="57">
+        <v>140</v>
+      </c>
       <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="M18" s="48" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15">
@@ -1575,10 +1893,16 @@
       <c r="I19" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
+      <c r="J19" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="K19" s="58">
+        <v>800</v>
+      </c>
       <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
+      <c r="M19" s="22" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
@@ -1604,12 +1928,18 @@
         <v>14</v>
       </c>
       <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
+      <c r="J20" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" s="58">
+        <v>800</v>
+      </c>
       <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M20" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15">
         <v>20</v>
       </c>
@@ -1635,12 +1965,18 @@
       <c r="I21" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
+      <c r="J21" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="K21" s="58">
+        <v>800</v>
+      </c>
       <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>21</v>
       </c>
@@ -1660,24 +1996,26 @@
         <v>34</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="K22" s="19"/>
+        <v>145</v>
+      </c>
+      <c r="K22" s="58">
+        <v>500</v>
+      </c>
       <c r="L22" s="19"/>
-      <c r="M22" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15">
         <v>22</v>
       </c>
@@ -1701,14 +2039,20 @@
         <v>14</v>
       </c>
       <c r="I23" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
+        <v>77</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="K23" s="58">
+        <v>500</v>
+      </c>
       <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-    </row>
-    <row r="24" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15">
         <v>23</v>
       </c>
@@ -1732,14 +2076,20 @@
         <v>14</v>
       </c>
       <c r="I24" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
+        <v>78</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="K24" s="58">
+        <v>500</v>
+      </c>
       <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15">
         <v>24</v>
       </c>
@@ -1756,21 +2106,27 @@
         <v>0.8125</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="18" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
+        <v>80</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="K25" s="58">
+        <v>500</v>
+      </c>
       <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15">
         <v>25</v>
       </c>
@@ -1794,14 +2150,20 @@
         <v>14</v>
       </c>
       <c r="I26" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
+        <v>81</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="K26" s="58">
+        <v>30</v>
+      </c>
       <c r="L26" s="19"/>
-      <c r="M26" s="19"/>
-    </row>
-    <row r="27" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15">
         <v>26</v>
       </c>
@@ -1825,14 +2187,20 @@
         <v>14</v>
       </c>
       <c r="I27" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
+        <v>82</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="K27" s="58">
+        <v>10</v>
+      </c>
       <c r="L27" s="19"/>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15">
         <v>27</v>
       </c>
@@ -1856,14 +2224,20 @@
         <v>14</v>
       </c>
       <c r="I28" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
+        <v>83</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="K28" s="58">
+        <v>20</v>
+      </c>
       <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="23">
         <v>28</v>
       </c>
@@ -1879,24 +2253,30 @@
       <c r="E29" s="25">
         <v>0.78819444444444442</v>
       </c>
-      <c r="F29" s="46" t="s">
+      <c r="F29" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="G29" s="47"/>
+      <c r="G29" s="63" t="s">
+        <v>156</v>
+      </c>
       <c r="H29" s="26" t="s">
         <v>41</v>
       </c>
       <c r="I29" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
+        <v>84</v>
+      </c>
+      <c r="J29" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="K29" s="59">
+        <v>500</v>
+      </c>
       <c r="L29" s="27"/>
-      <c r="M29" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="50" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23">
         <v>29</v>
       </c>
@@ -1912,22 +2292,28 @@
       <c r="E30" s="25">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F30" s="46" t="s">
+      <c r="F30" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="47"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="26" t="s">
         <v>41</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
+        <v>85</v>
+      </c>
+      <c r="J30" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="K30" s="59">
+        <v>800</v>
+      </c>
       <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-    </row>
-    <row r="31" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23">
         <v>30</v>
       </c>
@@ -1951,14 +2337,20 @@
         <v>41</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
+        <v>86</v>
+      </c>
+      <c r="J31" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="K31" s="59">
+        <v>800</v>
+      </c>
       <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M31" s="51" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="23">
         <v>31</v>
       </c>
@@ -1974,22 +2366,26 @@
       <c r="E32" s="25">
         <v>0.97222222222222221</v>
       </c>
-      <c r="F32" s="46" t="s">
+      <c r="F32" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="47"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="26" t="s">
         <v>41</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
+        <v>87</v>
+      </c>
+      <c r="J32" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="K32" s="59">
+        <v>500</v>
+      </c>
       <c r="L32" s="27"/>
       <c r="M32" s="27"/>
     </row>
-    <row r="33" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="23">
         <v>32</v>
       </c>
@@ -2013,14 +2409,20 @@
         <v>41</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
+        <v>88</v>
+      </c>
+      <c r="J33" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="K33" s="59">
+        <v>150</v>
+      </c>
       <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="51" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29">
         <v>33</v>
       </c>
@@ -2036,10 +2438,10 @@
       <c r="E34" s="31">
         <v>0.57638888888888884</v>
       </c>
-      <c r="F34" s="48" t="s">
+      <c r="F34" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="49"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32" t="s">
         <v>41</v>
       </c>
@@ -2049,7 +2451,7 @@
       <c r="L34" s="33"/>
       <c r="M34" s="33"/>
     </row>
-    <row r="35" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="29">
         <v>34</v>
       </c>
@@ -2065,10 +2467,10 @@
       <c r="E35" s="31">
         <v>0.65972222222222221</v>
       </c>
-      <c r="F35" s="48" t="s">
+      <c r="F35" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="49"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="32" t="s">
         <v>41</v>
       </c>
@@ -2094,10 +2496,10 @@
       <c r="E36" s="31">
         <v>0.73611111111111116</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="49"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32" t="s">
         <v>41</v>
       </c>
@@ -2131,14 +2533,20 @@
         <v>41</v>
       </c>
       <c r="I37" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
+        <v>89</v>
+      </c>
+      <c r="J37" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="K37" s="60">
+        <v>500</v>
+      </c>
       <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-    </row>
-    <row r="38" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M37" s="52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29">
         <v>37</v>
       </c>
@@ -2162,14 +2570,20 @@
         <v>41</v>
       </c>
       <c r="I38" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
+        <v>90</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="K38" s="60">
+        <v>500</v>
+      </c>
       <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-    </row>
-    <row r="39" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M38" s="52" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29">
         <v>38</v>
       </c>
@@ -2188,19 +2602,27 @@
       <c r="F39" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="G39" s="33"/>
+      <c r="G39" s="64" t="s">
+        <v>157</v>
+      </c>
       <c r="H39" s="32" t="s">
         <v>41</v>
       </c>
       <c r="I39" s="34" t="s">
-        <v>94</v>
-      </c>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="K39" s="60">
+        <v>500</v>
+      </c>
       <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-    </row>
-    <row r="40" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="53" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="29">
         <v>39</v>
       </c>
@@ -2224,12 +2646,18 @@
         <v>41</v>
       </c>
       <c r="I40" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
+        <v>92</v>
+      </c>
+      <c r="J40" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="K40" s="60">
+        <v>800</v>
+      </c>
       <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
+      <c r="M40" s="52" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="41" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="29">
@@ -2260,7 +2688,7 @@
       <c r="L41" s="33"/>
       <c r="M41" s="33"/>
     </row>
-    <row r="42" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -2279,7 +2707,7 @@
       <c r="F42" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G42" s="43"/>
+      <c r="G42" s="39"/>
       <c r="H42" s="38" t="s">
         <v>41</v>
       </c>
@@ -2289,7 +2717,7 @@
       <c r="L42" s="39"/>
       <c r="M42" s="39"/>
     </row>
-    <row r="43" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>42</v>
       </c>
@@ -2308,7 +2736,7 @@
       <c r="F43" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="G43" s="43"/>
+      <c r="G43" s="39"/>
       <c r="H43" s="38" t="s">
         <v>41</v>
       </c>
@@ -2337,7 +2765,7 @@
       <c r="F44" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="43"/>
+      <c r="G44" s="39"/>
       <c r="H44" s="38" t="s">
         <v>41</v>
       </c>
@@ -2363,20 +2791,26 @@
       <c r="E45" s="40">
         <v>0.72916666666666663</v>
       </c>
-      <c r="F45" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G45" s="45"/>
+      <c r="F45" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="G45" s="39"/>
       <c r="H45" s="38" t="s">
         <v>41</v>
       </c>
       <c r="I45" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="J45" s="39"/>
-      <c r="K45" s="39"/>
+        <v>94</v>
+      </c>
+      <c r="J45" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="K45" s="61">
+        <v>170</v>
+      </c>
       <c r="L45" s="39"/>
-      <c r="M45" s="39"/>
+      <c r="M45" s="54" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="41">
@@ -2394,20 +2828,26 @@
       <c r="E46" s="37">
         <v>0.78472222222222221</v>
       </c>
-      <c r="F46" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46" s="45"/>
+      <c r="F46" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="G46" s="39"/>
       <c r="H46" s="38" t="s">
         <v>41</v>
       </c>
       <c r="I46" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
+        <v>95</v>
+      </c>
+      <c r="J46" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="K46" s="61">
+        <v>170</v>
+      </c>
       <c r="L46" s="39"/>
-      <c r="M46" s="39"/>
+      <c r="M46" s="54" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="41">
@@ -2433,12 +2873,18 @@
         <v>41</v>
       </c>
       <c r="I47" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
+        <v>96</v>
+      </c>
+      <c r="J47" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="K47" s="61">
+        <v>500</v>
+      </c>
       <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
+      <c r="M47" s="54" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="48" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="41">
@@ -2464,12 +2910,18 @@
         <v>41</v>
       </c>
       <c r="I48" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
+        <v>97</v>
+      </c>
+      <c r="J48" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="K48" s="61">
+        <v>160</v>
+      </c>
       <c r="L48" s="39"/>
-      <c r="M48" s="39"/>
+      <c r="M48" s="54" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="49" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="41">
@@ -2495,12 +2947,18 @@
         <v>41</v>
       </c>
       <c r="I49" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="J49" s="39"/>
-      <c r="K49" s="39"/>
+        <v>98</v>
+      </c>
+      <c r="J49" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="K49" s="61">
+        <v>800</v>
+      </c>
       <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
+      <c r="M49" s="54" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="50" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="41">
@@ -2531,20 +2989,5701 @@
       <c r="L50" s="39"/>
       <c r="M50" s="39"/>
     </row>
+    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="M51" s="55"/>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="M52" s="55"/>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="M53" s="55"/>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G54" s="55"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="M54" s="55"/>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G55" s="55"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="55"/>
+      <c r="M55" s="55"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G56" s="55"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="55"/>
+      <c r="M56" s="55"/>
+    </row>
+    <row r="57" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G57" s="55"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="55"/>
+      <c r="M57" s="55"/>
+    </row>
+    <row r="58" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G58" s="55"/>
+      <c r="J58" s="55"/>
+      <c r="K58" s="55"/>
+      <c r="M58" s="55"/>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G59" s="55"/>
+      <c r="J59" s="55"/>
+      <c r="K59" s="55"/>
+      <c r="M59" s="55"/>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G60" s="55"/>
+      <c r="J60" s="55"/>
+      <c r="K60" s="55"/>
+      <c r="M60" s="55"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G61" s="55"/>
+      <c r="J61" s="55"/>
+      <c r="K61" s="55"/>
+      <c r="M61" s="55"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G62" s="55"/>
+      <c r="J62" s="55"/>
+      <c r="K62" s="55"/>
+      <c r="M62" s="55"/>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G63" s="55"/>
+      <c r="J63" s="55"/>
+      <c r="K63" s="55"/>
+      <c r="M63" s="55"/>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G64" s="55"/>
+      <c r="J64" s="55"/>
+      <c r="K64" s="55"/>
+      <c r="M64" s="55"/>
+    </row>
+    <row r="65" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G65" s="55"/>
+      <c r="J65" s="55"/>
+      <c r="K65" s="55"/>
+      <c r="M65" s="55"/>
+    </row>
+    <row r="66" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G66" s="55"/>
+      <c r="J66" s="55"/>
+      <c r="K66" s="55"/>
+      <c r="M66" s="55"/>
+    </row>
+    <row r="67" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="55"/>
+      <c r="J67" s="55"/>
+      <c r="K67" s="55"/>
+      <c r="M67" s="55"/>
+    </row>
+    <row r="68" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G68" s="55"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+      <c r="M68" s="55"/>
+    </row>
+    <row r="69" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G69" s="55"/>
+      <c r="J69" s="55"/>
+      <c r="K69" s="55"/>
+      <c r="M69" s="55"/>
+    </row>
+    <row r="70" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G70" s="55"/>
+      <c r="J70" s="55"/>
+      <c r="K70" s="55"/>
+      <c r="M70" s="55"/>
+    </row>
+    <row r="71" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G71" s="55"/>
+      <c r="J71" s="55"/>
+      <c r="K71" s="55"/>
+      <c r="M71" s="55"/>
+    </row>
+    <row r="72" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G72" s="55"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="M72" s="55"/>
+    </row>
+    <row r="73" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G73" s="55"/>
+      <c r="J73" s="55"/>
+      <c r="K73" s="55"/>
+      <c r="M73" s="55"/>
+    </row>
+    <row r="74" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G74" s="55"/>
+      <c r="J74" s="55"/>
+      <c r="K74" s="55"/>
+      <c r="M74" s="55"/>
+    </row>
+    <row r="75" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G75" s="55"/>
+      <c r="J75" s="55"/>
+      <c r="K75" s="55"/>
+      <c r="M75" s="55"/>
+    </row>
+    <row r="76" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G76" s="55"/>
+      <c r="J76" s="55"/>
+      <c r="K76" s="55"/>
+      <c r="M76" s="55"/>
+    </row>
+    <row r="77" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G77" s="55"/>
+      <c r="J77" s="55"/>
+      <c r="K77" s="55"/>
+      <c r="M77" s="55"/>
+    </row>
+    <row r="78" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G78" s="55"/>
+      <c r="J78" s="55"/>
+      <c r="K78" s="55"/>
+      <c r="M78" s="55"/>
+    </row>
+    <row r="79" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G79" s="55"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+      <c r="M79" s="55"/>
+    </row>
+    <row r="80" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="55"/>
+      <c r="J80" s="55"/>
+      <c r="K80" s="55"/>
+      <c r="M80" s="55"/>
+    </row>
+    <row r="81" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G81" s="55"/>
+      <c r="J81" s="55"/>
+      <c r="K81" s="55"/>
+      <c r="M81" s="55"/>
+    </row>
+    <row r="82" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G82" s="55"/>
+      <c r="J82" s="55"/>
+      <c r="K82" s="55"/>
+      <c r="M82" s="55"/>
+    </row>
+    <row r="83" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G83" s="55"/>
+      <c r="J83" s="55"/>
+      <c r="K83" s="55"/>
+      <c r="M83" s="55"/>
+    </row>
+    <row r="84" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="55"/>
+      <c r="J84" s="55"/>
+      <c r="K84" s="55"/>
+      <c r="M84" s="55"/>
+    </row>
+    <row r="85" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="55"/>
+      <c r="J85" s="55"/>
+      <c r="K85" s="55"/>
+      <c r="M85" s="55"/>
+    </row>
+    <row r="86" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="55"/>
+      <c r="J86" s="55"/>
+      <c r="K86" s="55"/>
+      <c r="M86" s="55"/>
+    </row>
+    <row r="87" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="55"/>
+      <c r="J87" s="55"/>
+      <c r="K87" s="55"/>
+      <c r="M87" s="55"/>
+    </row>
+    <row r="88" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G88" s="55"/>
+      <c r="J88" s="55"/>
+      <c r="K88" s="55"/>
+      <c r="M88" s="55"/>
+    </row>
+    <row r="89" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G89" s="55"/>
+      <c r="J89" s="55"/>
+      <c r="K89" s="55"/>
+      <c r="M89" s="55"/>
+    </row>
+    <row r="90" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G90" s="55"/>
+      <c r="J90" s="55"/>
+      <c r="K90" s="55"/>
+      <c r="M90" s="55"/>
+    </row>
+    <row r="91" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G91" s="55"/>
+      <c r="J91" s="55"/>
+      <c r="K91" s="55"/>
+      <c r="M91" s="55"/>
+    </row>
+    <row r="92" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G92" s="55"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
+      <c r="M92" s="55"/>
+    </row>
+    <row r="93" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="55"/>
+      <c r="J93" s="55"/>
+      <c r="K93" s="55"/>
+      <c r="M93" s="55"/>
+    </row>
+    <row r="94" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G94" s="55"/>
+      <c r="J94" s="55"/>
+      <c r="K94" s="55"/>
+      <c r="M94" s="55"/>
+    </row>
+    <row r="95" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G95" s="55"/>
+      <c r="J95" s="55"/>
+      <c r="K95" s="55"/>
+      <c r="M95" s="55"/>
+    </row>
+    <row r="96" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G96" s="55"/>
+      <c r="J96" s="55"/>
+      <c r="K96" s="55"/>
+      <c r="M96" s="55"/>
+    </row>
+    <row r="97" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G97" s="55"/>
+      <c r="J97" s="55"/>
+      <c r="K97" s="55"/>
+      <c r="M97" s="55"/>
+    </row>
+    <row r="98" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G98" s="55"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
+      <c r="M98" s="55"/>
+    </row>
+    <row r="99" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G99" s="55"/>
+      <c r="J99" s="55"/>
+      <c r="K99" s="55"/>
+      <c r="M99" s="55"/>
+    </row>
+    <row r="100" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G100" s="55"/>
+      <c r="J100" s="55"/>
+      <c r="K100" s="55"/>
+      <c r="M100" s="55"/>
+    </row>
+    <row r="101" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G101" s="55"/>
+      <c r="J101" s="55"/>
+      <c r="K101" s="55"/>
+      <c r="M101" s="55"/>
+    </row>
+    <row r="102" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G102" s="55"/>
+      <c r="J102" s="55"/>
+      <c r="K102" s="55"/>
+      <c r="M102" s="55"/>
+    </row>
+    <row r="103" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G103" s="55"/>
+      <c r="J103" s="55"/>
+      <c r="K103" s="55"/>
+      <c r="M103" s="55"/>
+    </row>
+    <row r="104" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G104" s="55"/>
+      <c r="J104" s="55"/>
+      <c r="K104" s="55"/>
+      <c r="M104" s="55"/>
+    </row>
+    <row r="105" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G105" s="55"/>
+      <c r="J105" s="55"/>
+      <c r="K105" s="55"/>
+      <c r="M105" s="55"/>
+    </row>
+    <row r="106" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="55"/>
+      <c r="J106" s="55"/>
+      <c r="K106" s="55"/>
+      <c r="M106" s="55"/>
+    </row>
+    <row r="107" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G107" s="55"/>
+      <c r="J107" s="55"/>
+      <c r="K107" s="55"/>
+      <c r="M107" s="55"/>
+    </row>
+    <row r="108" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G108" s="55"/>
+      <c r="J108" s="55"/>
+      <c r="K108" s="55"/>
+      <c r="M108" s="55"/>
+    </row>
+    <row r="109" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G109" s="55"/>
+      <c r="J109" s="55"/>
+      <c r="K109" s="55"/>
+      <c r="M109" s="55"/>
+    </row>
+    <row r="110" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G110" s="55"/>
+      <c r="J110" s="55"/>
+      <c r="K110" s="55"/>
+      <c r="M110" s="55"/>
+    </row>
+    <row r="111" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G111" s="55"/>
+      <c r="J111" s="55"/>
+      <c r="K111" s="55"/>
+      <c r="M111" s="55"/>
+    </row>
+    <row r="112" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G112" s="55"/>
+      <c r="J112" s="55"/>
+      <c r="K112" s="55"/>
+      <c r="M112" s="55"/>
+    </row>
+    <row r="113" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G113" s="55"/>
+      <c r="J113" s="55"/>
+      <c r="K113" s="55"/>
+      <c r="M113" s="55"/>
+    </row>
+    <row r="114" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G114" s="55"/>
+      <c r="J114" s="55"/>
+      <c r="K114" s="55"/>
+      <c r="M114" s="55"/>
+    </row>
+    <row r="115" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G115" s="55"/>
+      <c r="J115" s="55"/>
+      <c r="K115" s="55"/>
+      <c r="M115" s="55"/>
+    </row>
+    <row r="116" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G116" s="55"/>
+      <c r="J116" s="55"/>
+      <c r="K116" s="55"/>
+      <c r="M116" s="55"/>
+    </row>
+    <row r="117" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G117" s="55"/>
+      <c r="J117" s="55"/>
+      <c r="K117" s="55"/>
+      <c r="M117" s="55"/>
+    </row>
+    <row r="118" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G118" s="55"/>
+      <c r="J118" s="55"/>
+      <c r="K118" s="55"/>
+      <c r="M118" s="55"/>
+    </row>
+    <row r="119" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G119" s="55"/>
+      <c r="J119" s="55"/>
+      <c r="K119" s="55"/>
+      <c r="M119" s="55"/>
+    </row>
+    <row r="120" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G120" s="55"/>
+      <c r="J120" s="55"/>
+      <c r="K120" s="55"/>
+      <c r="M120" s="55"/>
+    </row>
+    <row r="121" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G121" s="55"/>
+      <c r="J121" s="55"/>
+      <c r="K121" s="55"/>
+      <c r="M121" s="55"/>
+    </row>
+    <row r="122" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G122" s="55"/>
+      <c r="J122" s="55"/>
+      <c r="K122" s="55"/>
+      <c r="M122" s="55"/>
+    </row>
+    <row r="123" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G123" s="55"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="M123" s="55"/>
+    </row>
+    <row r="124" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G124" s="55"/>
+      <c r="J124" s="55"/>
+      <c r="K124" s="55"/>
+      <c r="M124" s="55"/>
+    </row>
+    <row r="125" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G125" s="55"/>
+      <c r="J125" s="55"/>
+      <c r="K125" s="55"/>
+      <c r="M125" s="55"/>
+    </row>
+    <row r="126" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G126" s="55"/>
+      <c r="J126" s="55"/>
+      <c r="K126" s="55"/>
+      <c r="M126" s="55"/>
+    </row>
+    <row r="127" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G127" s="55"/>
+      <c r="J127" s="55"/>
+      <c r="K127" s="55"/>
+      <c r="M127" s="55"/>
+    </row>
+    <row r="128" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G128" s="55"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="55"/>
+      <c r="M128" s="55"/>
+    </row>
+    <row r="129" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G129" s="55"/>
+      <c r="J129" s="55"/>
+      <c r="K129" s="55"/>
+      <c r="M129" s="55"/>
+    </row>
+    <row r="130" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G130" s="55"/>
+      <c r="J130" s="55"/>
+      <c r="K130" s="55"/>
+      <c r="M130" s="55"/>
+    </row>
+    <row r="131" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G131" s="55"/>
+      <c r="J131" s="55"/>
+      <c r="K131" s="55"/>
+      <c r="M131" s="55"/>
+    </row>
+    <row r="132" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G132" s="55"/>
+      <c r="J132" s="55"/>
+      <c r="K132" s="55"/>
+      <c r="M132" s="55"/>
+    </row>
+    <row r="133" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G133" s="55"/>
+      <c r="J133" s="55"/>
+      <c r="K133" s="55"/>
+      <c r="M133" s="55"/>
+    </row>
+    <row r="134" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G134" s="55"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="55"/>
+      <c r="M134" s="55"/>
+    </row>
+    <row r="135" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G135" s="55"/>
+      <c r="J135" s="55"/>
+      <c r="K135" s="55"/>
+      <c r="M135" s="55"/>
+    </row>
+    <row r="136" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="M136" s="55"/>
+    </row>
+    <row r="137" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G137" s="55"/>
+      <c r="J137" s="55"/>
+      <c r="K137" s="55"/>
+      <c r="M137" s="55"/>
+    </row>
+    <row r="138" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G138" s="55"/>
+      <c r="J138" s="55"/>
+      <c r="K138" s="55"/>
+      <c r="M138" s="55"/>
+    </row>
+    <row r="139" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G139" s="55"/>
+      <c r="J139" s="55"/>
+      <c r="K139" s="55"/>
+      <c r="M139" s="55"/>
+    </row>
+    <row r="140" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G140" s="55"/>
+      <c r="J140" s="55"/>
+      <c r="K140" s="55"/>
+      <c r="M140" s="55"/>
+    </row>
+    <row r="141" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G141" s="55"/>
+      <c r="J141" s="55"/>
+      <c r="K141" s="55"/>
+      <c r="M141" s="55"/>
+    </row>
+    <row r="142" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G142" s="55"/>
+      <c r="J142" s="55"/>
+      <c r="K142" s="55"/>
+      <c r="M142" s="55"/>
+    </row>
+    <row r="143" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G143" s="55"/>
+      <c r="J143" s="55"/>
+      <c r="K143" s="55"/>
+      <c r="M143" s="55"/>
+    </row>
+    <row r="144" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G144" s="55"/>
+      <c r="J144" s="55"/>
+      <c r="K144" s="55"/>
+      <c r="M144" s="55"/>
+    </row>
+    <row r="145" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G145" s="55"/>
+      <c r="J145" s="55"/>
+      <c r="K145" s="55"/>
+      <c r="M145" s="55"/>
+    </row>
+    <row r="146" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G146" s="55"/>
+      <c r="J146" s="55"/>
+      <c r="K146" s="55"/>
+      <c r="M146" s="55"/>
+    </row>
+    <row r="147" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G147" s="55"/>
+      <c r="J147" s="55"/>
+      <c r="K147" s="55"/>
+      <c r="M147" s="55"/>
+    </row>
+    <row r="148" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G148" s="55"/>
+      <c r="J148" s="55"/>
+      <c r="K148" s="55"/>
+      <c r="M148" s="55"/>
+    </row>
+    <row r="149" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G149" s="55"/>
+      <c r="J149" s="55"/>
+      <c r="K149" s="55"/>
+      <c r="M149" s="55"/>
+    </row>
+    <row r="150" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G150" s="55"/>
+      <c r="J150" s="55"/>
+      <c r="K150" s="55"/>
+      <c r="M150" s="55"/>
+    </row>
+    <row r="151" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G151" s="55"/>
+      <c r="J151" s="55"/>
+      <c r="K151" s="55"/>
+      <c r="M151" s="55"/>
+    </row>
+    <row r="152" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G152" s="55"/>
+      <c r="J152" s="55"/>
+      <c r="K152" s="55"/>
+      <c r="M152" s="55"/>
+    </row>
+    <row r="153" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G153" s="55"/>
+      <c r="J153" s="55"/>
+      <c r="K153" s="55"/>
+      <c r="M153" s="55"/>
+    </row>
+    <row r="154" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G154" s="55"/>
+      <c r="J154" s="55"/>
+      <c r="K154" s="55"/>
+      <c r="M154" s="55"/>
+    </row>
+    <row r="155" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G155" s="55"/>
+      <c r="J155" s="55"/>
+      <c r="K155" s="55"/>
+      <c r="M155" s="55"/>
+    </row>
+    <row r="156" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G156" s="55"/>
+      <c r="J156" s="55"/>
+      <c r="K156" s="55"/>
+      <c r="M156" s="55"/>
+    </row>
+    <row r="157" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G157" s="55"/>
+      <c r="J157" s="55"/>
+      <c r="K157" s="55"/>
+      <c r="M157" s="55"/>
+    </row>
+    <row r="158" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G158" s="55"/>
+      <c r="J158" s="55"/>
+      <c r="K158" s="55"/>
+      <c r="M158" s="55"/>
+    </row>
+    <row r="159" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G159" s="55"/>
+      <c r="J159" s="55"/>
+      <c r="K159" s="55"/>
+      <c r="M159" s="55"/>
+    </row>
+    <row r="160" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G160" s="55"/>
+      <c r="J160" s="55"/>
+      <c r="K160" s="55"/>
+      <c r="M160" s="55"/>
+    </row>
+    <row r="161" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G161" s="55"/>
+      <c r="J161" s="55"/>
+      <c r="K161" s="55"/>
+      <c r="M161" s="55"/>
+    </row>
+    <row r="162" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G162" s="55"/>
+      <c r="J162" s="55"/>
+      <c r="K162" s="55"/>
+      <c r="M162" s="55"/>
+    </row>
+    <row r="163" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G163" s="55"/>
+      <c r="J163" s="55"/>
+      <c r="K163" s="55"/>
+      <c r="M163" s="55"/>
+    </row>
+    <row r="164" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G164" s="55"/>
+      <c r="J164" s="55"/>
+      <c r="K164" s="55"/>
+      <c r="M164" s="55"/>
+    </row>
+    <row r="165" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G165" s="55"/>
+      <c r="J165" s="55"/>
+      <c r="K165" s="55"/>
+      <c r="M165" s="55"/>
+    </row>
+    <row r="166" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G166" s="55"/>
+      <c r="J166" s="55"/>
+      <c r="K166" s="55"/>
+      <c r="M166" s="55"/>
+    </row>
+    <row r="167" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G167" s="55"/>
+      <c r="J167" s="55"/>
+      <c r="K167" s="55"/>
+      <c r="M167" s="55"/>
+    </row>
+    <row r="168" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G168" s="55"/>
+      <c r="J168" s="55"/>
+      <c r="K168" s="55"/>
+      <c r="M168" s="55"/>
+    </row>
+    <row r="169" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G169" s="55"/>
+      <c r="J169" s="55"/>
+      <c r="K169" s="55"/>
+      <c r="M169" s="55"/>
+    </row>
+    <row r="170" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G170" s="55"/>
+      <c r="J170" s="55"/>
+      <c r="K170" s="55"/>
+      <c r="M170" s="55"/>
+    </row>
+    <row r="171" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G171" s="55"/>
+      <c r="J171" s="55"/>
+      <c r="K171" s="55"/>
+      <c r="M171" s="55"/>
+    </row>
+    <row r="172" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G172" s="55"/>
+      <c r="J172" s="55"/>
+      <c r="K172" s="55"/>
+      <c r="M172" s="55"/>
+    </row>
+    <row r="173" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G173" s="55"/>
+      <c r="J173" s="55"/>
+      <c r="K173" s="55"/>
+      <c r="M173" s="55"/>
+    </row>
+    <row r="174" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G174" s="55"/>
+      <c r="J174" s="55"/>
+      <c r="K174" s="55"/>
+      <c r="M174" s="55"/>
+    </row>
+    <row r="175" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G175" s="55"/>
+      <c r="J175" s="55"/>
+      <c r="K175" s="55"/>
+      <c r="M175" s="55"/>
+    </row>
+    <row r="176" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G176" s="55"/>
+      <c r="J176" s="55"/>
+      <c r="K176" s="55"/>
+      <c r="M176" s="55"/>
+    </row>
+    <row r="177" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G177" s="55"/>
+      <c r="J177" s="55"/>
+      <c r="K177" s="55"/>
+      <c r="M177" s="55"/>
+    </row>
+    <row r="178" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G178" s="55"/>
+      <c r="J178" s="55"/>
+      <c r="K178" s="55"/>
+      <c r="M178" s="55"/>
+    </row>
+    <row r="179" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G179" s="55"/>
+      <c r="J179" s="55"/>
+      <c r="K179" s="55"/>
+      <c r="M179" s="55"/>
+    </row>
+    <row r="180" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G180" s="55"/>
+      <c r="J180" s="55"/>
+      <c r="K180" s="55"/>
+      <c r="M180" s="55"/>
+    </row>
+    <row r="181" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G181" s="55"/>
+      <c r="J181" s="55"/>
+      <c r="K181" s="55"/>
+      <c r="M181" s="55"/>
+    </row>
+    <row r="182" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G182" s="55"/>
+      <c r="J182" s="55"/>
+      <c r="K182" s="55"/>
+      <c r="M182" s="55"/>
+    </row>
+    <row r="183" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G183" s="55"/>
+      <c r="J183" s="55"/>
+      <c r="K183" s="55"/>
+      <c r="M183" s="55"/>
+    </row>
+    <row r="184" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G184" s="55"/>
+      <c r="J184" s="55"/>
+      <c r="K184" s="55"/>
+      <c r="M184" s="55"/>
+    </row>
+    <row r="185" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G185" s="55"/>
+      <c r="J185" s="55"/>
+      <c r="K185" s="55"/>
+      <c r="M185" s="55"/>
+    </row>
+    <row r="186" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G186" s="55"/>
+      <c r="J186" s="55"/>
+      <c r="K186" s="55"/>
+      <c r="M186" s="55"/>
+    </row>
+    <row r="187" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G187" s="55"/>
+      <c r="J187" s="55"/>
+      <c r="K187" s="55"/>
+      <c r="M187" s="55"/>
+    </row>
+    <row r="188" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G188" s="55"/>
+      <c r="J188" s="55"/>
+      <c r="K188" s="55"/>
+      <c r="M188" s="55"/>
+    </row>
+    <row r="189" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G189" s="55"/>
+      <c r="J189" s="55"/>
+      <c r="K189" s="55"/>
+      <c r="M189" s="55"/>
+    </row>
+    <row r="190" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G190" s="55"/>
+      <c r="J190" s="55"/>
+      <c r="K190" s="55"/>
+      <c r="M190" s="55"/>
+    </row>
+    <row r="191" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G191" s="55"/>
+      <c r="J191" s="55"/>
+      <c r="K191" s="55"/>
+      <c r="M191" s="55"/>
+    </row>
+    <row r="192" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G192" s="55"/>
+      <c r="J192" s="55"/>
+      <c r="K192" s="55"/>
+      <c r="M192" s="55"/>
+    </row>
+    <row r="193" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G193" s="55"/>
+      <c r="J193" s="55"/>
+      <c r="K193" s="55"/>
+      <c r="M193" s="55"/>
+    </row>
+    <row r="194" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G194" s="55"/>
+      <c r="J194" s="55"/>
+      <c r="K194" s="55"/>
+      <c r="M194" s="55"/>
+    </row>
+    <row r="195" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G195" s="55"/>
+      <c r="J195" s="55"/>
+      <c r="K195" s="55"/>
+      <c r="M195" s="55"/>
+    </row>
+    <row r="196" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G196" s="55"/>
+      <c r="J196" s="55"/>
+      <c r="K196" s="55"/>
+      <c r="M196" s="55"/>
+    </row>
+    <row r="197" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G197" s="55"/>
+      <c r="J197" s="55"/>
+      <c r="K197" s="55"/>
+      <c r="M197" s="55"/>
+    </row>
+    <row r="198" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G198" s="55"/>
+      <c r="J198" s="55"/>
+      <c r="K198" s="55"/>
+      <c r="M198" s="55"/>
+    </row>
+    <row r="199" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G199" s="55"/>
+      <c r="J199" s="55"/>
+      <c r="K199" s="55"/>
+      <c r="M199" s="55"/>
+    </row>
+    <row r="200" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G200" s="55"/>
+      <c r="J200" s="55"/>
+      <c r="K200" s="55"/>
+      <c r="M200" s="55"/>
+    </row>
+    <row r="201" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G201" s="55"/>
+      <c r="J201" s="55"/>
+      <c r="K201" s="55"/>
+      <c r="M201" s="55"/>
+    </row>
+    <row r="202" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G202" s="55"/>
+      <c r="J202" s="55"/>
+      <c r="K202" s="55"/>
+      <c r="M202" s="55"/>
+    </row>
+    <row r="203" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G203" s="55"/>
+      <c r="J203" s="55"/>
+      <c r="K203" s="55"/>
+      <c r="M203" s="55"/>
+    </row>
+    <row r="204" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G204" s="55"/>
+      <c r="J204" s="55"/>
+      <c r="K204" s="55"/>
+      <c r="M204" s="55"/>
+    </row>
+    <row r="205" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G205" s="55"/>
+      <c r="J205" s="55"/>
+      <c r="K205" s="55"/>
+      <c r="M205" s="55"/>
+    </row>
+    <row r="206" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G206" s="55"/>
+      <c r="J206" s="55"/>
+      <c r="K206" s="55"/>
+      <c r="M206" s="55"/>
+    </row>
+    <row r="207" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G207" s="55"/>
+      <c r="J207" s="55"/>
+      <c r="K207" s="55"/>
+      <c r="M207" s="55"/>
+    </row>
+    <row r="208" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G208" s="55"/>
+      <c r="J208" s="55"/>
+      <c r="K208" s="55"/>
+      <c r="M208" s="55"/>
+    </row>
+    <row r="209" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G209" s="55"/>
+      <c r="J209" s="55"/>
+      <c r="K209" s="55"/>
+      <c r="M209" s="55"/>
+    </row>
+    <row r="210" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G210" s="55"/>
+      <c r="J210" s="55"/>
+      <c r="K210" s="55"/>
+      <c r="M210" s="55"/>
+    </row>
+    <row r="211" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G211" s="55"/>
+      <c r="J211" s="55"/>
+      <c r="K211" s="55"/>
+      <c r="M211" s="55"/>
+    </row>
+    <row r="212" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G212" s="55"/>
+      <c r="J212" s="55"/>
+      <c r="K212" s="55"/>
+      <c r="M212" s="55"/>
+    </row>
+    <row r="213" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G213" s="55"/>
+      <c r="J213" s="55"/>
+      <c r="K213" s="55"/>
+      <c r="M213" s="55"/>
+    </row>
+    <row r="214" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G214" s="55"/>
+      <c r="J214" s="55"/>
+      <c r="K214" s="55"/>
+      <c r="M214" s="55"/>
+    </row>
+    <row r="215" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G215" s="55"/>
+      <c r="J215" s="55"/>
+      <c r="K215" s="55"/>
+      <c r="M215" s="55"/>
+    </row>
+    <row r="216" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G216" s="55"/>
+      <c r="J216" s="55"/>
+      <c r="K216" s="55"/>
+      <c r="M216" s="55"/>
+    </row>
+    <row r="217" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G217" s="55"/>
+      <c r="J217" s="55"/>
+      <c r="K217" s="55"/>
+      <c r="M217" s="55"/>
+    </row>
+    <row r="218" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G218" s="55"/>
+      <c r="J218" s="55"/>
+      <c r="K218" s="55"/>
+      <c r="M218" s="55"/>
+    </row>
+    <row r="219" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G219" s="55"/>
+      <c r="J219" s="55"/>
+      <c r="K219" s="55"/>
+      <c r="M219" s="55"/>
+    </row>
+    <row r="220" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G220" s="55"/>
+      <c r="J220" s="55"/>
+      <c r="K220" s="55"/>
+      <c r="M220" s="55"/>
+    </row>
+    <row r="221" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G221" s="55"/>
+      <c r="J221" s="55"/>
+      <c r="K221" s="55"/>
+      <c r="M221" s="55"/>
+    </row>
+    <row r="222" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G222" s="55"/>
+      <c r="J222" s="55"/>
+      <c r="K222" s="55"/>
+      <c r="M222" s="55"/>
+    </row>
+    <row r="223" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G223" s="55"/>
+      <c r="J223" s="55"/>
+      <c r="K223" s="55"/>
+      <c r="M223" s="55"/>
+    </row>
+    <row r="224" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G224" s="55"/>
+      <c r="J224" s="55"/>
+      <c r="K224" s="55"/>
+      <c r="M224" s="55"/>
+    </row>
+    <row r="225" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G225" s="55"/>
+      <c r="J225" s="55"/>
+      <c r="K225" s="55"/>
+      <c r="M225" s="55"/>
+    </row>
+    <row r="226" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G226" s="55"/>
+      <c r="J226" s="55"/>
+      <c r="K226" s="55"/>
+      <c r="M226" s="55"/>
+    </row>
+    <row r="227" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G227" s="55"/>
+      <c r="J227" s="55"/>
+      <c r="K227" s="55"/>
+      <c r="M227" s="55"/>
+    </row>
+    <row r="228" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G228" s="55"/>
+      <c r="J228" s="55"/>
+      <c r="K228" s="55"/>
+      <c r="M228" s="55"/>
+    </row>
+    <row r="229" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G229" s="55"/>
+      <c r="J229" s="55"/>
+      <c r="K229" s="55"/>
+      <c r="M229" s="55"/>
+    </row>
+    <row r="230" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G230" s="55"/>
+      <c r="J230" s="55"/>
+      <c r="K230" s="55"/>
+      <c r="M230" s="55"/>
+    </row>
+    <row r="231" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G231" s="55"/>
+      <c r="J231" s="55"/>
+      <c r="K231" s="55"/>
+      <c r="M231" s="55"/>
+    </row>
+    <row r="232" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G232" s="55"/>
+      <c r="J232" s="55"/>
+      <c r="K232" s="55"/>
+      <c r="M232" s="55"/>
+    </row>
+    <row r="233" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G233" s="55"/>
+      <c r="J233" s="55"/>
+      <c r="K233" s="55"/>
+      <c r="M233" s="55"/>
+    </row>
+    <row r="234" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G234" s="55"/>
+      <c r="J234" s="55"/>
+      <c r="K234" s="55"/>
+      <c r="M234" s="55"/>
+    </row>
+    <row r="235" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G235" s="55"/>
+      <c r="J235" s="55"/>
+      <c r="K235" s="55"/>
+      <c r="M235" s="55"/>
+    </row>
+    <row r="236" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G236" s="55"/>
+      <c r="J236" s="55"/>
+      <c r="K236" s="55"/>
+      <c r="M236" s="55"/>
+    </row>
+    <row r="237" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G237" s="55"/>
+      <c r="J237" s="55"/>
+      <c r="K237" s="55"/>
+      <c r="M237" s="55"/>
+    </row>
+    <row r="238" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G238" s="55"/>
+      <c r="J238" s="55"/>
+      <c r="K238" s="55"/>
+      <c r="M238" s="55"/>
+    </row>
+    <row r="239" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G239" s="55"/>
+      <c r="J239" s="55"/>
+      <c r="K239" s="55"/>
+      <c r="M239" s="55"/>
+    </row>
+    <row r="240" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G240" s="55"/>
+      <c r="J240" s="55"/>
+      <c r="K240" s="55"/>
+      <c r="M240" s="55"/>
+    </row>
+    <row r="241" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G241" s="55"/>
+      <c r="J241" s="55"/>
+      <c r="K241" s="55"/>
+      <c r="M241" s="55"/>
+    </row>
+    <row r="242" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G242" s="55"/>
+      <c r="J242" s="55"/>
+      <c r="K242" s="55"/>
+      <c r="M242" s="55"/>
+    </row>
+    <row r="243" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G243" s="55"/>
+      <c r="J243" s="55"/>
+      <c r="K243" s="55"/>
+      <c r="M243" s="55"/>
+    </row>
+    <row r="244" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G244" s="55"/>
+      <c r="J244" s="55"/>
+      <c r="K244" s="55"/>
+      <c r="M244" s="55"/>
+    </row>
+    <row r="245" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G245" s="55"/>
+      <c r="J245" s="55"/>
+      <c r="K245" s="55"/>
+      <c r="M245" s="55"/>
+    </row>
+    <row r="246" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G246" s="55"/>
+      <c r="J246" s="55"/>
+      <c r="K246" s="55"/>
+      <c r="M246" s="55"/>
+    </row>
+    <row r="247" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G247" s="55"/>
+      <c r="J247" s="55"/>
+      <c r="K247" s="55"/>
+      <c r="M247" s="55"/>
+    </row>
+    <row r="248" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G248" s="55"/>
+      <c r="J248" s="55"/>
+      <c r="K248" s="55"/>
+      <c r="M248" s="55"/>
+    </row>
+    <row r="249" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G249" s="55"/>
+      <c r="J249" s="55"/>
+      <c r="K249" s="55"/>
+      <c r="M249" s="55"/>
+    </row>
+    <row r="250" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G250" s="55"/>
+      <c r="J250" s="55"/>
+      <c r="K250" s="55"/>
+      <c r="M250" s="55"/>
+    </row>
+    <row r="251" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G251" s="55"/>
+      <c r="J251" s="55"/>
+      <c r="K251" s="55"/>
+      <c r="M251" s="55"/>
+    </row>
+    <row r="252" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G252" s="55"/>
+      <c r="J252" s="55"/>
+      <c r="K252" s="55"/>
+      <c r="M252" s="55"/>
+    </row>
+    <row r="253" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G253" s="55"/>
+      <c r="J253" s="55"/>
+      <c r="K253" s="55"/>
+      <c r="M253" s="55"/>
+    </row>
+    <row r="254" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G254" s="55"/>
+      <c r="J254" s="55"/>
+      <c r="K254" s="55"/>
+      <c r="M254" s="55"/>
+    </row>
+    <row r="255" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G255" s="55"/>
+      <c r="J255" s="55"/>
+      <c r="K255" s="55"/>
+      <c r="M255" s="55"/>
+    </row>
+    <row r="256" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G256" s="55"/>
+      <c r="J256" s="55"/>
+      <c r="K256" s="55"/>
+      <c r="M256" s="55"/>
+    </row>
+    <row r="257" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G257" s="55"/>
+      <c r="J257" s="55"/>
+      <c r="K257" s="55"/>
+      <c r="M257" s="55"/>
+    </row>
+    <row r="258" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G258" s="55"/>
+      <c r="J258" s="55"/>
+      <c r="K258" s="55"/>
+      <c r="M258" s="55"/>
+    </row>
+    <row r="259" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G259" s="55"/>
+      <c r="J259" s="55"/>
+      <c r="K259" s="55"/>
+      <c r="M259" s="55"/>
+    </row>
+    <row r="260" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G260" s="55"/>
+      <c r="J260" s="55"/>
+      <c r="K260" s="55"/>
+      <c r="M260" s="55"/>
+    </row>
+    <row r="261" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G261" s="55"/>
+      <c r="J261" s="55"/>
+      <c r="K261" s="55"/>
+      <c r="M261" s="55"/>
+    </row>
+    <row r="262" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G262" s="55"/>
+      <c r="J262" s="55"/>
+      <c r="K262" s="55"/>
+      <c r="M262" s="55"/>
+    </row>
+    <row r="263" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G263" s="55"/>
+      <c r="J263" s="55"/>
+      <c r="K263" s="55"/>
+      <c r="M263" s="55"/>
+    </row>
+    <row r="264" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G264" s="55"/>
+      <c r="J264" s="55"/>
+      <c r="K264" s="55"/>
+      <c r="M264" s="55"/>
+    </row>
+    <row r="265" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G265" s="55"/>
+      <c r="J265" s="55"/>
+      <c r="K265" s="55"/>
+      <c r="M265" s="55"/>
+    </row>
+    <row r="266" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G266" s="55"/>
+      <c r="J266" s="55"/>
+      <c r="K266" s="55"/>
+      <c r="M266" s="55"/>
+    </row>
+    <row r="267" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G267" s="55"/>
+      <c r="J267" s="55"/>
+      <c r="K267" s="55"/>
+      <c r="M267" s="55"/>
+    </row>
+    <row r="268" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G268" s="55"/>
+      <c r="J268" s="55"/>
+      <c r="K268" s="55"/>
+      <c r="M268" s="55"/>
+    </row>
+    <row r="269" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G269" s="55"/>
+      <c r="J269" s="55"/>
+      <c r="K269" s="55"/>
+      <c r="M269" s="55"/>
+    </row>
+    <row r="270" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G270" s="55"/>
+      <c r="J270" s="55"/>
+      <c r="K270" s="55"/>
+      <c r="M270" s="55"/>
+    </row>
+    <row r="271" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G271" s="55"/>
+      <c r="J271" s="55"/>
+      <c r="K271" s="55"/>
+      <c r="M271" s="55"/>
+    </row>
+    <row r="272" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G272" s="55"/>
+      <c r="J272" s="55"/>
+      <c r="K272" s="55"/>
+      <c r="M272" s="55"/>
+    </row>
+    <row r="273" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G273" s="55"/>
+      <c r="J273" s="55"/>
+      <c r="K273" s="55"/>
+      <c r="M273" s="55"/>
+    </row>
+    <row r="274" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G274" s="55"/>
+      <c r="J274" s="55"/>
+      <c r="K274" s="55"/>
+      <c r="M274" s="55"/>
+    </row>
+    <row r="275" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G275" s="55"/>
+      <c r="J275" s="55"/>
+      <c r="K275" s="55"/>
+      <c r="M275" s="55"/>
+    </row>
+    <row r="276" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G276" s="55"/>
+      <c r="J276" s="55"/>
+      <c r="K276" s="55"/>
+      <c r="M276" s="55"/>
+    </row>
+    <row r="277" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G277" s="55"/>
+      <c r="J277" s="55"/>
+      <c r="K277" s="55"/>
+      <c r="M277" s="55"/>
+    </row>
+    <row r="278" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G278" s="55"/>
+      <c r="J278" s="55"/>
+      <c r="K278" s="55"/>
+      <c r="M278" s="55"/>
+    </row>
+    <row r="279" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G279" s="55"/>
+      <c r="J279" s="55"/>
+      <c r="K279" s="55"/>
+      <c r="M279" s="55"/>
+    </row>
+    <row r="280" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G280" s="55"/>
+      <c r="J280" s="55"/>
+      <c r="K280" s="55"/>
+      <c r="M280" s="55"/>
+    </row>
+    <row r="281" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G281" s="55"/>
+      <c r="J281" s="55"/>
+      <c r="K281" s="55"/>
+      <c r="M281" s="55"/>
+    </row>
+    <row r="282" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G282" s="55"/>
+      <c r="J282" s="55"/>
+      <c r="K282" s="55"/>
+      <c r="M282" s="55"/>
+    </row>
+    <row r="283" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G283" s="55"/>
+      <c r="J283" s="55"/>
+      <c r="K283" s="55"/>
+      <c r="M283" s="55"/>
+    </row>
+    <row r="284" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G284" s="55"/>
+      <c r="J284" s="55"/>
+      <c r="K284" s="55"/>
+      <c r="M284" s="55"/>
+    </row>
+    <row r="285" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G285" s="55"/>
+      <c r="J285" s="55"/>
+      <c r="K285" s="55"/>
+      <c r="M285" s="55"/>
+    </row>
+    <row r="286" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G286" s="55"/>
+      <c r="J286" s="55"/>
+      <c r="K286" s="55"/>
+      <c r="M286" s="55"/>
+    </row>
+    <row r="287" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G287" s="55"/>
+      <c r="J287" s="55"/>
+      <c r="K287" s="55"/>
+      <c r="M287" s="55"/>
+    </row>
+    <row r="288" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G288" s="55"/>
+      <c r="J288" s="55"/>
+      <c r="K288" s="55"/>
+      <c r="M288" s="55"/>
+    </row>
+    <row r="289" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G289" s="55"/>
+      <c r="J289" s="55"/>
+      <c r="K289" s="55"/>
+      <c r="M289" s="55"/>
+    </row>
+    <row r="290" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G290" s="55"/>
+      <c r="J290" s="55"/>
+      <c r="K290" s="55"/>
+      <c r="M290" s="55"/>
+    </row>
+    <row r="291" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G291" s="55"/>
+      <c r="J291" s="55"/>
+      <c r="K291" s="55"/>
+      <c r="M291" s="55"/>
+    </row>
+    <row r="292" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G292" s="55"/>
+      <c r="J292" s="55"/>
+      <c r="K292" s="55"/>
+      <c r="M292" s="55"/>
+    </row>
+    <row r="293" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G293" s="55"/>
+      <c r="J293" s="55"/>
+      <c r="K293" s="55"/>
+      <c r="M293" s="55"/>
+    </row>
+    <row r="294" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G294" s="55"/>
+      <c r="J294" s="55"/>
+      <c r="K294" s="55"/>
+      <c r="M294" s="55"/>
+    </row>
+    <row r="295" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G295" s="55"/>
+      <c r="J295" s="55"/>
+      <c r="K295" s="55"/>
+      <c r="M295" s="55"/>
+    </row>
+    <row r="296" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G296" s="55"/>
+      <c r="J296" s="55"/>
+      <c r="K296" s="55"/>
+      <c r="M296" s="55"/>
+    </row>
+    <row r="297" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G297" s="55"/>
+      <c r="J297" s="55"/>
+      <c r="K297" s="55"/>
+      <c r="M297" s="55"/>
+    </row>
+    <row r="298" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G298" s="55"/>
+      <c r="J298" s="55"/>
+      <c r="K298" s="55"/>
+      <c r="M298" s="55"/>
+    </row>
+    <row r="299" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G299" s="55"/>
+      <c r="J299" s="55"/>
+      <c r="K299" s="55"/>
+      <c r="M299" s="55"/>
+    </row>
+    <row r="300" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G300" s="55"/>
+      <c r="J300" s="55"/>
+      <c r="K300" s="55"/>
+      <c r="M300" s="55"/>
+    </row>
+    <row r="301" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G301" s="55"/>
+      <c r="J301" s="55"/>
+      <c r="K301" s="55"/>
+      <c r="M301" s="55"/>
+    </row>
+    <row r="302" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G302" s="55"/>
+      <c r="J302" s="55"/>
+      <c r="K302" s="55"/>
+      <c r="M302" s="55"/>
+    </row>
+    <row r="303" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G303" s="55"/>
+      <c r="J303" s="55"/>
+      <c r="K303" s="55"/>
+      <c r="M303" s="55"/>
+    </row>
+    <row r="304" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G304" s="55"/>
+      <c r="J304" s="55"/>
+      <c r="K304" s="55"/>
+      <c r="M304" s="55"/>
+    </row>
+    <row r="305" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G305" s="55"/>
+      <c r="J305" s="55"/>
+      <c r="K305" s="55"/>
+      <c r="M305" s="55"/>
+    </row>
+    <row r="306" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G306" s="55"/>
+      <c r="J306" s="55"/>
+      <c r="K306" s="55"/>
+      <c r="M306" s="55"/>
+    </row>
+    <row r="307" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G307" s="55"/>
+      <c r="J307" s="55"/>
+      <c r="K307" s="55"/>
+      <c r="M307" s="55"/>
+    </row>
+    <row r="308" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G308" s="55"/>
+      <c r="J308" s="55"/>
+      <c r="K308" s="55"/>
+      <c r="M308" s="55"/>
+    </row>
+    <row r="309" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G309" s="55"/>
+      <c r="J309" s="55"/>
+      <c r="K309" s="55"/>
+      <c r="M309" s="55"/>
+    </row>
+    <row r="310" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G310" s="55"/>
+      <c r="J310" s="55"/>
+      <c r="K310" s="55"/>
+      <c r="M310" s="55"/>
+    </row>
+    <row r="311" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G311" s="55"/>
+      <c r="J311" s="55"/>
+      <c r="K311" s="55"/>
+      <c r="M311" s="55"/>
+    </row>
+    <row r="312" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G312" s="55"/>
+      <c r="J312" s="55"/>
+      <c r="K312" s="55"/>
+      <c r="M312" s="55"/>
+    </row>
+    <row r="313" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G313" s="55"/>
+      <c r="J313" s="55"/>
+      <c r="K313" s="55"/>
+      <c r="M313" s="55"/>
+    </row>
+    <row r="314" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G314" s="55"/>
+      <c r="J314" s="55"/>
+      <c r="K314" s="55"/>
+      <c r="M314" s="55"/>
+    </row>
+    <row r="315" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G315" s="55"/>
+      <c r="J315" s="55"/>
+      <c r="K315" s="55"/>
+      <c r="M315" s="55"/>
+    </row>
+    <row r="316" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G316" s="55"/>
+      <c r="J316" s="55"/>
+      <c r="K316" s="55"/>
+      <c r="M316" s="55"/>
+    </row>
+    <row r="317" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G317" s="55"/>
+      <c r="J317" s="55"/>
+      <c r="K317" s="55"/>
+      <c r="M317" s="55"/>
+    </row>
+    <row r="318" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G318" s="55"/>
+      <c r="J318" s="55"/>
+      <c r="K318" s="55"/>
+      <c r="M318" s="55"/>
+    </row>
+    <row r="319" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G319" s="55"/>
+      <c r="J319" s="55"/>
+      <c r="K319" s="55"/>
+      <c r="M319" s="55"/>
+    </row>
+    <row r="320" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G320" s="55"/>
+      <c r="J320" s="55"/>
+      <c r="K320" s="55"/>
+      <c r="M320" s="55"/>
+    </row>
+    <row r="321" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G321" s="55"/>
+      <c r="J321" s="55"/>
+      <c r="K321" s="55"/>
+      <c r="M321" s="55"/>
+    </row>
+    <row r="322" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G322" s="55"/>
+      <c r="J322" s="55"/>
+      <c r="K322" s="55"/>
+      <c r="M322" s="55"/>
+    </row>
+    <row r="323" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G323" s="55"/>
+      <c r="J323" s="55"/>
+      <c r="K323" s="55"/>
+      <c r="M323" s="55"/>
+    </row>
+    <row r="324" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G324" s="55"/>
+      <c r="J324" s="55"/>
+      <c r="K324" s="55"/>
+      <c r="M324" s="55"/>
+    </row>
+    <row r="325" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G325" s="55"/>
+      <c r="J325" s="55"/>
+      <c r="K325" s="55"/>
+      <c r="M325" s="55"/>
+    </row>
+    <row r="326" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G326" s="55"/>
+      <c r="J326" s="55"/>
+      <c r="K326" s="55"/>
+      <c r="M326" s="55"/>
+    </row>
+    <row r="327" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G327" s="55"/>
+      <c r="J327" s="55"/>
+      <c r="K327" s="55"/>
+      <c r="M327" s="55"/>
+    </row>
+    <row r="328" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G328" s="55"/>
+      <c r="J328" s="55"/>
+      <c r="K328" s="55"/>
+      <c r="M328" s="55"/>
+    </row>
+    <row r="329" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G329" s="55"/>
+      <c r="J329" s="55"/>
+      <c r="K329" s="55"/>
+      <c r="M329" s="55"/>
+    </row>
+    <row r="330" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G330" s="55"/>
+      <c r="J330" s="55"/>
+      <c r="K330" s="55"/>
+      <c r="M330" s="55"/>
+    </row>
+    <row r="331" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G331" s="55"/>
+      <c r="J331" s="55"/>
+      <c r="K331" s="55"/>
+      <c r="M331" s="55"/>
+    </row>
+    <row r="332" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G332" s="55"/>
+      <c r="J332" s="55"/>
+      <c r="K332" s="55"/>
+      <c r="M332" s="55"/>
+    </row>
+    <row r="333" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G333" s="55"/>
+      <c r="J333" s="55"/>
+      <c r="K333" s="55"/>
+      <c r="M333" s="55"/>
+    </row>
+    <row r="334" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G334" s="55"/>
+      <c r="J334" s="55"/>
+      <c r="K334" s="55"/>
+      <c r="M334" s="55"/>
+    </row>
+    <row r="335" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G335" s="55"/>
+      <c r="J335" s="55"/>
+      <c r="K335" s="55"/>
+      <c r="M335" s="55"/>
+    </row>
+    <row r="336" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G336" s="55"/>
+      <c r="J336" s="55"/>
+      <c r="K336" s="55"/>
+      <c r="M336" s="55"/>
+    </row>
+    <row r="337" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G337" s="55"/>
+      <c r="J337" s="55"/>
+      <c r="K337" s="55"/>
+      <c r="M337" s="55"/>
+    </row>
+    <row r="338" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G338" s="55"/>
+      <c r="J338" s="55"/>
+      <c r="K338" s="55"/>
+      <c r="M338" s="55"/>
+    </row>
+    <row r="339" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G339" s="55"/>
+      <c r="J339" s="55"/>
+      <c r="K339" s="55"/>
+      <c r="M339" s="55"/>
+    </row>
+    <row r="340" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G340" s="55"/>
+      <c r="J340" s="55"/>
+      <c r="K340" s="55"/>
+      <c r="M340" s="55"/>
+    </row>
+    <row r="341" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G341" s="55"/>
+      <c r="J341" s="55"/>
+      <c r="K341" s="55"/>
+      <c r="M341" s="55"/>
+    </row>
+    <row r="342" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G342" s="55"/>
+      <c r="J342" s="55"/>
+      <c r="K342" s="55"/>
+      <c r="M342" s="55"/>
+    </row>
+    <row r="343" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G343" s="55"/>
+      <c r="J343" s="55"/>
+      <c r="K343" s="55"/>
+      <c r="M343" s="55"/>
+    </row>
+    <row r="344" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G344" s="55"/>
+      <c r="J344" s="55"/>
+      <c r="K344" s="55"/>
+      <c r="M344" s="55"/>
+    </row>
+    <row r="345" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G345" s="55"/>
+      <c r="J345" s="55"/>
+      <c r="K345" s="55"/>
+      <c r="M345" s="55"/>
+    </row>
+    <row r="346" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G346" s="55"/>
+      <c r="J346" s="55"/>
+      <c r="K346" s="55"/>
+      <c r="M346" s="55"/>
+    </row>
+    <row r="347" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G347" s="55"/>
+      <c r="J347" s="55"/>
+      <c r="K347" s="55"/>
+      <c r="M347" s="55"/>
+    </row>
+    <row r="348" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G348" s="55"/>
+      <c r="J348" s="55"/>
+      <c r="K348" s="55"/>
+      <c r="M348" s="55"/>
+    </row>
+    <row r="349" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G349" s="55"/>
+      <c r="J349" s="55"/>
+      <c r="K349" s="55"/>
+      <c r="M349" s="55"/>
+    </row>
+    <row r="350" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G350" s="55"/>
+      <c r="J350" s="55"/>
+      <c r="K350" s="55"/>
+      <c r="M350" s="55"/>
+    </row>
+    <row r="351" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G351" s="55"/>
+      <c r="J351" s="55"/>
+      <c r="K351" s="55"/>
+      <c r="M351" s="55"/>
+    </row>
+    <row r="352" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G352" s="55"/>
+      <c r="J352" s="55"/>
+      <c r="K352" s="55"/>
+      <c r="M352" s="55"/>
+    </row>
+    <row r="353" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G353" s="55"/>
+      <c r="J353" s="55"/>
+      <c r="K353" s="55"/>
+      <c r="M353" s="55"/>
+    </row>
+    <row r="354" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G354" s="55"/>
+      <c r="J354" s="55"/>
+      <c r="K354" s="55"/>
+      <c r="M354" s="55"/>
+    </row>
+    <row r="355" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G355" s="55"/>
+      <c r="J355" s="55"/>
+      <c r="K355" s="55"/>
+      <c r="M355" s="55"/>
+    </row>
+    <row r="356" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G356" s="55"/>
+      <c r="J356" s="55"/>
+      <c r="K356" s="55"/>
+      <c r="M356" s="55"/>
+    </row>
+    <row r="357" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G357" s="55"/>
+      <c r="J357" s="55"/>
+      <c r="K357" s="55"/>
+      <c r="M357" s="55"/>
+    </row>
+    <row r="358" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G358" s="55"/>
+      <c r="J358" s="55"/>
+      <c r="K358" s="55"/>
+      <c r="M358" s="55"/>
+    </row>
+    <row r="359" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G359" s="55"/>
+      <c r="J359" s="55"/>
+      <c r="K359" s="55"/>
+      <c r="M359" s="55"/>
+    </row>
+    <row r="360" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G360" s="55"/>
+      <c r="J360" s="55"/>
+      <c r="K360" s="55"/>
+      <c r="M360" s="55"/>
+    </row>
+    <row r="361" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G361" s="55"/>
+      <c r="J361" s="55"/>
+      <c r="K361" s="55"/>
+      <c r="M361" s="55"/>
+    </row>
+    <row r="362" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G362" s="55"/>
+      <c r="J362" s="55"/>
+      <c r="K362" s="55"/>
+      <c r="M362" s="55"/>
+    </row>
+    <row r="363" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G363" s="55"/>
+      <c r="J363" s="55"/>
+      <c r="K363" s="55"/>
+      <c r="M363" s="55"/>
+    </row>
+    <row r="364" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G364" s="55"/>
+      <c r="J364" s="55"/>
+      <c r="K364" s="55"/>
+      <c r="M364" s="55"/>
+    </row>
+    <row r="365" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G365" s="55"/>
+      <c r="J365" s="55"/>
+      <c r="K365" s="55"/>
+      <c r="M365" s="55"/>
+    </row>
+    <row r="366" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G366" s="55"/>
+      <c r="J366" s="55"/>
+      <c r="K366" s="55"/>
+      <c r="M366" s="55"/>
+    </row>
+    <row r="367" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G367" s="55"/>
+      <c r="J367" s="55"/>
+      <c r="K367" s="55"/>
+      <c r="M367" s="55"/>
+    </row>
+    <row r="368" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G368" s="55"/>
+      <c r="J368" s="55"/>
+      <c r="K368" s="55"/>
+      <c r="M368" s="55"/>
+    </row>
+    <row r="369" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G369" s="55"/>
+      <c r="J369" s="55"/>
+      <c r="K369" s="55"/>
+      <c r="M369" s="55"/>
+    </row>
+    <row r="370" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G370" s="55"/>
+      <c r="J370" s="55"/>
+      <c r="K370" s="55"/>
+      <c r="M370" s="55"/>
+    </row>
+    <row r="371" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G371" s="55"/>
+      <c r="J371" s="55"/>
+      <c r="K371" s="55"/>
+      <c r="M371" s="55"/>
+    </row>
+    <row r="372" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G372" s="55"/>
+      <c r="J372" s="55"/>
+      <c r="K372" s="55"/>
+      <c r="M372" s="55"/>
+    </row>
+    <row r="373" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G373" s="55"/>
+      <c r="J373" s="55"/>
+      <c r="K373" s="55"/>
+      <c r="M373" s="55"/>
+    </row>
+    <row r="374" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G374" s="55"/>
+      <c r="J374" s="55"/>
+      <c r="K374" s="55"/>
+      <c r="M374" s="55"/>
+    </row>
+    <row r="375" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G375" s="55"/>
+      <c r="J375" s="55"/>
+      <c r="K375" s="55"/>
+      <c r="M375" s="55"/>
+    </row>
+    <row r="376" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G376" s="55"/>
+      <c r="J376" s="55"/>
+      <c r="K376" s="55"/>
+      <c r="M376" s="55"/>
+    </row>
+    <row r="377" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G377" s="55"/>
+      <c r="J377" s="55"/>
+      <c r="K377" s="55"/>
+      <c r="M377" s="55"/>
+    </row>
+    <row r="378" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G378" s="55"/>
+      <c r="J378" s="55"/>
+      <c r="K378" s="55"/>
+      <c r="M378" s="55"/>
+    </row>
+    <row r="379" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G379" s="55"/>
+      <c r="J379" s="55"/>
+      <c r="K379" s="55"/>
+      <c r="M379" s="55"/>
+    </row>
+    <row r="380" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G380" s="55"/>
+      <c r="J380" s="55"/>
+      <c r="K380" s="55"/>
+      <c r="M380" s="55"/>
+    </row>
+    <row r="381" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G381" s="55"/>
+      <c r="J381" s="55"/>
+      <c r="K381" s="55"/>
+      <c r="M381" s="55"/>
+    </row>
+    <row r="382" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G382" s="55"/>
+      <c r="J382" s="55"/>
+      <c r="K382" s="55"/>
+      <c r="M382" s="55"/>
+    </row>
+    <row r="383" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G383" s="55"/>
+      <c r="J383" s="55"/>
+      <c r="K383" s="55"/>
+      <c r="M383" s="55"/>
+    </row>
+    <row r="384" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G384" s="55"/>
+      <c r="J384" s="55"/>
+      <c r="K384" s="55"/>
+      <c r="M384" s="55"/>
+    </row>
+    <row r="385" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G385" s="55"/>
+      <c r="J385" s="55"/>
+      <c r="K385" s="55"/>
+      <c r="M385" s="55"/>
+    </row>
+    <row r="386" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G386" s="55"/>
+      <c r="J386" s="55"/>
+      <c r="K386" s="55"/>
+      <c r="M386" s="55"/>
+    </row>
+    <row r="387" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G387" s="55"/>
+      <c r="J387" s="55"/>
+      <c r="K387" s="55"/>
+      <c r="M387" s="55"/>
+    </row>
+    <row r="388" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G388" s="55"/>
+      <c r="J388" s="55"/>
+      <c r="K388" s="55"/>
+      <c r="M388" s="55"/>
+    </row>
+    <row r="389" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G389" s="55"/>
+      <c r="J389" s="55"/>
+      <c r="K389" s="55"/>
+      <c r="M389" s="55"/>
+    </row>
+    <row r="390" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G390" s="55"/>
+      <c r="J390" s="55"/>
+      <c r="K390" s="55"/>
+      <c r="M390" s="55"/>
+    </row>
+    <row r="391" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G391" s="55"/>
+      <c r="J391" s="55"/>
+      <c r="K391" s="55"/>
+      <c r="M391" s="55"/>
+    </row>
+    <row r="392" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G392" s="55"/>
+      <c r="J392" s="55"/>
+      <c r="K392" s="55"/>
+      <c r="M392" s="55"/>
+    </row>
+    <row r="393" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G393" s="55"/>
+      <c r="J393" s="55"/>
+      <c r="K393" s="55"/>
+      <c r="M393" s="55"/>
+    </row>
+    <row r="394" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G394" s="55"/>
+      <c r="J394" s="55"/>
+      <c r="K394" s="55"/>
+      <c r="M394" s="55"/>
+    </row>
+    <row r="395" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G395" s="55"/>
+      <c r="J395" s="55"/>
+      <c r="K395" s="55"/>
+      <c r="M395" s="55"/>
+    </row>
+    <row r="396" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G396" s="55"/>
+      <c r="J396" s="55"/>
+      <c r="K396" s="55"/>
+      <c r="M396" s="55"/>
+    </row>
+    <row r="397" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G397" s="55"/>
+      <c r="J397" s="55"/>
+      <c r="K397" s="55"/>
+      <c r="M397" s="55"/>
+    </row>
+    <row r="398" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G398" s="55"/>
+      <c r="J398" s="55"/>
+      <c r="K398" s="55"/>
+      <c r="M398" s="55"/>
+    </row>
+    <row r="399" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G399" s="55"/>
+      <c r="J399" s="55"/>
+      <c r="K399" s="55"/>
+      <c r="M399" s="55"/>
+    </row>
+    <row r="400" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G400" s="55"/>
+      <c r="J400" s="55"/>
+      <c r="K400" s="55"/>
+      <c r="M400" s="55"/>
+    </row>
+    <row r="401" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G401" s="55"/>
+      <c r="J401" s="55"/>
+      <c r="K401" s="55"/>
+      <c r="M401" s="55"/>
+    </row>
+    <row r="402" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G402" s="55"/>
+      <c r="J402" s="55"/>
+      <c r="K402" s="55"/>
+      <c r="M402" s="55"/>
+    </row>
+    <row r="403" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G403" s="55"/>
+      <c r="J403" s="55"/>
+      <c r="K403" s="55"/>
+      <c r="M403" s="55"/>
+    </row>
+    <row r="404" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G404" s="55"/>
+      <c r="J404" s="55"/>
+      <c r="K404" s="55"/>
+      <c r="M404" s="55"/>
+    </row>
+    <row r="405" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G405" s="55"/>
+      <c r="J405" s="55"/>
+      <c r="K405" s="55"/>
+      <c r="M405" s="55"/>
+    </row>
+    <row r="406" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G406" s="55"/>
+      <c r="J406" s="55"/>
+      <c r="K406" s="55"/>
+      <c r="M406" s="55"/>
+    </row>
+    <row r="407" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G407" s="55"/>
+      <c r="J407" s="55"/>
+      <c r="K407" s="55"/>
+      <c r="M407" s="55"/>
+    </row>
+    <row r="408" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G408" s="55"/>
+      <c r="J408" s="55"/>
+      <c r="K408" s="55"/>
+      <c r="M408" s="55"/>
+    </row>
+    <row r="409" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G409" s="55"/>
+      <c r="J409" s="55"/>
+      <c r="K409" s="55"/>
+      <c r="M409" s="55"/>
+    </row>
+    <row r="410" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G410" s="55"/>
+      <c r="J410" s="55"/>
+      <c r="K410" s="55"/>
+      <c r="M410" s="55"/>
+    </row>
+    <row r="411" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G411" s="55"/>
+      <c r="J411" s="55"/>
+      <c r="K411" s="55"/>
+      <c r="M411" s="55"/>
+    </row>
+    <row r="412" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G412" s="55"/>
+      <c r="J412" s="55"/>
+      <c r="K412" s="55"/>
+      <c r="M412" s="55"/>
+    </row>
+    <row r="413" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G413" s="55"/>
+      <c r="J413" s="55"/>
+      <c r="K413" s="55"/>
+      <c r="M413" s="55"/>
+    </row>
+    <row r="414" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G414" s="55"/>
+      <c r="J414" s="55"/>
+      <c r="K414" s="55"/>
+      <c r="M414" s="55"/>
+    </row>
+    <row r="415" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G415" s="55"/>
+      <c r="J415" s="55"/>
+      <c r="K415" s="55"/>
+      <c r="M415" s="55"/>
+    </row>
+    <row r="416" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G416" s="55"/>
+      <c r="J416" s="55"/>
+      <c r="K416" s="55"/>
+      <c r="M416" s="55"/>
+    </row>
+    <row r="417" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G417" s="55"/>
+      <c r="J417" s="55"/>
+      <c r="K417" s="55"/>
+      <c r="M417" s="55"/>
+    </row>
+    <row r="418" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G418" s="55"/>
+      <c r="J418" s="55"/>
+      <c r="K418" s="55"/>
+      <c r="M418" s="55"/>
+    </row>
+    <row r="419" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G419" s="55"/>
+      <c r="J419" s="55"/>
+      <c r="K419" s="55"/>
+      <c r="M419" s="55"/>
+    </row>
+    <row r="420" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G420" s="55"/>
+      <c r="J420" s="55"/>
+      <c r="K420" s="55"/>
+      <c r="M420" s="55"/>
+    </row>
+    <row r="421" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G421" s="55"/>
+      <c r="J421" s="55"/>
+      <c r="K421" s="55"/>
+      <c r="M421" s="55"/>
+    </row>
+    <row r="422" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G422" s="55"/>
+      <c r="J422" s="55"/>
+      <c r="K422" s="55"/>
+      <c r="M422" s="55"/>
+    </row>
+    <row r="423" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G423" s="55"/>
+      <c r="J423" s="55"/>
+      <c r="K423" s="55"/>
+      <c r="M423" s="55"/>
+    </row>
+    <row r="424" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G424" s="55"/>
+      <c r="J424" s="55"/>
+      <c r="K424" s="55"/>
+      <c r="M424" s="55"/>
+    </row>
+    <row r="425" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G425" s="55"/>
+      <c r="J425" s="55"/>
+      <c r="K425" s="55"/>
+      <c r="M425" s="55"/>
+    </row>
+    <row r="426" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G426" s="55"/>
+      <c r="J426" s="55"/>
+      <c r="K426" s="55"/>
+      <c r="M426" s="55"/>
+    </row>
+    <row r="427" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G427" s="55"/>
+      <c r="J427" s="55"/>
+      <c r="K427" s="55"/>
+      <c r="M427" s="55"/>
+    </row>
+    <row r="428" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G428" s="55"/>
+      <c r="J428" s="55"/>
+      <c r="K428" s="55"/>
+      <c r="M428" s="55"/>
+    </row>
+    <row r="429" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G429" s="55"/>
+      <c r="J429" s="55"/>
+      <c r="K429" s="55"/>
+      <c r="M429" s="55"/>
+    </row>
+    <row r="430" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G430" s="55"/>
+      <c r="J430" s="55"/>
+      <c r="K430" s="55"/>
+      <c r="M430" s="55"/>
+    </row>
+    <row r="431" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G431" s="55"/>
+      <c r="J431" s="55"/>
+      <c r="K431" s="55"/>
+      <c r="M431" s="55"/>
+    </row>
+    <row r="432" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G432" s="55"/>
+      <c r="J432" s="55"/>
+      <c r="K432" s="55"/>
+      <c r="M432" s="55"/>
+    </row>
+    <row r="433" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G433" s="55"/>
+      <c r="J433" s="55"/>
+      <c r="K433" s="55"/>
+      <c r="M433" s="55"/>
+    </row>
+    <row r="434" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G434" s="55"/>
+      <c r="J434" s="55"/>
+      <c r="K434" s="55"/>
+      <c r="M434" s="55"/>
+    </row>
+    <row r="435" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G435" s="55"/>
+      <c r="J435" s="55"/>
+      <c r="K435" s="55"/>
+      <c r="M435" s="55"/>
+    </row>
+    <row r="436" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G436" s="55"/>
+      <c r="J436" s="55"/>
+      <c r="K436" s="55"/>
+      <c r="M436" s="55"/>
+    </row>
+    <row r="437" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G437" s="55"/>
+      <c r="J437" s="55"/>
+      <c r="K437" s="55"/>
+      <c r="M437" s="55"/>
+    </row>
+    <row r="438" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G438" s="55"/>
+      <c r="J438" s="55"/>
+      <c r="K438" s="55"/>
+      <c r="M438" s="55"/>
+    </row>
+    <row r="439" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G439" s="55"/>
+      <c r="J439" s="55"/>
+      <c r="K439" s="55"/>
+      <c r="M439" s="55"/>
+    </row>
+    <row r="440" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G440" s="55"/>
+      <c r="J440" s="55"/>
+      <c r="K440" s="55"/>
+      <c r="M440" s="55"/>
+    </row>
+    <row r="441" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G441" s="55"/>
+      <c r="J441" s="55"/>
+      <c r="K441" s="55"/>
+      <c r="M441" s="55"/>
+    </row>
+    <row r="442" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G442" s="55"/>
+      <c r="J442" s="55"/>
+      <c r="K442" s="55"/>
+      <c r="M442" s="55"/>
+    </row>
+    <row r="443" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G443" s="55"/>
+      <c r="J443" s="55"/>
+      <c r="K443" s="55"/>
+      <c r="M443" s="55"/>
+    </row>
+    <row r="444" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G444" s="55"/>
+      <c r="J444" s="55"/>
+      <c r="K444" s="55"/>
+      <c r="M444" s="55"/>
+    </row>
+    <row r="445" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G445" s="55"/>
+      <c r="J445" s="55"/>
+      <c r="K445" s="55"/>
+      <c r="M445" s="55"/>
+    </row>
+    <row r="446" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G446" s="55"/>
+      <c r="J446" s="55"/>
+      <c r="K446" s="55"/>
+      <c r="M446" s="55"/>
+    </row>
+    <row r="447" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G447" s="55"/>
+      <c r="J447" s="55"/>
+      <c r="K447" s="55"/>
+      <c r="M447" s="55"/>
+    </row>
+    <row r="448" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G448" s="55"/>
+      <c r="J448" s="55"/>
+      <c r="K448" s="55"/>
+      <c r="M448" s="55"/>
+    </row>
+    <row r="449" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G449" s="55"/>
+      <c r="J449" s="55"/>
+      <c r="K449" s="55"/>
+      <c r="M449" s="55"/>
+    </row>
+    <row r="450" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G450" s="55"/>
+      <c r="J450" s="55"/>
+      <c r="K450" s="55"/>
+      <c r="M450" s="55"/>
+    </row>
+    <row r="451" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G451" s="55"/>
+      <c r="J451" s="55"/>
+      <c r="K451" s="55"/>
+      <c r="M451" s="55"/>
+    </row>
+    <row r="452" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G452" s="55"/>
+      <c r="J452" s="55"/>
+      <c r="K452" s="55"/>
+      <c r="M452" s="55"/>
+    </row>
+    <row r="453" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G453" s="55"/>
+      <c r="J453" s="55"/>
+      <c r="K453" s="55"/>
+      <c r="M453" s="55"/>
+    </row>
+    <row r="454" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G454" s="55"/>
+      <c r="J454" s="55"/>
+      <c r="K454" s="55"/>
+      <c r="M454" s="55"/>
+    </row>
+    <row r="455" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G455" s="55"/>
+      <c r="J455" s="55"/>
+      <c r="K455" s="55"/>
+      <c r="M455" s="55"/>
+    </row>
+    <row r="456" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G456" s="55"/>
+      <c r="J456" s="55"/>
+      <c r="K456" s="55"/>
+      <c r="M456" s="55"/>
+    </row>
+    <row r="457" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G457" s="55"/>
+      <c r="J457" s="55"/>
+      <c r="K457" s="55"/>
+      <c r="M457" s="55"/>
+    </row>
+    <row r="458" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G458" s="55"/>
+      <c r="J458" s="55"/>
+      <c r="K458" s="55"/>
+      <c r="M458" s="55"/>
+    </row>
+    <row r="459" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G459" s="55"/>
+      <c r="J459" s="55"/>
+      <c r="K459" s="55"/>
+      <c r="M459" s="55"/>
+    </row>
+    <row r="460" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G460" s="55"/>
+      <c r="J460" s="55"/>
+      <c r="K460" s="55"/>
+      <c r="M460" s="55"/>
+    </row>
+    <row r="461" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G461" s="55"/>
+      <c r="J461" s="55"/>
+      <c r="K461" s="55"/>
+      <c r="M461" s="55"/>
+    </row>
+    <row r="462" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G462" s="55"/>
+      <c r="J462" s="55"/>
+      <c r="K462" s="55"/>
+      <c r="M462" s="55"/>
+    </row>
+    <row r="463" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G463" s="55"/>
+      <c r="J463" s="55"/>
+      <c r="K463" s="55"/>
+      <c r="M463" s="55"/>
+    </row>
+    <row r="464" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G464" s="55"/>
+      <c r="J464" s="55"/>
+      <c r="K464" s="55"/>
+      <c r="M464" s="55"/>
+    </row>
+    <row r="465" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G465" s="55"/>
+      <c r="J465" s="55"/>
+      <c r="K465" s="55"/>
+      <c r="M465" s="55"/>
+    </row>
+    <row r="466" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G466" s="55"/>
+      <c r="J466" s="55"/>
+      <c r="K466" s="55"/>
+      <c r="M466" s="55"/>
+    </row>
+    <row r="467" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G467" s="55"/>
+      <c r="J467" s="55"/>
+      <c r="K467" s="55"/>
+      <c r="M467" s="55"/>
+    </row>
+    <row r="468" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G468" s="55"/>
+      <c r="J468" s="55"/>
+      <c r="K468" s="55"/>
+      <c r="M468" s="55"/>
+    </row>
+    <row r="469" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G469" s="55"/>
+      <c r="J469" s="55"/>
+      <c r="K469" s="55"/>
+      <c r="M469" s="55"/>
+    </row>
+    <row r="470" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G470" s="55"/>
+      <c r="J470" s="55"/>
+      <c r="K470" s="55"/>
+      <c r="M470" s="55"/>
+    </row>
+    <row r="471" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G471" s="55"/>
+      <c r="J471" s="55"/>
+      <c r="K471" s="55"/>
+      <c r="M471" s="55"/>
+    </row>
+    <row r="472" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G472" s="55"/>
+      <c r="J472" s="55"/>
+      <c r="K472" s="55"/>
+      <c r="M472" s="55"/>
+    </row>
+    <row r="473" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G473" s="55"/>
+      <c r="J473" s="55"/>
+      <c r="K473" s="55"/>
+      <c r="M473" s="55"/>
+    </row>
+    <row r="474" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G474" s="55"/>
+      <c r="J474" s="55"/>
+      <c r="K474" s="55"/>
+      <c r="M474" s="55"/>
+    </row>
+    <row r="475" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G475" s="55"/>
+      <c r="J475" s="55"/>
+      <c r="K475" s="55"/>
+      <c r="M475" s="55"/>
+    </row>
+    <row r="476" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G476" s="55"/>
+      <c r="J476" s="55"/>
+      <c r="K476" s="55"/>
+      <c r="M476" s="55"/>
+    </row>
+    <row r="477" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G477" s="55"/>
+      <c r="J477" s="55"/>
+      <c r="K477" s="55"/>
+      <c r="M477" s="55"/>
+    </row>
+    <row r="478" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G478" s="55"/>
+      <c r="J478" s="55"/>
+      <c r="K478" s="55"/>
+      <c r="M478" s="55"/>
+    </row>
+    <row r="479" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G479" s="55"/>
+      <c r="J479" s="55"/>
+      <c r="K479" s="55"/>
+      <c r="M479" s="55"/>
+    </row>
+    <row r="480" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G480" s="55"/>
+      <c r="J480" s="55"/>
+      <c r="K480" s="55"/>
+      <c r="M480" s="55"/>
+    </row>
+    <row r="481" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G481" s="55"/>
+      <c r="J481" s="55"/>
+      <c r="K481" s="55"/>
+      <c r="M481" s="55"/>
+    </row>
+    <row r="482" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G482" s="55"/>
+      <c r="J482" s="55"/>
+      <c r="K482" s="55"/>
+      <c r="M482" s="55"/>
+    </row>
+    <row r="483" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G483" s="55"/>
+      <c r="J483" s="55"/>
+      <c r="K483" s="55"/>
+      <c r="M483" s="55"/>
+    </row>
+    <row r="484" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G484" s="55"/>
+      <c r="J484" s="55"/>
+      <c r="K484" s="55"/>
+      <c r="M484" s="55"/>
+    </row>
+    <row r="485" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G485" s="55"/>
+      <c r="J485" s="55"/>
+      <c r="K485" s="55"/>
+      <c r="M485" s="55"/>
+    </row>
+    <row r="486" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G486" s="55"/>
+      <c r="J486" s="55"/>
+      <c r="K486" s="55"/>
+      <c r="M486" s="55"/>
+    </row>
+    <row r="487" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G487" s="55"/>
+      <c r="J487" s="55"/>
+      <c r="K487" s="55"/>
+      <c r="M487" s="55"/>
+    </row>
+    <row r="488" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G488" s="55"/>
+      <c r="J488" s="55"/>
+      <c r="K488" s="55"/>
+      <c r="M488" s="55"/>
+    </row>
+    <row r="489" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G489" s="55"/>
+      <c r="J489" s="55"/>
+      <c r="K489" s="55"/>
+      <c r="M489" s="55"/>
+    </row>
+    <row r="490" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G490" s="55"/>
+      <c r="J490" s="55"/>
+      <c r="K490" s="55"/>
+      <c r="M490" s="55"/>
+    </row>
+    <row r="491" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G491" s="55"/>
+      <c r="J491" s="55"/>
+      <c r="K491" s="55"/>
+      <c r="M491" s="55"/>
+    </row>
+    <row r="492" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G492" s="55"/>
+      <c r="J492" s="55"/>
+      <c r="K492" s="55"/>
+      <c r="M492" s="55"/>
+    </row>
+    <row r="493" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G493" s="55"/>
+      <c r="J493" s="55"/>
+      <c r="K493" s="55"/>
+      <c r="M493" s="55"/>
+    </row>
+    <row r="494" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G494" s="55"/>
+      <c r="J494" s="55"/>
+      <c r="K494" s="55"/>
+      <c r="M494" s="55"/>
+    </row>
+    <row r="495" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G495" s="55"/>
+      <c r="J495" s="55"/>
+      <c r="K495" s="55"/>
+      <c r="M495" s="55"/>
+    </row>
+    <row r="496" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G496" s="55"/>
+      <c r="J496" s="55"/>
+      <c r="K496" s="55"/>
+      <c r="M496" s="55"/>
+    </row>
+    <row r="497" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G497" s="55"/>
+      <c r="J497" s="55"/>
+      <c r="K497" s="55"/>
+      <c r="M497" s="55"/>
+    </row>
+    <row r="498" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G498" s="55"/>
+      <c r="J498" s="55"/>
+      <c r="K498" s="55"/>
+      <c r="M498" s="55"/>
+    </row>
+    <row r="499" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G499" s="55"/>
+      <c r="J499" s="55"/>
+      <c r="K499" s="55"/>
+      <c r="M499" s="55"/>
+    </row>
+    <row r="500" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G500" s="55"/>
+      <c r="J500" s="55"/>
+      <c r="K500" s="55"/>
+      <c r="M500" s="55"/>
+    </row>
+    <row r="501" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G501" s="55"/>
+      <c r="J501" s="55"/>
+      <c r="K501" s="55"/>
+      <c r="M501" s="55"/>
+    </row>
+    <row r="502" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G502" s="55"/>
+      <c r="J502" s="55"/>
+      <c r="K502" s="55"/>
+      <c r="M502" s="55"/>
+    </row>
+    <row r="503" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G503" s="55"/>
+      <c r="J503" s="55"/>
+      <c r="K503" s="55"/>
+      <c r="M503" s="55"/>
+    </row>
+    <row r="504" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G504" s="55"/>
+      <c r="J504" s="55"/>
+      <c r="K504" s="55"/>
+      <c r="M504" s="55"/>
+    </row>
+    <row r="505" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G505" s="55"/>
+      <c r="J505" s="55"/>
+      <c r="K505" s="55"/>
+      <c r="M505" s="55"/>
+    </row>
+    <row r="506" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G506" s="55"/>
+      <c r="J506" s="55"/>
+      <c r="K506" s="55"/>
+      <c r="M506" s="55"/>
+    </row>
+    <row r="507" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G507" s="55"/>
+      <c r="J507" s="55"/>
+      <c r="K507" s="55"/>
+      <c r="M507" s="55"/>
+    </row>
+    <row r="508" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G508" s="55"/>
+      <c r="J508" s="55"/>
+      <c r="K508" s="55"/>
+      <c r="M508" s="55"/>
+    </row>
+    <row r="509" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G509" s="55"/>
+      <c r="J509" s="55"/>
+      <c r="K509" s="55"/>
+      <c r="M509" s="55"/>
+    </row>
+    <row r="510" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G510" s="55"/>
+      <c r="J510" s="55"/>
+      <c r="K510" s="55"/>
+      <c r="M510" s="55"/>
+    </row>
+    <row r="511" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G511" s="55"/>
+      <c r="J511" s="55"/>
+      <c r="K511" s="55"/>
+      <c r="M511" s="55"/>
+    </row>
+    <row r="512" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G512" s="55"/>
+      <c r="J512" s="55"/>
+      <c r="K512" s="55"/>
+      <c r="M512" s="55"/>
+    </row>
+    <row r="513" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G513" s="55"/>
+      <c r="J513" s="55"/>
+      <c r="K513" s="55"/>
+      <c r="M513" s="55"/>
+    </row>
+    <row r="514" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G514" s="55"/>
+      <c r="J514" s="55"/>
+      <c r="K514" s="55"/>
+      <c r="M514" s="55"/>
+    </row>
+    <row r="515" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G515" s="55"/>
+      <c r="J515" s="55"/>
+      <c r="K515" s="55"/>
+      <c r="M515" s="55"/>
+    </row>
+    <row r="516" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G516" s="55"/>
+      <c r="J516" s="55"/>
+      <c r="K516" s="55"/>
+      <c r="M516" s="55"/>
+    </row>
+    <row r="517" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G517" s="55"/>
+      <c r="J517" s="55"/>
+      <c r="K517" s="55"/>
+      <c r="M517" s="55"/>
+    </row>
+    <row r="518" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G518" s="55"/>
+      <c r="J518" s="55"/>
+      <c r="K518" s="55"/>
+      <c r="M518" s="55"/>
+    </row>
+    <row r="519" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G519" s="55"/>
+      <c r="J519" s="55"/>
+      <c r="K519" s="55"/>
+      <c r="M519" s="55"/>
+    </row>
+    <row r="520" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G520" s="55"/>
+      <c r="J520" s="55"/>
+      <c r="K520" s="55"/>
+      <c r="M520" s="55"/>
+    </row>
+    <row r="521" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G521" s="55"/>
+      <c r="J521" s="55"/>
+      <c r="K521" s="55"/>
+      <c r="M521" s="55"/>
+    </row>
+    <row r="522" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G522" s="55"/>
+      <c r="J522" s="55"/>
+      <c r="K522" s="55"/>
+      <c r="M522" s="55"/>
+    </row>
+    <row r="523" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G523" s="55"/>
+      <c r="J523" s="55"/>
+      <c r="K523" s="55"/>
+      <c r="M523" s="55"/>
+    </row>
+    <row r="524" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G524" s="55"/>
+      <c r="J524" s="55"/>
+      <c r="K524" s="55"/>
+      <c r="M524" s="55"/>
+    </row>
+    <row r="525" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G525" s="55"/>
+      <c r="J525" s="55"/>
+      <c r="K525" s="55"/>
+      <c r="M525" s="55"/>
+    </row>
+    <row r="526" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G526" s="55"/>
+      <c r="J526" s="55"/>
+      <c r="K526" s="55"/>
+      <c r="M526" s="55"/>
+    </row>
+    <row r="527" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G527" s="55"/>
+      <c r="J527" s="55"/>
+      <c r="K527" s="55"/>
+      <c r="M527" s="55"/>
+    </row>
+    <row r="528" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G528" s="55"/>
+      <c r="J528" s="55"/>
+      <c r="K528" s="55"/>
+      <c r="M528" s="55"/>
+    </row>
+    <row r="529" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G529" s="55"/>
+      <c r="J529" s="55"/>
+      <c r="K529" s="55"/>
+      <c r="M529" s="55"/>
+    </row>
+    <row r="530" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G530" s="55"/>
+      <c r="J530" s="55"/>
+      <c r="K530" s="55"/>
+      <c r="M530" s="55"/>
+    </row>
+    <row r="531" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G531" s="55"/>
+      <c r="J531" s="55"/>
+      <c r="K531" s="55"/>
+      <c r="M531" s="55"/>
+    </row>
+    <row r="532" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G532" s="55"/>
+      <c r="J532" s="55"/>
+      <c r="K532" s="55"/>
+      <c r="M532" s="55"/>
+    </row>
+    <row r="533" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G533" s="55"/>
+      <c r="J533" s="55"/>
+      <c r="K533" s="55"/>
+      <c r="M533" s="55"/>
+    </row>
+    <row r="534" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G534" s="55"/>
+      <c r="J534" s="55"/>
+      <c r="K534" s="55"/>
+      <c r="M534" s="55"/>
+    </row>
+    <row r="535" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G535" s="55"/>
+      <c r="J535" s="55"/>
+      <c r="K535" s="55"/>
+      <c r="M535" s="55"/>
+    </row>
+    <row r="536" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G536" s="55"/>
+      <c r="J536" s="55"/>
+      <c r="K536" s="55"/>
+      <c r="M536" s="55"/>
+    </row>
+    <row r="537" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G537" s="55"/>
+      <c r="J537" s="55"/>
+      <c r="K537" s="55"/>
+      <c r="M537" s="55"/>
+    </row>
+    <row r="538" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G538" s="55"/>
+      <c r="J538" s="55"/>
+      <c r="K538" s="55"/>
+      <c r="M538" s="55"/>
+    </row>
+    <row r="539" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G539" s="55"/>
+      <c r="J539" s="55"/>
+      <c r="K539" s="55"/>
+      <c r="M539" s="55"/>
+    </row>
+    <row r="540" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G540" s="55"/>
+      <c r="J540" s="55"/>
+      <c r="K540" s="55"/>
+      <c r="M540" s="55"/>
+    </row>
+    <row r="541" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G541" s="55"/>
+      <c r="J541" s="55"/>
+      <c r="K541" s="55"/>
+      <c r="M541" s="55"/>
+    </row>
+    <row r="542" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G542" s="55"/>
+      <c r="J542" s="55"/>
+      <c r="K542" s="55"/>
+      <c r="M542" s="55"/>
+    </row>
+    <row r="543" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G543" s="55"/>
+      <c r="J543" s="55"/>
+      <c r="K543" s="55"/>
+      <c r="M543" s="55"/>
+    </row>
+    <row r="544" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G544" s="55"/>
+      <c r="J544" s="55"/>
+      <c r="K544" s="55"/>
+      <c r="M544" s="55"/>
+    </row>
+    <row r="545" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G545" s="55"/>
+      <c r="J545" s="55"/>
+      <c r="K545" s="55"/>
+      <c r="M545" s="55"/>
+    </row>
+    <row r="546" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G546" s="55"/>
+      <c r="J546" s="55"/>
+      <c r="K546" s="55"/>
+      <c r="M546" s="55"/>
+    </row>
+    <row r="547" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G547" s="55"/>
+      <c r="J547" s="55"/>
+      <c r="K547" s="55"/>
+      <c r="M547" s="55"/>
+    </row>
+    <row r="548" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G548" s="55"/>
+      <c r="J548" s="55"/>
+      <c r="K548" s="55"/>
+      <c r="M548" s="55"/>
+    </row>
+    <row r="549" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G549" s="55"/>
+      <c r="J549" s="55"/>
+      <c r="K549" s="55"/>
+      <c r="M549" s="55"/>
+    </row>
+    <row r="550" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G550" s="55"/>
+      <c r="J550" s="55"/>
+      <c r="K550" s="55"/>
+      <c r="M550" s="55"/>
+    </row>
+    <row r="551" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G551" s="55"/>
+      <c r="J551" s="55"/>
+      <c r="K551" s="55"/>
+      <c r="M551" s="55"/>
+    </row>
+    <row r="552" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G552" s="55"/>
+      <c r="J552" s="55"/>
+      <c r="K552" s="55"/>
+      <c r="M552" s="55"/>
+    </row>
+    <row r="553" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G553" s="55"/>
+      <c r="J553" s="55"/>
+      <c r="K553" s="55"/>
+      <c r="M553" s="55"/>
+    </row>
+    <row r="554" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G554" s="55"/>
+      <c r="J554" s="55"/>
+      <c r="K554" s="55"/>
+      <c r="M554" s="55"/>
+    </row>
+    <row r="555" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G555" s="55"/>
+      <c r="J555" s="55"/>
+      <c r="K555" s="55"/>
+      <c r="M555" s="55"/>
+    </row>
+    <row r="556" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G556" s="55"/>
+      <c r="J556" s="55"/>
+      <c r="K556" s="55"/>
+      <c r="M556" s="55"/>
+    </row>
+    <row r="557" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G557" s="55"/>
+      <c r="J557" s="55"/>
+      <c r="K557" s="55"/>
+      <c r="M557" s="55"/>
+    </row>
+    <row r="558" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G558" s="55"/>
+      <c r="J558" s="55"/>
+      <c r="K558" s="55"/>
+      <c r="M558" s="55"/>
+    </row>
+    <row r="559" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G559" s="55"/>
+      <c r="J559" s="55"/>
+      <c r="K559" s="55"/>
+      <c r="M559" s="55"/>
+    </row>
+    <row r="560" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G560" s="55"/>
+      <c r="J560" s="55"/>
+      <c r="K560" s="55"/>
+      <c r="M560" s="55"/>
+    </row>
+    <row r="561" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G561" s="55"/>
+      <c r="J561" s="55"/>
+      <c r="K561" s="55"/>
+      <c r="M561" s="55"/>
+    </row>
+    <row r="562" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G562" s="55"/>
+      <c r="J562" s="55"/>
+      <c r="K562" s="55"/>
+      <c r="M562" s="55"/>
+    </row>
+    <row r="563" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G563" s="55"/>
+      <c r="J563" s="55"/>
+      <c r="K563" s="55"/>
+      <c r="M563" s="55"/>
+    </row>
+    <row r="564" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G564" s="55"/>
+      <c r="J564" s="55"/>
+      <c r="K564" s="55"/>
+      <c r="M564" s="55"/>
+    </row>
+    <row r="565" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G565" s="55"/>
+      <c r="J565" s="55"/>
+      <c r="K565" s="55"/>
+      <c r="M565" s="55"/>
+    </row>
+    <row r="566" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G566" s="55"/>
+      <c r="J566" s="55"/>
+      <c r="K566" s="55"/>
+      <c r="M566" s="55"/>
+    </row>
+    <row r="567" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G567" s="55"/>
+      <c r="J567" s="55"/>
+      <c r="K567" s="55"/>
+      <c r="M567" s="55"/>
+    </row>
+    <row r="568" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G568" s="55"/>
+      <c r="J568" s="55"/>
+      <c r="K568" s="55"/>
+      <c r="M568" s="55"/>
+    </row>
+    <row r="569" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G569" s="55"/>
+      <c r="J569" s="55"/>
+      <c r="K569" s="55"/>
+      <c r="M569" s="55"/>
+    </row>
+    <row r="570" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G570" s="55"/>
+      <c r="J570" s="55"/>
+      <c r="K570" s="55"/>
+      <c r="M570" s="55"/>
+    </row>
+    <row r="571" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G571" s="55"/>
+      <c r="J571" s="55"/>
+      <c r="K571" s="55"/>
+      <c r="M571" s="55"/>
+    </row>
+    <row r="572" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G572" s="55"/>
+      <c r="J572" s="55"/>
+      <c r="K572" s="55"/>
+      <c r="M572" s="55"/>
+    </row>
+    <row r="573" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G573" s="55"/>
+      <c r="J573" s="55"/>
+      <c r="K573" s="55"/>
+      <c r="M573" s="55"/>
+    </row>
+    <row r="574" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G574" s="55"/>
+      <c r="J574" s="55"/>
+      <c r="K574" s="55"/>
+      <c r="M574" s="55"/>
+    </row>
+    <row r="575" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G575" s="55"/>
+      <c r="J575" s="55"/>
+      <c r="K575" s="55"/>
+      <c r="M575" s="55"/>
+    </row>
+    <row r="576" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G576" s="55"/>
+      <c r="J576" s="55"/>
+      <c r="K576" s="55"/>
+      <c r="M576" s="55"/>
+    </row>
+    <row r="577" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G577" s="55"/>
+      <c r="J577" s="55"/>
+      <c r="K577" s="55"/>
+      <c r="M577" s="55"/>
+    </row>
+    <row r="578" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G578" s="55"/>
+      <c r="J578" s="55"/>
+      <c r="K578" s="55"/>
+      <c r="M578" s="55"/>
+    </row>
+    <row r="579" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G579" s="55"/>
+      <c r="J579" s="55"/>
+      <c r="K579" s="55"/>
+      <c r="M579" s="55"/>
+    </row>
+    <row r="580" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G580" s="55"/>
+      <c r="J580" s="55"/>
+      <c r="K580" s="55"/>
+      <c r="M580" s="55"/>
+    </row>
+    <row r="581" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G581" s="55"/>
+      <c r="J581" s="55"/>
+      <c r="K581" s="55"/>
+      <c r="M581" s="55"/>
+    </row>
+    <row r="582" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G582" s="55"/>
+      <c r="J582" s="55"/>
+      <c r="K582" s="55"/>
+      <c r="M582" s="55"/>
+    </row>
+    <row r="583" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G583" s="55"/>
+      <c r="J583" s="55"/>
+      <c r="K583" s="55"/>
+      <c r="M583" s="55"/>
+    </row>
+    <row r="584" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G584" s="55"/>
+      <c r="J584" s="55"/>
+      <c r="K584" s="55"/>
+      <c r="M584" s="55"/>
+    </row>
+    <row r="585" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G585" s="55"/>
+      <c r="J585" s="55"/>
+      <c r="K585" s="55"/>
+      <c r="M585" s="55"/>
+    </row>
+    <row r="586" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G586" s="55"/>
+      <c r="J586" s="55"/>
+      <c r="K586" s="55"/>
+      <c r="M586" s="55"/>
+    </row>
+    <row r="587" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G587" s="55"/>
+      <c r="J587" s="55"/>
+      <c r="K587" s="55"/>
+      <c r="M587" s="55"/>
+    </row>
+    <row r="588" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G588" s="55"/>
+      <c r="J588" s="55"/>
+      <c r="K588" s="55"/>
+      <c r="M588" s="55"/>
+    </row>
+    <row r="589" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G589" s="55"/>
+      <c r="J589" s="55"/>
+      <c r="K589" s="55"/>
+      <c r="M589" s="55"/>
+    </row>
+    <row r="590" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G590" s="55"/>
+      <c r="J590" s="55"/>
+      <c r="K590" s="55"/>
+      <c r="M590" s="55"/>
+    </row>
+    <row r="591" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G591" s="55"/>
+      <c r="J591" s="55"/>
+      <c r="K591" s="55"/>
+      <c r="M591" s="55"/>
+    </row>
+    <row r="592" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G592" s="55"/>
+      <c r="J592" s="55"/>
+      <c r="K592" s="55"/>
+      <c r="M592" s="55"/>
+    </row>
+    <row r="593" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G593" s="55"/>
+      <c r="J593" s="55"/>
+      <c r="K593" s="55"/>
+      <c r="M593" s="55"/>
+    </row>
+    <row r="594" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G594" s="55"/>
+      <c r="J594" s="55"/>
+      <c r="K594" s="55"/>
+      <c r="M594" s="55"/>
+    </row>
+    <row r="595" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G595" s="55"/>
+      <c r="J595" s="55"/>
+      <c r="K595" s="55"/>
+      <c r="M595" s="55"/>
+    </row>
+    <row r="596" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G596" s="55"/>
+      <c r="J596" s="55"/>
+      <c r="K596" s="55"/>
+      <c r="M596" s="55"/>
+    </row>
+    <row r="597" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G597" s="55"/>
+      <c r="J597" s="55"/>
+      <c r="K597" s="55"/>
+      <c r="M597" s="55"/>
+    </row>
+    <row r="598" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G598" s="55"/>
+      <c r="J598" s="55"/>
+      <c r="K598" s="55"/>
+      <c r="M598" s="55"/>
+    </row>
+    <row r="599" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G599" s="55"/>
+      <c r="J599" s="55"/>
+      <c r="K599" s="55"/>
+      <c r="M599" s="55"/>
+    </row>
+    <row r="600" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G600" s="55"/>
+      <c r="J600" s="55"/>
+      <c r="K600" s="55"/>
+      <c r="M600" s="55"/>
+    </row>
+    <row r="601" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G601" s="55"/>
+      <c r="J601" s="55"/>
+      <c r="K601" s="55"/>
+      <c r="M601" s="55"/>
+    </row>
+    <row r="602" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G602" s="55"/>
+      <c r="J602" s="55"/>
+      <c r="K602" s="55"/>
+      <c r="M602" s="55"/>
+    </row>
+    <row r="603" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G603" s="55"/>
+      <c r="J603" s="55"/>
+      <c r="K603" s="55"/>
+      <c r="M603" s="55"/>
+    </row>
+    <row r="604" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G604" s="55"/>
+      <c r="J604" s="55"/>
+      <c r="K604" s="55"/>
+      <c r="M604" s="55"/>
+    </row>
+    <row r="605" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G605" s="55"/>
+      <c r="J605" s="55"/>
+      <c r="K605" s="55"/>
+      <c r="M605" s="55"/>
+    </row>
+    <row r="606" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G606" s="55"/>
+      <c r="J606" s="55"/>
+      <c r="K606" s="55"/>
+      <c r="M606" s="55"/>
+    </row>
+    <row r="607" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G607" s="55"/>
+      <c r="J607" s="55"/>
+      <c r="K607" s="55"/>
+      <c r="M607" s="55"/>
+    </row>
+    <row r="608" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G608" s="55"/>
+      <c r="J608" s="55"/>
+      <c r="K608" s="55"/>
+      <c r="M608" s="55"/>
+    </row>
+    <row r="609" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G609" s="55"/>
+      <c r="J609" s="55"/>
+      <c r="K609" s="55"/>
+      <c r="M609" s="55"/>
+    </row>
+    <row r="610" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G610" s="55"/>
+      <c r="J610" s="55"/>
+      <c r="K610" s="55"/>
+      <c r="M610" s="55"/>
+    </row>
+    <row r="611" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G611" s="55"/>
+      <c r="J611" s="55"/>
+      <c r="K611" s="55"/>
+      <c r="M611" s="55"/>
+    </row>
+    <row r="612" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G612" s="55"/>
+      <c r="J612" s="55"/>
+      <c r="K612" s="55"/>
+      <c r="M612" s="55"/>
+    </row>
+    <row r="613" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G613" s="55"/>
+      <c r="J613" s="55"/>
+      <c r="K613" s="55"/>
+      <c r="M613" s="55"/>
+    </row>
+    <row r="614" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G614" s="55"/>
+      <c r="J614" s="55"/>
+      <c r="K614" s="55"/>
+      <c r="M614" s="55"/>
+    </row>
+    <row r="615" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G615" s="55"/>
+      <c r="J615" s="55"/>
+      <c r="K615" s="55"/>
+      <c r="M615" s="55"/>
+    </row>
+    <row r="616" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G616" s="55"/>
+      <c r="J616" s="55"/>
+      <c r="K616" s="55"/>
+      <c r="M616" s="55"/>
+    </row>
+    <row r="617" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G617" s="55"/>
+      <c r="J617" s="55"/>
+      <c r="K617" s="55"/>
+      <c r="M617" s="55"/>
+    </row>
+    <row r="618" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G618" s="55"/>
+      <c r="J618" s="55"/>
+      <c r="K618" s="55"/>
+      <c r="M618" s="55"/>
+    </row>
+    <row r="619" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G619" s="55"/>
+      <c r="J619" s="55"/>
+      <c r="K619" s="55"/>
+      <c r="M619" s="55"/>
+    </row>
+    <row r="620" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G620" s="55"/>
+      <c r="J620" s="55"/>
+      <c r="K620" s="55"/>
+      <c r="M620" s="55"/>
+    </row>
+    <row r="621" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G621" s="55"/>
+      <c r="J621" s="55"/>
+      <c r="K621" s="55"/>
+      <c r="M621" s="55"/>
+    </row>
+    <row r="622" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G622" s="55"/>
+      <c r="J622" s="55"/>
+      <c r="K622" s="55"/>
+      <c r="M622" s="55"/>
+    </row>
+    <row r="623" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G623" s="55"/>
+      <c r="J623" s="55"/>
+      <c r="K623" s="55"/>
+      <c r="M623" s="55"/>
+    </row>
+    <row r="624" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G624" s="55"/>
+      <c r="J624" s="55"/>
+      <c r="K624" s="55"/>
+      <c r="M624" s="55"/>
+    </row>
+    <row r="625" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G625" s="55"/>
+      <c r="J625" s="55"/>
+      <c r="K625" s="55"/>
+      <c r="M625" s="55"/>
+    </row>
+    <row r="626" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G626" s="55"/>
+      <c r="J626" s="55"/>
+      <c r="K626" s="55"/>
+      <c r="M626" s="55"/>
+    </row>
+    <row r="627" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G627" s="55"/>
+      <c r="J627" s="55"/>
+      <c r="K627" s="55"/>
+      <c r="M627" s="55"/>
+    </row>
+    <row r="628" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G628" s="55"/>
+      <c r="J628" s="55"/>
+      <c r="K628" s="55"/>
+      <c r="M628" s="55"/>
+    </row>
+    <row r="629" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G629" s="55"/>
+      <c r="J629" s="55"/>
+      <c r="K629" s="55"/>
+      <c r="M629" s="55"/>
+    </row>
+    <row r="630" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G630" s="55"/>
+      <c r="J630" s="55"/>
+      <c r="K630" s="55"/>
+      <c r="M630" s="55"/>
+    </row>
+    <row r="631" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G631" s="55"/>
+      <c r="J631" s="55"/>
+      <c r="K631" s="55"/>
+      <c r="M631" s="55"/>
+    </row>
+    <row r="632" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G632" s="55"/>
+      <c r="J632" s="55"/>
+      <c r="K632" s="55"/>
+      <c r="M632" s="55"/>
+    </row>
+    <row r="633" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G633" s="55"/>
+      <c r="J633" s="55"/>
+      <c r="K633" s="55"/>
+      <c r="M633" s="55"/>
+    </row>
+    <row r="634" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G634" s="55"/>
+      <c r="J634" s="55"/>
+      <c r="K634" s="55"/>
+      <c r="M634" s="55"/>
+    </row>
+    <row r="635" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G635" s="55"/>
+      <c r="J635" s="55"/>
+      <c r="K635" s="55"/>
+      <c r="M635" s="55"/>
+    </row>
+    <row r="636" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G636" s="55"/>
+      <c r="J636" s="55"/>
+      <c r="K636" s="55"/>
+      <c r="M636" s="55"/>
+    </row>
+    <row r="637" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G637" s="55"/>
+      <c r="J637" s="55"/>
+      <c r="K637" s="55"/>
+      <c r="M637" s="55"/>
+    </row>
+    <row r="638" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G638" s="55"/>
+      <c r="J638" s="55"/>
+      <c r="K638" s="55"/>
+      <c r="M638" s="55"/>
+    </row>
+    <row r="639" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G639" s="55"/>
+      <c r="J639" s="55"/>
+      <c r="K639" s="55"/>
+      <c r="M639" s="55"/>
+    </row>
+    <row r="640" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G640" s="55"/>
+      <c r="J640" s="55"/>
+      <c r="K640" s="55"/>
+      <c r="M640" s="55"/>
+    </row>
+    <row r="641" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G641" s="55"/>
+      <c r="J641" s="55"/>
+      <c r="K641" s="55"/>
+      <c r="M641" s="55"/>
+    </row>
+    <row r="642" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G642" s="55"/>
+      <c r="J642" s="55"/>
+      <c r="K642" s="55"/>
+      <c r="M642" s="55"/>
+    </row>
+    <row r="643" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G643" s="55"/>
+      <c r="J643" s="55"/>
+      <c r="K643" s="55"/>
+      <c r="M643" s="55"/>
+    </row>
+    <row r="644" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G644" s="55"/>
+      <c r="J644" s="55"/>
+      <c r="K644" s="55"/>
+      <c r="M644" s="55"/>
+    </row>
+    <row r="645" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G645" s="55"/>
+      <c r="J645" s="55"/>
+      <c r="K645" s="55"/>
+      <c r="M645" s="55"/>
+    </row>
+    <row r="646" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G646" s="55"/>
+      <c r="J646" s="55"/>
+      <c r="K646" s="55"/>
+      <c r="M646" s="55"/>
+    </row>
+    <row r="647" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G647" s="55"/>
+      <c r="J647" s="55"/>
+      <c r="K647" s="55"/>
+      <c r="M647" s="55"/>
+    </row>
+    <row r="648" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G648" s="55"/>
+      <c r="J648" s="55"/>
+      <c r="K648" s="55"/>
+      <c r="M648" s="55"/>
+    </row>
+    <row r="649" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G649" s="55"/>
+      <c r="J649" s="55"/>
+      <c r="K649" s="55"/>
+      <c r="M649" s="55"/>
+    </row>
+    <row r="650" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G650" s="55"/>
+      <c r="J650" s="55"/>
+      <c r="K650" s="55"/>
+      <c r="M650" s="55"/>
+    </row>
+    <row r="651" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G651" s="55"/>
+      <c r="J651" s="55"/>
+      <c r="K651" s="55"/>
+      <c r="M651" s="55"/>
+    </row>
+    <row r="652" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G652" s="55"/>
+      <c r="J652" s="55"/>
+      <c r="K652" s="55"/>
+      <c r="M652" s="55"/>
+    </row>
+    <row r="653" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G653" s="55"/>
+      <c r="J653" s="55"/>
+      <c r="K653" s="55"/>
+      <c r="M653" s="55"/>
+    </row>
+    <row r="654" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G654" s="55"/>
+      <c r="J654" s="55"/>
+      <c r="K654" s="55"/>
+      <c r="M654" s="55"/>
+    </row>
+    <row r="655" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G655" s="55"/>
+      <c r="J655" s="55"/>
+      <c r="K655" s="55"/>
+      <c r="M655" s="55"/>
+    </row>
+    <row r="656" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G656" s="55"/>
+      <c r="J656" s="55"/>
+      <c r="K656" s="55"/>
+      <c r="M656" s="55"/>
+    </row>
+    <row r="657" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G657" s="55"/>
+      <c r="J657" s="55"/>
+      <c r="K657" s="55"/>
+      <c r="M657" s="55"/>
+    </row>
+    <row r="658" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G658" s="55"/>
+      <c r="J658" s="55"/>
+      <c r="K658" s="55"/>
+      <c r="M658" s="55"/>
+    </row>
+    <row r="659" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G659" s="55"/>
+      <c r="J659" s="55"/>
+      <c r="K659" s="55"/>
+      <c r="M659" s="55"/>
+    </row>
+    <row r="660" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G660" s="55"/>
+      <c r="J660" s="55"/>
+      <c r="K660" s="55"/>
+      <c r="M660" s="55"/>
+    </row>
+    <row r="661" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G661" s="55"/>
+      <c r="J661" s="55"/>
+      <c r="K661" s="55"/>
+      <c r="M661" s="55"/>
+    </row>
+    <row r="662" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G662" s="55"/>
+      <c r="J662" s="55"/>
+      <c r="K662" s="55"/>
+      <c r="M662" s="55"/>
+    </row>
+    <row r="663" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G663" s="55"/>
+      <c r="J663" s="55"/>
+      <c r="K663" s="55"/>
+      <c r="M663" s="55"/>
+    </row>
+    <row r="664" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G664" s="55"/>
+      <c r="J664" s="55"/>
+      <c r="K664" s="55"/>
+      <c r="M664" s="55"/>
+    </row>
+    <row r="665" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G665" s="55"/>
+      <c r="J665" s="55"/>
+      <c r="K665" s="55"/>
+      <c r="M665" s="55"/>
+    </row>
+    <row r="666" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G666" s="55"/>
+      <c r="J666" s="55"/>
+      <c r="K666" s="55"/>
+      <c r="M666" s="55"/>
+    </row>
+    <row r="667" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G667" s="55"/>
+      <c r="J667" s="55"/>
+      <c r="K667" s="55"/>
+      <c r="M667" s="55"/>
+    </row>
+    <row r="668" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G668" s="55"/>
+      <c r="J668" s="55"/>
+      <c r="K668" s="55"/>
+      <c r="M668" s="55"/>
+    </row>
+    <row r="669" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G669" s="55"/>
+      <c r="J669" s="55"/>
+      <c r="K669" s="55"/>
+      <c r="M669" s="55"/>
+    </row>
+    <row r="670" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G670" s="55"/>
+      <c r="J670" s="55"/>
+      <c r="K670" s="55"/>
+      <c r="M670" s="55"/>
+    </row>
+    <row r="671" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G671" s="55"/>
+      <c r="J671" s="55"/>
+      <c r="K671" s="55"/>
+      <c r="M671" s="55"/>
+    </row>
+    <row r="672" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G672" s="55"/>
+      <c r="J672" s="55"/>
+      <c r="K672" s="55"/>
+      <c r="M672" s="55"/>
+    </row>
+    <row r="673" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G673" s="55"/>
+      <c r="J673" s="55"/>
+      <c r="K673" s="55"/>
+      <c r="M673" s="55"/>
+    </row>
+    <row r="674" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G674" s="55"/>
+      <c r="J674" s="55"/>
+      <c r="K674" s="55"/>
+      <c r="M674" s="55"/>
+    </row>
+    <row r="675" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G675" s="55"/>
+      <c r="J675" s="55"/>
+      <c r="K675" s="55"/>
+      <c r="M675" s="55"/>
+    </row>
+    <row r="676" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G676" s="55"/>
+      <c r="J676" s="55"/>
+      <c r="K676" s="55"/>
+      <c r="M676" s="55"/>
+    </row>
+    <row r="677" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G677" s="55"/>
+      <c r="J677" s="55"/>
+      <c r="K677" s="55"/>
+      <c r="M677" s="55"/>
+    </row>
+    <row r="678" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G678" s="55"/>
+      <c r="J678" s="55"/>
+      <c r="K678" s="55"/>
+      <c r="M678" s="55"/>
+    </row>
+    <row r="679" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G679" s="55"/>
+      <c r="J679" s="55"/>
+      <c r="K679" s="55"/>
+      <c r="M679" s="55"/>
+    </row>
+    <row r="680" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G680" s="55"/>
+      <c r="J680" s="55"/>
+      <c r="K680" s="55"/>
+      <c r="M680" s="55"/>
+    </row>
+    <row r="681" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G681" s="55"/>
+      <c r="J681" s="55"/>
+      <c r="K681" s="55"/>
+      <c r="M681" s="55"/>
+    </row>
+    <row r="682" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G682" s="55"/>
+      <c r="J682" s="55"/>
+      <c r="K682" s="55"/>
+      <c r="M682" s="55"/>
+    </row>
+    <row r="683" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G683" s="55"/>
+      <c r="J683" s="55"/>
+      <c r="K683" s="55"/>
+      <c r="M683" s="55"/>
+    </row>
+    <row r="684" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G684" s="55"/>
+      <c r="J684" s="55"/>
+      <c r="K684" s="55"/>
+      <c r="M684" s="55"/>
+    </row>
+    <row r="685" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G685" s="55"/>
+      <c r="J685" s="55"/>
+      <c r="K685" s="55"/>
+      <c r="M685" s="55"/>
+    </row>
+    <row r="686" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G686" s="55"/>
+      <c r="J686" s="55"/>
+      <c r="K686" s="55"/>
+      <c r="M686" s="55"/>
+    </row>
+    <row r="687" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G687" s="55"/>
+      <c r="J687" s="55"/>
+      <c r="K687" s="55"/>
+      <c r="M687" s="55"/>
+    </row>
+    <row r="688" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G688" s="55"/>
+      <c r="J688" s="55"/>
+      <c r="K688" s="55"/>
+      <c r="M688" s="55"/>
+    </row>
+    <row r="689" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G689" s="55"/>
+      <c r="J689" s="55"/>
+      <c r="K689" s="55"/>
+      <c r="M689" s="55"/>
+    </row>
+    <row r="690" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G690" s="55"/>
+      <c r="J690" s="55"/>
+      <c r="K690" s="55"/>
+      <c r="M690" s="55"/>
+    </row>
+    <row r="691" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G691" s="55"/>
+      <c r="J691" s="55"/>
+      <c r="K691" s="55"/>
+      <c r="M691" s="55"/>
+    </row>
+    <row r="692" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G692" s="55"/>
+      <c r="J692" s="55"/>
+      <c r="K692" s="55"/>
+      <c r="M692" s="55"/>
+    </row>
+    <row r="693" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G693" s="55"/>
+      <c r="J693" s="55"/>
+      <c r="K693" s="55"/>
+      <c r="M693" s="55"/>
+    </row>
+    <row r="694" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G694" s="55"/>
+      <c r="J694" s="55"/>
+      <c r="K694" s="55"/>
+      <c r="M694" s="55"/>
+    </row>
+    <row r="695" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G695" s="55"/>
+      <c r="J695" s="55"/>
+      <c r="K695" s="55"/>
+      <c r="M695" s="55"/>
+    </row>
+    <row r="696" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G696" s="55"/>
+      <c r="J696" s="55"/>
+      <c r="K696" s="55"/>
+      <c r="M696" s="55"/>
+    </row>
+    <row r="697" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G697" s="55"/>
+      <c r="J697" s="55"/>
+      <c r="K697" s="55"/>
+      <c r="M697" s="55"/>
+    </row>
+    <row r="698" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G698" s="55"/>
+      <c r="J698" s="55"/>
+      <c r="K698" s="55"/>
+      <c r="M698" s="55"/>
+    </row>
+    <row r="699" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G699" s="55"/>
+      <c r="J699" s="55"/>
+      <c r="K699" s="55"/>
+      <c r="M699" s="55"/>
+    </row>
+    <row r="700" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G700" s="55"/>
+      <c r="J700" s="55"/>
+      <c r="K700" s="55"/>
+      <c r="M700" s="55"/>
+    </row>
+    <row r="701" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G701" s="55"/>
+      <c r="J701" s="55"/>
+      <c r="K701" s="55"/>
+      <c r="M701" s="55"/>
+    </row>
+    <row r="702" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G702" s="55"/>
+      <c r="J702" s="55"/>
+      <c r="K702" s="55"/>
+      <c r="M702" s="55"/>
+    </row>
+    <row r="703" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G703" s="55"/>
+      <c r="J703" s="55"/>
+      <c r="K703" s="55"/>
+      <c r="M703" s="55"/>
+    </row>
+    <row r="704" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G704" s="55"/>
+      <c r="J704" s="55"/>
+      <c r="K704" s="55"/>
+      <c r="M704" s="55"/>
+    </row>
+    <row r="705" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G705" s="55"/>
+      <c r="J705" s="55"/>
+      <c r="K705" s="55"/>
+      <c r="M705" s="55"/>
+    </row>
+    <row r="706" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G706" s="55"/>
+      <c r="J706" s="55"/>
+      <c r="K706" s="55"/>
+      <c r="M706" s="55"/>
+    </row>
+    <row r="707" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G707" s="55"/>
+      <c r="J707" s="55"/>
+      <c r="K707" s="55"/>
+      <c r="M707" s="55"/>
+    </row>
+    <row r="708" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G708" s="55"/>
+      <c r="J708" s="55"/>
+      <c r="K708" s="55"/>
+      <c r="M708" s="55"/>
+    </row>
+    <row r="709" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G709" s="55"/>
+      <c r="J709" s="55"/>
+      <c r="K709" s="55"/>
+      <c r="M709" s="55"/>
+    </row>
+    <row r="710" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G710" s="55"/>
+      <c r="J710" s="55"/>
+      <c r="K710" s="55"/>
+      <c r="M710" s="55"/>
+    </row>
+    <row r="711" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G711" s="55"/>
+      <c r="J711" s="55"/>
+      <c r="K711" s="55"/>
+      <c r="M711" s="55"/>
+    </row>
+    <row r="712" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G712" s="55"/>
+      <c r="J712" s="55"/>
+      <c r="K712" s="55"/>
+      <c r="M712" s="55"/>
+    </row>
+    <row r="713" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G713" s="55"/>
+      <c r="J713" s="55"/>
+      <c r="K713" s="55"/>
+      <c r="M713" s="55"/>
+    </row>
+    <row r="714" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G714" s="55"/>
+      <c r="J714" s="55"/>
+      <c r="K714" s="55"/>
+      <c r="M714" s="55"/>
+    </row>
+    <row r="715" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G715" s="55"/>
+      <c r="J715" s="55"/>
+      <c r="K715" s="55"/>
+      <c r="M715" s="55"/>
+    </row>
+    <row r="716" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G716" s="55"/>
+      <c r="J716" s="55"/>
+      <c r="K716" s="55"/>
+      <c r="M716" s="55"/>
+    </row>
+    <row r="717" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G717" s="55"/>
+      <c r="J717" s="55"/>
+      <c r="K717" s="55"/>
+      <c r="M717" s="55"/>
+    </row>
+    <row r="718" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G718" s="55"/>
+      <c r="J718" s="55"/>
+      <c r="K718" s="55"/>
+      <c r="M718" s="55"/>
+    </row>
+    <row r="719" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G719" s="55"/>
+      <c r="J719" s="55"/>
+      <c r="K719" s="55"/>
+      <c r="M719" s="55"/>
+    </row>
+    <row r="720" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G720" s="55"/>
+      <c r="J720" s="55"/>
+      <c r="K720" s="55"/>
+      <c r="M720" s="55"/>
+    </row>
+    <row r="721" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G721" s="55"/>
+      <c r="J721" s="55"/>
+      <c r="K721" s="55"/>
+      <c r="M721" s="55"/>
+    </row>
+    <row r="722" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G722" s="55"/>
+      <c r="J722" s="55"/>
+      <c r="K722" s="55"/>
+      <c r="M722" s="55"/>
+    </row>
+    <row r="723" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G723" s="55"/>
+      <c r="J723" s="55"/>
+      <c r="K723" s="55"/>
+      <c r="M723" s="55"/>
+    </row>
+    <row r="724" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G724" s="55"/>
+      <c r="J724" s="55"/>
+      <c r="K724" s="55"/>
+      <c r="M724" s="55"/>
+    </row>
+    <row r="725" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G725" s="55"/>
+      <c r="J725" s="55"/>
+      <c r="K725" s="55"/>
+      <c r="M725" s="55"/>
+    </row>
+    <row r="726" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G726" s="55"/>
+      <c r="J726" s="55"/>
+      <c r="K726" s="55"/>
+      <c r="M726" s="55"/>
+    </row>
+    <row r="727" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G727" s="55"/>
+      <c r="J727" s="55"/>
+      <c r="K727" s="55"/>
+      <c r="M727" s="55"/>
+    </row>
+    <row r="728" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G728" s="55"/>
+      <c r="J728" s="55"/>
+      <c r="K728" s="55"/>
+      <c r="M728" s="55"/>
+    </row>
+    <row r="729" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G729" s="55"/>
+      <c r="J729" s="55"/>
+      <c r="K729" s="55"/>
+      <c r="M729" s="55"/>
+    </row>
+    <row r="730" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G730" s="55"/>
+      <c r="J730" s="55"/>
+      <c r="K730" s="55"/>
+      <c r="M730" s="55"/>
+    </row>
+    <row r="731" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G731" s="55"/>
+      <c r="J731" s="55"/>
+      <c r="K731" s="55"/>
+      <c r="M731" s="55"/>
+    </row>
+    <row r="732" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G732" s="55"/>
+      <c r="J732" s="55"/>
+      <c r="K732" s="55"/>
+      <c r="M732" s="55"/>
+    </row>
+    <row r="733" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G733" s="55"/>
+      <c r="J733" s="55"/>
+      <c r="K733" s="55"/>
+      <c r="M733" s="55"/>
+    </row>
+    <row r="734" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G734" s="55"/>
+      <c r="J734" s="55"/>
+      <c r="K734" s="55"/>
+      <c r="M734" s="55"/>
+    </row>
+    <row r="735" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G735" s="55"/>
+      <c r="J735" s="55"/>
+      <c r="K735" s="55"/>
+      <c r="M735" s="55"/>
+    </row>
+    <row r="736" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G736" s="55"/>
+      <c r="J736" s="55"/>
+      <c r="K736" s="55"/>
+      <c r="M736" s="55"/>
+    </row>
+    <row r="737" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G737" s="55"/>
+      <c r="J737" s="55"/>
+      <c r="K737" s="55"/>
+      <c r="M737" s="55"/>
+    </row>
+    <row r="738" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G738" s="55"/>
+      <c r="J738" s="55"/>
+      <c r="K738" s="55"/>
+      <c r="M738" s="55"/>
+    </row>
+    <row r="739" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G739" s="55"/>
+      <c r="J739" s="55"/>
+      <c r="K739" s="55"/>
+      <c r="M739" s="55"/>
+    </row>
+    <row r="740" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G740" s="55"/>
+      <c r="J740" s="55"/>
+      <c r="K740" s="55"/>
+      <c r="M740" s="55"/>
+    </row>
+    <row r="741" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G741" s="55"/>
+      <c r="J741" s="55"/>
+      <c r="K741" s="55"/>
+      <c r="M741" s="55"/>
+    </row>
+    <row r="742" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G742" s="55"/>
+      <c r="J742" s="55"/>
+      <c r="K742" s="55"/>
+      <c r="M742" s="55"/>
+    </row>
+    <row r="743" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G743" s="55"/>
+      <c r="J743" s="55"/>
+      <c r="K743" s="55"/>
+      <c r="M743" s="55"/>
+    </row>
+    <row r="744" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G744" s="55"/>
+      <c r="J744" s="55"/>
+      <c r="K744" s="55"/>
+      <c r="M744" s="55"/>
+    </row>
+    <row r="745" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G745" s="55"/>
+      <c r="J745" s="55"/>
+      <c r="K745" s="55"/>
+      <c r="M745" s="55"/>
+    </row>
+    <row r="746" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G746" s="55"/>
+      <c r="J746" s="55"/>
+      <c r="K746" s="55"/>
+      <c r="M746" s="55"/>
+    </row>
+    <row r="747" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G747" s="55"/>
+      <c r="J747" s="55"/>
+      <c r="K747" s="55"/>
+      <c r="M747" s="55"/>
+    </row>
+    <row r="748" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G748" s="55"/>
+      <c r="J748" s="55"/>
+      <c r="K748" s="55"/>
+      <c r="M748" s="55"/>
+    </row>
+    <row r="749" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G749" s="55"/>
+      <c r="J749" s="55"/>
+      <c r="K749" s="55"/>
+      <c r="M749" s="55"/>
+    </row>
+    <row r="750" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G750" s="55"/>
+      <c r="J750" s="55"/>
+      <c r="K750" s="55"/>
+      <c r="M750" s="55"/>
+    </row>
+    <row r="751" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G751" s="55"/>
+      <c r="J751" s="55"/>
+      <c r="K751" s="55"/>
+      <c r="M751" s="55"/>
+    </row>
+    <row r="752" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G752" s="55"/>
+      <c r="J752" s="55"/>
+      <c r="K752" s="55"/>
+      <c r="M752" s="55"/>
+    </row>
+    <row r="753" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G753" s="55"/>
+      <c r="J753" s="55"/>
+      <c r="K753" s="55"/>
+      <c r="M753" s="55"/>
+    </row>
+    <row r="754" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G754" s="55"/>
+      <c r="J754" s="55"/>
+      <c r="K754" s="55"/>
+      <c r="M754" s="55"/>
+    </row>
+    <row r="755" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G755" s="55"/>
+      <c r="J755" s="55"/>
+      <c r="K755" s="55"/>
+      <c r="M755" s="55"/>
+    </row>
+    <row r="756" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G756" s="55"/>
+      <c r="J756" s="55"/>
+      <c r="K756" s="55"/>
+      <c r="M756" s="55"/>
+    </row>
+    <row r="757" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G757" s="55"/>
+      <c r="J757" s="55"/>
+      <c r="K757" s="55"/>
+      <c r="M757" s="55"/>
+    </row>
+    <row r="758" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G758" s="55"/>
+      <c r="J758" s="55"/>
+      <c r="K758" s="55"/>
+      <c r="M758" s="55"/>
+    </row>
+    <row r="759" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G759" s="55"/>
+      <c r="J759" s="55"/>
+      <c r="K759" s="55"/>
+      <c r="M759" s="55"/>
+    </row>
+    <row r="760" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G760" s="55"/>
+      <c r="J760" s="55"/>
+      <c r="K760" s="55"/>
+      <c r="M760" s="55"/>
+    </row>
+    <row r="761" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G761" s="55"/>
+      <c r="J761" s="55"/>
+      <c r="K761" s="55"/>
+      <c r="M761" s="55"/>
+    </row>
+    <row r="762" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G762" s="55"/>
+      <c r="J762" s="55"/>
+      <c r="K762" s="55"/>
+      <c r="M762" s="55"/>
+    </row>
+    <row r="763" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G763" s="55"/>
+      <c r="J763" s="55"/>
+      <c r="K763" s="55"/>
+      <c r="M763" s="55"/>
+    </row>
+    <row r="764" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G764" s="55"/>
+      <c r="J764" s="55"/>
+      <c r="K764" s="55"/>
+      <c r="M764" s="55"/>
+    </row>
+    <row r="765" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G765" s="55"/>
+      <c r="J765" s="55"/>
+      <c r="K765" s="55"/>
+      <c r="M765" s="55"/>
+    </row>
+    <row r="766" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G766" s="55"/>
+      <c r="J766" s="55"/>
+      <c r="K766" s="55"/>
+      <c r="M766" s="55"/>
+    </row>
+    <row r="767" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G767" s="55"/>
+      <c r="J767" s="55"/>
+      <c r="K767" s="55"/>
+      <c r="M767" s="55"/>
+    </row>
+    <row r="768" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G768" s="55"/>
+      <c r="J768" s="55"/>
+      <c r="K768" s="55"/>
+      <c r="M768" s="55"/>
+    </row>
+    <row r="769" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G769" s="55"/>
+      <c r="J769" s="55"/>
+      <c r="K769" s="55"/>
+      <c r="M769" s="55"/>
+    </row>
+    <row r="770" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G770" s="55"/>
+      <c r="J770" s="55"/>
+      <c r="K770" s="55"/>
+      <c r="M770" s="55"/>
+    </row>
+    <row r="771" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G771" s="55"/>
+      <c r="J771" s="55"/>
+      <c r="K771" s="55"/>
+      <c r="M771" s="55"/>
+    </row>
+    <row r="772" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G772" s="55"/>
+      <c r="J772" s="55"/>
+      <c r="K772" s="55"/>
+      <c r="M772" s="55"/>
+    </row>
+    <row r="773" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G773" s="55"/>
+      <c r="J773" s="55"/>
+      <c r="K773" s="55"/>
+      <c r="M773" s="55"/>
+    </row>
+    <row r="774" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G774" s="55"/>
+      <c r="J774" s="55"/>
+      <c r="K774" s="55"/>
+      <c r="M774" s="55"/>
+    </row>
+    <row r="775" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G775" s="55"/>
+      <c r="J775" s="55"/>
+      <c r="K775" s="55"/>
+      <c r="M775" s="55"/>
+    </row>
+    <row r="776" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G776" s="55"/>
+      <c r="J776" s="55"/>
+      <c r="K776" s="55"/>
+      <c r="M776" s="55"/>
+    </row>
+    <row r="777" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G777" s="55"/>
+      <c r="J777" s="55"/>
+      <c r="K777" s="55"/>
+      <c r="M777" s="55"/>
+    </row>
+    <row r="778" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G778" s="55"/>
+      <c r="J778" s="55"/>
+      <c r="K778" s="55"/>
+      <c r="M778" s="55"/>
+    </row>
+    <row r="779" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G779" s="55"/>
+      <c r="J779" s="55"/>
+      <c r="K779" s="55"/>
+      <c r="M779" s="55"/>
+    </row>
+    <row r="780" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G780" s="55"/>
+      <c r="J780" s="55"/>
+      <c r="K780" s="55"/>
+      <c r="M780" s="55"/>
+    </row>
+    <row r="781" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G781" s="55"/>
+      <c r="J781" s="55"/>
+      <c r="K781" s="55"/>
+      <c r="M781" s="55"/>
+    </row>
+    <row r="782" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G782" s="55"/>
+      <c r="J782" s="55"/>
+      <c r="K782" s="55"/>
+      <c r="M782" s="55"/>
+    </row>
+    <row r="783" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G783" s="55"/>
+      <c r="J783" s="55"/>
+      <c r="K783" s="55"/>
+      <c r="M783" s="55"/>
+    </row>
+    <row r="784" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G784" s="55"/>
+      <c r="J784" s="55"/>
+      <c r="K784" s="55"/>
+      <c r="M784" s="55"/>
+    </row>
+    <row r="785" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G785" s="55"/>
+      <c r="J785" s="55"/>
+      <c r="K785" s="55"/>
+      <c r="M785" s="55"/>
+    </row>
+    <row r="786" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G786" s="55"/>
+      <c r="J786" s="55"/>
+      <c r="K786" s="55"/>
+      <c r="M786" s="55"/>
+    </row>
+    <row r="787" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G787" s="55"/>
+      <c r="J787" s="55"/>
+      <c r="K787" s="55"/>
+      <c r="M787" s="55"/>
+    </row>
+    <row r="788" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G788" s="55"/>
+      <c r="J788" s="55"/>
+      <c r="K788" s="55"/>
+      <c r="M788" s="55"/>
+    </row>
+    <row r="789" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G789" s="55"/>
+      <c r="J789" s="55"/>
+      <c r="K789" s="55"/>
+      <c r="M789" s="55"/>
+    </row>
+    <row r="790" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G790" s="55"/>
+      <c r="J790" s="55"/>
+      <c r="K790" s="55"/>
+      <c r="M790" s="55"/>
+    </row>
+    <row r="791" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G791" s="55"/>
+      <c r="J791" s="55"/>
+      <c r="K791" s="55"/>
+      <c r="M791" s="55"/>
+    </row>
+    <row r="792" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G792" s="55"/>
+      <c r="J792" s="55"/>
+      <c r="K792" s="55"/>
+      <c r="M792" s="55"/>
+    </row>
+    <row r="793" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G793" s="55"/>
+      <c r="J793" s="55"/>
+      <c r="K793" s="55"/>
+      <c r="M793" s="55"/>
+    </row>
+    <row r="794" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G794" s="55"/>
+      <c r="J794" s="55"/>
+      <c r="K794" s="55"/>
+      <c r="M794" s="55"/>
+    </row>
+    <row r="795" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G795" s="55"/>
+      <c r="J795" s="55"/>
+      <c r="K795" s="55"/>
+      <c r="M795" s="55"/>
+    </row>
+    <row r="796" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G796" s="55"/>
+      <c r="J796" s="55"/>
+      <c r="K796" s="55"/>
+      <c r="M796" s="55"/>
+    </row>
+    <row r="797" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G797" s="55"/>
+      <c r="J797" s="55"/>
+      <c r="K797" s="55"/>
+      <c r="M797" s="55"/>
+    </row>
+    <row r="798" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G798" s="55"/>
+      <c r="J798" s="55"/>
+      <c r="K798" s="55"/>
+      <c r="M798" s="55"/>
+    </row>
+    <row r="799" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G799" s="55"/>
+      <c r="J799" s="55"/>
+      <c r="K799" s="55"/>
+      <c r="M799" s="55"/>
+    </row>
+    <row r="800" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G800" s="55"/>
+      <c r="J800" s="55"/>
+      <c r="K800" s="55"/>
+      <c r="M800" s="55"/>
+    </row>
+    <row r="801" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G801" s="55"/>
+      <c r="J801" s="55"/>
+      <c r="K801" s="55"/>
+      <c r="M801" s="55"/>
+    </row>
+    <row r="802" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G802" s="55"/>
+      <c r="J802" s="55"/>
+      <c r="K802" s="55"/>
+      <c r="M802" s="55"/>
+    </row>
+    <row r="803" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G803" s="55"/>
+      <c r="J803" s="55"/>
+      <c r="K803" s="55"/>
+      <c r="M803" s="55"/>
+    </row>
+    <row r="804" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G804" s="55"/>
+      <c r="J804" s="55"/>
+      <c r="K804" s="55"/>
+      <c r="M804" s="55"/>
+    </row>
+    <row r="805" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G805" s="55"/>
+      <c r="J805" s="55"/>
+      <c r="K805" s="55"/>
+      <c r="M805" s="55"/>
+    </row>
+    <row r="806" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G806" s="55"/>
+      <c r="J806" s="55"/>
+      <c r="K806" s="55"/>
+      <c r="M806" s="55"/>
+    </row>
+    <row r="807" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G807" s="55"/>
+      <c r="J807" s="55"/>
+      <c r="K807" s="55"/>
+      <c r="M807" s="55"/>
+    </row>
+    <row r="808" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G808" s="55"/>
+      <c r="J808" s="55"/>
+      <c r="K808" s="55"/>
+      <c r="M808" s="55"/>
+    </row>
+    <row r="809" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G809" s="55"/>
+      <c r="J809" s="55"/>
+      <c r="K809" s="55"/>
+      <c r="M809" s="55"/>
+    </row>
+    <row r="810" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G810" s="55"/>
+      <c r="J810" s="55"/>
+      <c r="K810" s="55"/>
+      <c r="M810" s="55"/>
+    </row>
+    <row r="811" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G811" s="55"/>
+      <c r="J811" s="55"/>
+      <c r="K811" s="55"/>
+      <c r="M811" s="55"/>
+    </row>
+    <row r="812" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G812" s="55"/>
+      <c r="J812" s="55"/>
+      <c r="K812" s="55"/>
+      <c r="M812" s="55"/>
+    </row>
+    <row r="813" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G813" s="55"/>
+      <c r="J813" s="55"/>
+      <c r="K813" s="55"/>
+      <c r="M813" s="55"/>
+    </row>
+    <row r="814" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G814" s="55"/>
+      <c r="J814" s="55"/>
+      <c r="K814" s="55"/>
+      <c r="M814" s="55"/>
+    </row>
+    <row r="815" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G815" s="55"/>
+      <c r="J815" s="55"/>
+      <c r="K815" s="55"/>
+      <c r="M815" s="55"/>
+    </row>
+    <row r="816" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G816" s="55"/>
+      <c r="J816" s="55"/>
+      <c r="K816" s="55"/>
+      <c r="M816" s="55"/>
+    </row>
+    <row r="817" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G817" s="55"/>
+      <c r="J817" s="55"/>
+      <c r="K817" s="55"/>
+      <c r="M817" s="55"/>
+    </row>
+    <row r="818" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G818" s="55"/>
+      <c r="J818" s="55"/>
+      <c r="K818" s="55"/>
+      <c r="M818" s="55"/>
+    </row>
+    <row r="819" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G819" s="55"/>
+      <c r="J819" s="55"/>
+      <c r="K819" s="55"/>
+      <c r="M819" s="55"/>
+    </row>
+    <row r="820" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G820" s="55"/>
+      <c r="J820" s="55"/>
+      <c r="K820" s="55"/>
+      <c r="M820" s="55"/>
+    </row>
+    <row r="821" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G821" s="55"/>
+      <c r="J821" s="55"/>
+      <c r="K821" s="55"/>
+      <c r="M821" s="55"/>
+    </row>
+    <row r="822" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G822" s="55"/>
+      <c r="J822" s="55"/>
+      <c r="K822" s="55"/>
+      <c r="M822" s="55"/>
+    </row>
+    <row r="823" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G823" s="55"/>
+      <c r="J823" s="55"/>
+      <c r="K823" s="55"/>
+      <c r="M823" s="55"/>
+    </row>
+    <row r="824" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G824" s="55"/>
+      <c r="J824" s="55"/>
+      <c r="K824" s="55"/>
+      <c r="M824" s="55"/>
+    </row>
+    <row r="825" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G825" s="55"/>
+      <c r="J825" s="55"/>
+      <c r="K825" s="55"/>
+      <c r="M825" s="55"/>
+    </row>
+    <row r="826" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G826" s="55"/>
+      <c r="J826" s="55"/>
+      <c r="K826" s="55"/>
+      <c r="M826" s="55"/>
+    </row>
+    <row r="827" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G827" s="55"/>
+      <c r="J827" s="55"/>
+      <c r="K827" s="55"/>
+      <c r="M827" s="55"/>
+    </row>
+    <row r="828" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G828" s="55"/>
+      <c r="J828" s="55"/>
+      <c r="K828" s="55"/>
+      <c r="M828" s="55"/>
+    </row>
+    <row r="829" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G829" s="55"/>
+      <c r="J829" s="55"/>
+      <c r="K829" s="55"/>
+      <c r="M829" s="55"/>
+    </row>
+    <row r="830" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G830" s="55"/>
+      <c r="J830" s="55"/>
+      <c r="K830" s="55"/>
+      <c r="M830" s="55"/>
+    </row>
+    <row r="831" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G831" s="55"/>
+      <c r="J831" s="55"/>
+      <c r="K831" s="55"/>
+      <c r="M831" s="55"/>
+    </row>
+    <row r="832" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G832" s="55"/>
+      <c r="J832" s="55"/>
+      <c r="K832" s="55"/>
+      <c r="M832" s="55"/>
+    </row>
+    <row r="833" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G833" s="55"/>
+      <c r="J833" s="55"/>
+      <c r="K833" s="55"/>
+      <c r="M833" s="55"/>
+    </row>
+    <row r="834" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G834" s="55"/>
+      <c r="J834" s="55"/>
+      <c r="K834" s="55"/>
+      <c r="M834" s="55"/>
+    </row>
+    <row r="835" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G835" s="55"/>
+      <c r="J835" s="55"/>
+      <c r="K835" s="55"/>
+      <c r="M835" s="55"/>
+    </row>
+    <row r="836" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G836" s="55"/>
+      <c r="J836" s="55"/>
+      <c r="K836" s="55"/>
+      <c r="M836" s="55"/>
+    </row>
+    <row r="837" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G837" s="55"/>
+      <c r="J837" s="55"/>
+      <c r="K837" s="55"/>
+      <c r="M837" s="55"/>
+    </row>
+    <row r="838" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G838" s="55"/>
+      <c r="J838" s="55"/>
+      <c r="K838" s="55"/>
+      <c r="M838" s="55"/>
+    </row>
+    <row r="839" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G839" s="55"/>
+      <c r="J839" s="55"/>
+      <c r="K839" s="55"/>
+      <c r="M839" s="55"/>
+    </row>
+    <row r="840" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G840" s="55"/>
+      <c r="J840" s="55"/>
+      <c r="K840" s="55"/>
+      <c r="M840" s="55"/>
+    </row>
+    <row r="841" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G841" s="55"/>
+      <c r="J841" s="55"/>
+      <c r="K841" s="55"/>
+      <c r="M841" s="55"/>
+    </row>
+    <row r="842" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G842" s="55"/>
+      <c r="J842" s="55"/>
+      <c r="K842" s="55"/>
+      <c r="M842" s="55"/>
+    </row>
+    <row r="843" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G843" s="55"/>
+      <c r="J843" s="55"/>
+      <c r="K843" s="55"/>
+      <c r="M843" s="55"/>
+    </row>
+    <row r="844" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G844" s="55"/>
+      <c r="J844" s="55"/>
+      <c r="K844" s="55"/>
+      <c r="M844" s="55"/>
+    </row>
+    <row r="845" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G845" s="55"/>
+      <c r="J845" s="55"/>
+      <c r="K845" s="55"/>
+      <c r="M845" s="55"/>
+    </row>
+    <row r="846" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G846" s="55"/>
+      <c r="J846" s="55"/>
+      <c r="K846" s="55"/>
+      <c r="M846" s="55"/>
+    </row>
+    <row r="847" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G847" s="55"/>
+      <c r="J847" s="55"/>
+      <c r="K847" s="55"/>
+      <c r="M847" s="55"/>
+    </row>
+    <row r="848" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G848" s="55"/>
+      <c r="J848" s="55"/>
+      <c r="K848" s="55"/>
+      <c r="M848" s="55"/>
+    </row>
+    <row r="849" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G849" s="55"/>
+      <c r="J849" s="55"/>
+      <c r="K849" s="55"/>
+      <c r="M849" s="55"/>
+    </row>
+    <row r="850" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G850" s="55"/>
+      <c r="J850" s="55"/>
+      <c r="K850" s="55"/>
+      <c r="M850" s="55"/>
+    </row>
+    <row r="851" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G851" s="55"/>
+      <c r="J851" s="55"/>
+      <c r="K851" s="55"/>
+      <c r="M851" s="55"/>
+    </row>
+    <row r="852" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G852" s="55"/>
+      <c r="J852" s="55"/>
+      <c r="K852" s="55"/>
+      <c r="M852" s="55"/>
+    </row>
+    <row r="853" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G853" s="55"/>
+      <c r="J853" s="55"/>
+      <c r="K853" s="55"/>
+      <c r="M853" s="55"/>
+    </row>
+    <row r="854" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G854" s="55"/>
+      <c r="J854" s="55"/>
+      <c r="K854" s="55"/>
+      <c r="M854" s="55"/>
+    </row>
+    <row r="855" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G855" s="55"/>
+      <c r="J855" s="55"/>
+      <c r="K855" s="55"/>
+      <c r="M855" s="55"/>
+    </row>
+    <row r="856" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G856" s="55"/>
+      <c r="J856" s="55"/>
+      <c r="K856" s="55"/>
+      <c r="M856" s="55"/>
+    </row>
+    <row r="857" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G857" s="55"/>
+      <c r="J857" s="55"/>
+      <c r="K857" s="55"/>
+      <c r="M857" s="55"/>
+    </row>
+    <row r="858" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G858" s="55"/>
+      <c r="J858" s="55"/>
+      <c r="K858" s="55"/>
+      <c r="M858" s="55"/>
+    </row>
+    <row r="859" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G859" s="55"/>
+      <c r="J859" s="55"/>
+      <c r="K859" s="55"/>
+      <c r="M859" s="55"/>
+    </row>
+    <row r="860" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G860" s="55"/>
+      <c r="J860" s="55"/>
+      <c r="K860" s="55"/>
+      <c r="M860" s="55"/>
+    </row>
+    <row r="861" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G861" s="55"/>
+      <c r="J861" s="55"/>
+      <c r="K861" s="55"/>
+      <c r="M861" s="55"/>
+    </row>
+    <row r="862" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G862" s="55"/>
+      <c r="J862" s="55"/>
+      <c r="K862" s="55"/>
+      <c r="M862" s="55"/>
+    </row>
+    <row r="863" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G863" s="55"/>
+      <c r="J863" s="55"/>
+      <c r="K863" s="55"/>
+      <c r="M863" s="55"/>
+    </row>
+    <row r="864" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G864" s="55"/>
+      <c r="J864" s="55"/>
+      <c r="K864" s="55"/>
+      <c r="M864" s="55"/>
+    </row>
+    <row r="865" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G865" s="55"/>
+      <c r="J865" s="55"/>
+      <c r="K865" s="55"/>
+      <c r="M865" s="55"/>
+    </row>
+    <row r="866" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G866" s="55"/>
+      <c r="J866" s="55"/>
+      <c r="K866" s="55"/>
+      <c r="M866" s="55"/>
+    </row>
+    <row r="867" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G867" s="55"/>
+      <c r="J867" s="55"/>
+      <c r="K867" s="55"/>
+      <c r="M867" s="55"/>
+    </row>
+    <row r="868" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G868" s="55"/>
+      <c r="J868" s="55"/>
+      <c r="K868" s="55"/>
+      <c r="M868" s="55"/>
+    </row>
+    <row r="869" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G869" s="55"/>
+      <c r="J869" s="55"/>
+      <c r="K869" s="55"/>
+      <c r="M869" s="55"/>
+    </row>
+    <row r="870" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G870" s="55"/>
+      <c r="J870" s="55"/>
+      <c r="K870" s="55"/>
+      <c r="M870" s="55"/>
+    </row>
+    <row r="871" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G871" s="55"/>
+      <c r="J871" s="55"/>
+      <c r="K871" s="55"/>
+      <c r="M871" s="55"/>
+    </row>
+    <row r="872" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G872" s="55"/>
+      <c r="J872" s="55"/>
+      <c r="K872" s="55"/>
+      <c r="M872" s="55"/>
+    </row>
+    <row r="873" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G873" s="55"/>
+      <c r="J873" s="55"/>
+      <c r="K873" s="55"/>
+      <c r="M873" s="55"/>
+    </row>
+    <row r="874" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G874" s="55"/>
+      <c r="J874" s="55"/>
+      <c r="K874" s="55"/>
+      <c r="M874" s="55"/>
+    </row>
+    <row r="875" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G875" s="55"/>
+      <c r="J875" s="55"/>
+      <c r="K875" s="55"/>
+      <c r="M875" s="55"/>
+    </row>
+    <row r="876" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G876" s="55"/>
+      <c r="J876" s="55"/>
+      <c r="K876" s="55"/>
+      <c r="M876" s="55"/>
+    </row>
+    <row r="877" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G877" s="55"/>
+      <c r="J877" s="55"/>
+      <c r="K877" s="55"/>
+      <c r="M877" s="55"/>
+    </row>
+    <row r="878" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G878" s="55"/>
+      <c r="J878" s="55"/>
+      <c r="K878" s="55"/>
+      <c r="M878" s="55"/>
+    </row>
+    <row r="879" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G879" s="55"/>
+      <c r="J879" s="55"/>
+      <c r="K879" s="55"/>
+      <c r="M879" s="55"/>
+    </row>
+    <row r="880" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G880" s="55"/>
+      <c r="J880" s="55"/>
+      <c r="K880" s="55"/>
+      <c r="M880" s="55"/>
+    </row>
+    <row r="881" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G881" s="55"/>
+      <c r="J881" s="55"/>
+      <c r="K881" s="55"/>
+      <c r="M881" s="55"/>
+    </row>
+    <row r="882" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G882" s="55"/>
+      <c r="J882" s="55"/>
+      <c r="K882" s="55"/>
+      <c r="M882" s="55"/>
+    </row>
+    <row r="883" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G883" s="55"/>
+      <c r="J883" s="55"/>
+      <c r="K883" s="55"/>
+      <c r="M883" s="55"/>
+    </row>
+    <row r="884" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G884" s="55"/>
+      <c r="J884" s="55"/>
+      <c r="K884" s="55"/>
+      <c r="M884" s="55"/>
+    </row>
+    <row r="885" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G885" s="55"/>
+      <c r="J885" s="55"/>
+      <c r="K885" s="55"/>
+      <c r="M885" s="55"/>
+    </row>
+    <row r="886" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G886" s="55"/>
+      <c r="J886" s="55"/>
+      <c r="K886" s="55"/>
+      <c r="M886" s="55"/>
+    </row>
+    <row r="887" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G887" s="55"/>
+      <c r="J887" s="55"/>
+      <c r="K887" s="55"/>
+      <c r="M887" s="55"/>
+    </row>
+    <row r="888" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G888" s="55"/>
+      <c r="J888" s="55"/>
+      <c r="K888" s="55"/>
+      <c r="M888" s="55"/>
+    </row>
+    <row r="889" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G889" s="55"/>
+      <c r="J889" s="55"/>
+      <c r="K889" s="55"/>
+      <c r="M889" s="55"/>
+    </row>
+    <row r="890" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G890" s="55"/>
+      <c r="J890" s="55"/>
+      <c r="K890" s="55"/>
+      <c r="M890" s="55"/>
+    </row>
+    <row r="891" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G891" s="55"/>
+      <c r="J891" s="55"/>
+      <c r="K891" s="55"/>
+      <c r="M891" s="55"/>
+    </row>
+    <row r="892" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G892" s="55"/>
+      <c r="J892" s="55"/>
+      <c r="K892" s="55"/>
+      <c r="M892" s="55"/>
+    </row>
+    <row r="893" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G893" s="55"/>
+      <c r="J893" s="55"/>
+      <c r="K893" s="55"/>
+      <c r="M893" s="55"/>
+    </row>
+    <row r="894" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G894" s="55"/>
+      <c r="J894" s="55"/>
+      <c r="K894" s="55"/>
+      <c r="M894" s="55"/>
+    </row>
+    <row r="895" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G895" s="55"/>
+      <c r="J895" s="55"/>
+      <c r="K895" s="55"/>
+      <c r="M895" s="55"/>
+    </row>
+    <row r="896" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G896" s="55"/>
+      <c r="J896" s="55"/>
+      <c r="K896" s="55"/>
+      <c r="M896" s="55"/>
+    </row>
+    <row r="897" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G897" s="55"/>
+      <c r="J897" s="55"/>
+      <c r="K897" s="55"/>
+      <c r="M897" s="55"/>
+    </row>
+    <row r="898" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G898" s="55"/>
+      <c r="J898" s="55"/>
+      <c r="K898" s="55"/>
+      <c r="M898" s="55"/>
+    </row>
+    <row r="899" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G899" s="55"/>
+      <c r="J899" s="55"/>
+      <c r="K899" s="55"/>
+      <c r="M899" s="55"/>
+    </row>
+    <row r="900" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G900" s="55"/>
+      <c r="J900" s="55"/>
+      <c r="K900" s="55"/>
+      <c r="M900" s="55"/>
+    </row>
+    <row r="901" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G901" s="55"/>
+      <c r="J901" s="55"/>
+      <c r="K901" s="55"/>
+      <c r="M901" s="55"/>
+    </row>
+    <row r="902" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G902" s="55"/>
+      <c r="J902" s="55"/>
+      <c r="K902" s="55"/>
+      <c r="M902" s="55"/>
+    </row>
+    <row r="903" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G903" s="55"/>
+      <c r="J903" s="55"/>
+      <c r="K903" s="55"/>
+      <c r="M903" s="55"/>
+    </row>
+    <row r="904" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G904" s="55"/>
+      <c r="J904" s="55"/>
+      <c r="K904" s="55"/>
+      <c r="M904" s="55"/>
+    </row>
+    <row r="905" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G905" s="55"/>
+      <c r="J905" s="55"/>
+      <c r="K905" s="55"/>
+      <c r="M905" s="55"/>
+    </row>
+    <row r="906" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G906" s="55"/>
+      <c r="J906" s="55"/>
+      <c r="K906" s="55"/>
+      <c r="M906" s="55"/>
+    </row>
+    <row r="907" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G907" s="55"/>
+      <c r="J907" s="55"/>
+      <c r="K907" s="55"/>
+      <c r="M907" s="55"/>
+    </row>
+    <row r="908" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G908" s="55"/>
+      <c r="J908" s="55"/>
+      <c r="K908" s="55"/>
+      <c r="M908" s="55"/>
+    </row>
+    <row r="909" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G909" s="55"/>
+      <c r="J909" s="55"/>
+      <c r="K909" s="55"/>
+      <c r="M909" s="55"/>
+    </row>
+    <row r="910" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G910" s="55"/>
+      <c r="J910" s="55"/>
+      <c r="K910" s="55"/>
+      <c r="M910" s="55"/>
+    </row>
+    <row r="911" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G911" s="55"/>
+      <c r="J911" s="55"/>
+      <c r="K911" s="55"/>
+      <c r="M911" s="55"/>
+    </row>
+    <row r="912" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G912" s="55"/>
+      <c r="J912" s="55"/>
+      <c r="K912" s="55"/>
+      <c r="M912" s="55"/>
+    </row>
+    <row r="913" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G913" s="55"/>
+      <c r="J913" s="55"/>
+      <c r="K913" s="55"/>
+      <c r="M913" s="55"/>
+    </row>
+    <row r="914" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G914" s="55"/>
+      <c r="J914" s="55"/>
+      <c r="K914" s="55"/>
+      <c r="M914" s="55"/>
+    </row>
+    <row r="915" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G915" s="55"/>
+      <c r="J915" s="55"/>
+      <c r="K915" s="55"/>
+      <c r="M915" s="55"/>
+    </row>
+    <row r="916" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G916" s="55"/>
+      <c r="J916" s="55"/>
+      <c r="K916" s="55"/>
+      <c r="M916" s="55"/>
+    </row>
+    <row r="917" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G917" s="55"/>
+      <c r="J917" s="55"/>
+      <c r="K917" s="55"/>
+      <c r="M917" s="55"/>
+    </row>
+    <row r="918" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G918" s="55"/>
+      <c r="J918" s="55"/>
+      <c r="K918" s="55"/>
+      <c r="M918" s="55"/>
+    </row>
+    <row r="919" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G919" s="55"/>
+      <c r="J919" s="55"/>
+      <c r="K919" s="55"/>
+      <c r="M919" s="55"/>
+    </row>
+    <row r="920" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G920" s="55"/>
+      <c r="J920" s="55"/>
+      <c r="K920" s="55"/>
+      <c r="M920" s="55"/>
+    </row>
+    <row r="921" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G921" s="55"/>
+      <c r="J921" s="55"/>
+      <c r="K921" s="55"/>
+      <c r="M921" s="55"/>
+    </row>
+    <row r="922" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G922" s="55"/>
+      <c r="J922" s="55"/>
+      <c r="K922" s="55"/>
+      <c r="M922" s="55"/>
+    </row>
+    <row r="923" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G923" s="55"/>
+      <c r="J923" s="55"/>
+      <c r="K923" s="55"/>
+      <c r="M923" s="55"/>
+    </row>
+    <row r="924" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G924" s="55"/>
+      <c r="J924" s="55"/>
+      <c r="K924" s="55"/>
+      <c r="M924" s="55"/>
+    </row>
+    <row r="925" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G925" s="55"/>
+      <c r="J925" s="55"/>
+      <c r="K925" s="55"/>
+      <c r="M925" s="55"/>
+    </row>
+    <row r="926" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G926" s="55"/>
+      <c r="J926" s="55"/>
+      <c r="K926" s="55"/>
+      <c r="M926" s="55"/>
+    </row>
+    <row r="927" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G927" s="55"/>
+      <c r="J927" s="55"/>
+      <c r="K927" s="55"/>
+      <c r="M927" s="55"/>
+    </row>
+    <row r="928" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G928" s="55"/>
+      <c r="J928" s="55"/>
+      <c r="K928" s="55"/>
+      <c r="M928" s="55"/>
+    </row>
+    <row r="929" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G929" s="55"/>
+      <c r="J929" s="55"/>
+      <c r="K929" s="55"/>
+      <c r="M929" s="55"/>
+    </row>
+    <row r="930" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G930" s="55"/>
+      <c r="J930" s="55"/>
+      <c r="K930" s="55"/>
+      <c r="M930" s="55"/>
+    </row>
+    <row r="931" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G931" s="55"/>
+      <c r="J931" s="55"/>
+      <c r="K931" s="55"/>
+      <c r="M931" s="55"/>
+    </row>
+    <row r="932" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G932" s="55"/>
+      <c r="J932" s="55"/>
+      <c r="K932" s="55"/>
+      <c r="M932" s="55"/>
+    </row>
+    <row r="933" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G933" s="55"/>
+      <c r="J933" s="55"/>
+      <c r="K933" s="55"/>
+      <c r="M933" s="55"/>
+    </row>
+    <row r="934" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G934" s="55"/>
+      <c r="J934" s="55"/>
+      <c r="K934" s="55"/>
+      <c r="M934" s="55"/>
+    </row>
+    <row r="935" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G935" s="55"/>
+      <c r="J935" s="55"/>
+      <c r="K935" s="55"/>
+      <c r="M935" s="55"/>
+    </row>
+    <row r="936" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G936" s="55"/>
+      <c r="J936" s="55"/>
+      <c r="K936" s="55"/>
+      <c r="M936" s="55"/>
+    </row>
+    <row r="937" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G937" s="55"/>
+      <c r="J937" s="55"/>
+      <c r="K937" s="55"/>
+      <c r="M937" s="55"/>
+    </row>
+    <row r="938" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G938" s="55"/>
+      <c r="J938" s="55"/>
+      <c r="K938" s="55"/>
+      <c r="M938" s="55"/>
+    </row>
+    <row r="939" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G939" s="55"/>
+      <c r="J939" s="55"/>
+      <c r="K939" s="55"/>
+      <c r="M939" s="55"/>
+    </row>
+    <row r="940" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G940" s="55"/>
+      <c r="J940" s="55"/>
+      <c r="K940" s="55"/>
+      <c r="M940" s="55"/>
+    </row>
+    <row r="941" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G941" s="55"/>
+      <c r="J941" s="55"/>
+      <c r="K941" s="55"/>
+      <c r="M941" s="55"/>
+    </row>
+    <row r="942" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G942" s="55"/>
+      <c r="J942" s="55"/>
+      <c r="K942" s="55"/>
+      <c r="M942" s="55"/>
+    </row>
+    <row r="943" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G943" s="55"/>
+      <c r="J943" s="55"/>
+      <c r="K943" s="55"/>
+      <c r="M943" s="55"/>
+    </row>
+    <row r="944" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G944" s="55"/>
+      <c r="J944" s="55"/>
+      <c r="K944" s="55"/>
+      <c r="M944" s="55"/>
+    </row>
+    <row r="945" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G945" s="55"/>
+      <c r="J945" s="55"/>
+      <c r="K945" s="55"/>
+      <c r="M945" s="55"/>
+    </row>
+    <row r="946" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G946" s="55"/>
+      <c r="J946" s="55"/>
+      <c r="K946" s="55"/>
+      <c r="M946" s="55"/>
+    </row>
+    <row r="947" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G947" s="55"/>
+      <c r="J947" s="55"/>
+      <c r="K947" s="55"/>
+      <c r="M947" s="55"/>
+    </row>
+    <row r="948" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G948" s="55"/>
+      <c r="J948" s="55"/>
+      <c r="K948" s="55"/>
+      <c r="M948" s="55"/>
+    </row>
+    <row r="949" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G949" s="55"/>
+      <c r="J949" s="55"/>
+      <c r="K949" s="55"/>
+      <c r="M949" s="55"/>
+    </row>
+    <row r="950" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G950" s="55"/>
+      <c r="J950" s="55"/>
+      <c r="K950" s="55"/>
+      <c r="M950" s="55"/>
+    </row>
+    <row r="951" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G951" s="55"/>
+      <c r="J951" s="55"/>
+      <c r="K951" s="55"/>
+      <c r="M951" s="55"/>
+    </row>
+    <row r="952" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G952" s="55"/>
+      <c r="J952" s="55"/>
+      <c r="K952" s="55"/>
+      <c r="M952" s="55"/>
+    </row>
+    <row r="953" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G953" s="55"/>
+      <c r="J953" s="55"/>
+      <c r="K953" s="55"/>
+      <c r="M953" s="55"/>
+    </row>
+    <row r="954" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G954" s="55"/>
+      <c r="J954" s="55"/>
+      <c r="K954" s="55"/>
+      <c r="M954" s="55"/>
+    </row>
+    <row r="955" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G955" s="55"/>
+      <c r="J955" s="55"/>
+      <c r="K955" s="55"/>
+      <c r="M955" s="55"/>
+    </row>
+    <row r="956" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G956" s="55"/>
+      <c r="J956" s="55"/>
+      <c r="K956" s="55"/>
+      <c r="M956" s="55"/>
+    </row>
+    <row r="957" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G957" s="55"/>
+      <c r="J957" s="55"/>
+      <c r="K957" s="55"/>
+      <c r="M957" s="55"/>
+    </row>
+    <row r="958" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G958" s="55"/>
+      <c r="J958" s="55"/>
+      <c r="K958" s="55"/>
+      <c r="M958" s="55"/>
+    </row>
+    <row r="959" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G959" s="55"/>
+      <c r="J959" s="55"/>
+      <c r="K959" s="55"/>
+      <c r="M959" s="55"/>
+    </row>
+    <row r="960" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G960" s="55"/>
+      <c r="J960" s="55"/>
+      <c r="K960" s="55"/>
+      <c r="M960" s="55"/>
+    </row>
+    <row r="961" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G961" s="55"/>
+      <c r="J961" s="55"/>
+      <c r="K961" s="55"/>
+      <c r="M961" s="55"/>
+    </row>
+    <row r="962" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G962" s="55"/>
+      <c r="J962" s="55"/>
+      <c r="K962" s="55"/>
+      <c r="M962" s="55"/>
+    </row>
+    <row r="963" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G963" s="55"/>
+      <c r="J963" s="55"/>
+      <c r="K963" s="55"/>
+      <c r="M963" s="55"/>
+    </row>
+    <row r="964" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G964" s="55"/>
+      <c r="J964" s="55"/>
+      <c r="K964" s="55"/>
+      <c r="M964" s="55"/>
+    </row>
+    <row r="965" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G965" s="55"/>
+      <c r="J965" s="55"/>
+      <c r="K965" s="55"/>
+      <c r="M965" s="55"/>
+    </row>
+    <row r="966" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G966" s="55"/>
+      <c r="J966" s="55"/>
+      <c r="K966" s="55"/>
+      <c r="M966" s="55"/>
+    </row>
+    <row r="967" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G967" s="55"/>
+      <c r="J967" s="55"/>
+      <c r="K967" s="55"/>
+      <c r="M967" s="55"/>
+    </row>
+    <row r="968" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G968" s="55"/>
+      <c r="J968" s="55"/>
+      <c r="K968" s="55"/>
+      <c r="M968" s="55"/>
+    </row>
+    <row r="969" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G969" s="55"/>
+      <c r="J969" s="55"/>
+      <c r="K969" s="55"/>
+      <c r="M969" s="55"/>
+    </row>
+    <row r="970" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G970" s="55"/>
+      <c r="J970" s="55"/>
+      <c r="K970" s="55"/>
+      <c r="M970" s="55"/>
+    </row>
+    <row r="971" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G971" s="55"/>
+      <c r="J971" s="55"/>
+      <c r="K971" s="55"/>
+      <c r="M971" s="55"/>
+    </row>
+    <row r="972" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G972" s="55"/>
+      <c r="J972" s="55"/>
+      <c r="K972" s="55"/>
+      <c r="M972" s="55"/>
+    </row>
+    <row r="973" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G973" s="55"/>
+      <c r="J973" s="55"/>
+      <c r="K973" s="55"/>
+      <c r="M973" s="55"/>
+    </row>
+    <row r="974" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G974" s="55"/>
+      <c r="J974" s="55"/>
+      <c r="K974" s="55"/>
+      <c r="M974" s="55"/>
+    </row>
+    <row r="975" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G975" s="55"/>
+      <c r="J975" s="55"/>
+      <c r="K975" s="55"/>
+      <c r="M975" s="55"/>
+    </row>
+    <row r="976" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G976" s="55"/>
+      <c r="J976" s="55"/>
+      <c r="K976" s="55"/>
+      <c r="M976" s="55"/>
+    </row>
+    <row r="977" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G977" s="55"/>
+      <c r="J977" s="55"/>
+      <c r="K977" s="55"/>
+      <c r="M977" s="55"/>
+    </row>
+    <row r="978" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G978" s="55"/>
+      <c r="J978" s="55"/>
+      <c r="K978" s="55"/>
+      <c r="M978" s="55"/>
+    </row>
+    <row r="979" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G979" s="55"/>
+      <c r="J979" s="55"/>
+      <c r="K979" s="55"/>
+      <c r="M979" s="55"/>
+    </row>
+    <row r="980" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G980" s="55"/>
+      <c r="J980" s="55"/>
+      <c r="K980" s="55"/>
+      <c r="M980" s="55"/>
+    </row>
+    <row r="981" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G981" s="55"/>
+      <c r="J981" s="55"/>
+      <c r="K981" s="55"/>
+      <c r="M981" s="55"/>
+    </row>
+    <row r="982" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G982" s="55"/>
+      <c r="J982" s="55"/>
+      <c r="K982" s="55"/>
+      <c r="M982" s="55"/>
+    </row>
+    <row r="983" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G983" s="55"/>
+      <c r="J983" s="55"/>
+      <c r="K983" s="55"/>
+      <c r="M983" s="55"/>
+    </row>
+    <row r="984" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G984" s="55"/>
+      <c r="J984" s="55"/>
+      <c r="K984" s="55"/>
+      <c r="M984" s="55"/>
+    </row>
+    <row r="985" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G985" s="55"/>
+      <c r="J985" s="55"/>
+      <c r="K985" s="55"/>
+      <c r="M985" s="55"/>
+    </row>
+    <row r="986" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G986" s="55"/>
+      <c r="J986" s="55"/>
+      <c r="K986" s="55"/>
+      <c r="M986" s="55"/>
+    </row>
+    <row r="987" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G987" s="55"/>
+      <c r="J987" s="55"/>
+      <c r="K987" s="55"/>
+      <c r="M987" s="55"/>
+    </row>
+    <row r="988" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G988" s="55"/>
+      <c r="J988" s="55"/>
+      <c r="K988" s="55"/>
+      <c r="M988" s="55"/>
+    </row>
+    <row r="989" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G989" s="55"/>
+      <c r="J989" s="55"/>
+      <c r="K989" s="55"/>
+      <c r="M989" s="55"/>
+    </row>
+    <row r="990" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G990" s="55"/>
+      <c r="J990" s="55"/>
+      <c r="K990" s="55"/>
+      <c r="M990" s="55"/>
+    </row>
+    <row r="991" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G991" s="55"/>
+      <c r="J991" s="55"/>
+      <c r="K991" s="55"/>
+      <c r="M991" s="55"/>
+    </row>
+    <row r="992" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G992" s="55"/>
+      <c r="J992" s="55"/>
+      <c r="K992" s="55"/>
+      <c r="M992" s="55"/>
+    </row>
+    <row r="993" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G993" s="55"/>
+      <c r="J993" s="55"/>
+      <c r="K993" s="55"/>
+      <c r="M993" s="55"/>
+    </row>
+    <row r="994" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G994" s="55"/>
+      <c r="J994" s="55"/>
+      <c r="K994" s="55"/>
+      <c r="M994" s="55"/>
+    </row>
+    <row r="995" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G995" s="55"/>
+      <c r="J995" s="55"/>
+      <c r="K995" s="55"/>
+      <c r="M995" s="55"/>
+    </row>
+    <row r="996" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G996" s="55"/>
+      <c r="J996" s="55"/>
+      <c r="K996" s="55"/>
+      <c r="M996" s="55"/>
+    </row>
+    <row r="997" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G997" s="55"/>
+      <c r="J997" s="55"/>
+      <c r="K997" s="55"/>
+      <c r="M997" s="55"/>
+    </row>
+    <row r="998" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G998" s="55"/>
+      <c r="J998" s="55"/>
+      <c r="K998" s="55"/>
+      <c r="M998" s="55"/>
+    </row>
+    <row r="999" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G999" s="55"/>
+      <c r="J999" s="55"/>
+      <c r="K999" s="55"/>
+      <c r="M999" s="55"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
+++ b/PD2026_app/app/src/main/assets/PD2026_program_test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fptsk-my.sharepoint.com/personal/david_badin_fpt_sk/Documents/Dropbox/Public/davidbadin.github.io/PD2026_app/app/src/main/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{131C7504-4BF9-426D-AA88-46AFE32DC43B}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="11_A0C5AF05679CC48EEEB2533C3055F42FBB256A8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F256121-EDB0-4FDD-A09B-C48C81E9F6B5}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60555" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PD2026" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="203">
   <si>
     <t>ID</t>
   </si>
@@ -119,477 +119,548 @@
     <t>ska</t>
   </si>
   <si>
-    <t>RAID SIREN</t>
-  </si>
-  <si>
-    <t>Crust-punkový, ale pokojne aj stoner metalový rachot prinesú deťom chalani z bratislavskej kapely Raid Siren.📣🎸 
-Mladá krv je na hudobných akciách vítaná, navyše otvárať festival má tiež svoje čaro.</t>
-  </si>
-  <si>
-    <t>crust punk/metal</t>
-  </si>
-  <si>
-    <t>TRI GROŠE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tri groše (official), to je dobre známa parta zo slovensko-česko-poľského pohraničia, ktorá je pomaly 40 rokov na koncertných pódiách, kde ponúka rýdzi punkový nárez.🎸🤘 
+    <t>bratislavske-dievcata</t>
+  </si>
+  <si>
+    <t>ME AGAINST ALL</t>
+  </si>
+  <si>
+    <t>Na Punkáči deťom má tradične miesto aj hardcore, tento konkrétny prichádza z hlavného mesta Slovenska, volá sa Me Against All a ty sa môžeš tešiť na poriadnu dávku energie i hluku.😎🤘🎸</t>
+  </si>
+  <si>
+    <t>4G65acjLviUr58H3B722mL</t>
+  </si>
+  <si>
+    <t>hardcore</t>
+  </si>
+  <si>
+    <t>me-against-all</t>
+  </si>
+  <si>
+    <t>TRUE REASON</t>
+  </si>
+  <si>
+    <t>Hardcorovú scénu na 15. ročníku Punkáči deťom zastúpi aj topoľčianska formácia TRUE REASON, ktorá mieša newyorský štýl s rapovými textami. Kapela je známa aj svojim zahraničnými vystúpeniami a v opatovskom kempingu takisto predvedie, aké je to mať hardcore v žilách.🤘🎸</t>
+  </si>
+  <si>
+    <t>4OEQkBWf92X3bNdCbeBgHc</t>
+  </si>
+  <si>
+    <t>true-reason</t>
+  </si>
+  <si>
+    <t>GROBIANI</t>
+  </si>
+  <si>
+    <t>Ďalšia kapela, ktorá vystúpi na Punkáči deťom 2026, je plná chlapcov na úrovni. Grobiani majú punk rock radi, medzi nimi a priaznivcami je teda zrejmá symbióza a to od prvého momentu, ako sa rozoznejú nástroje. Presvedčiť sa o tom veľa námahy nestojí. 😉</t>
+  </si>
+  <si>
+    <t>29RP9HnJfe7Rxb5GizZjYS</t>
+  </si>
+  <si>
+    <t>grobiani</t>
+  </si>
+  <si>
+    <t>PUNKREAS</t>
+  </si>
+  <si>
+    <t>Line-up rozširuje aj dobre známa formácia z Moldavy Punkreas. Tá, samozrejme, ponúkne spojenie punkrockovej hudby so životom a presvedčením, že sa to na tejto scéne stále oplatí robiť. Stálica scény navyše ukáže svoj jasný postoj.</t>
+  </si>
+  <si>
+    <t>350GFtOr7gi2kXqO5kFLOQ</t>
+  </si>
+  <si>
+    <t>punkreas</t>
+  </si>
+  <si>
+    <t>HOTEN TOTEN</t>
+  </si>
+  <si>
+    <t>HT, alebo celým bázvom Hoten Toten je dobre známa stálica scény, ktorá je zárukou koncertného predstavenia najvyššej kvality a inak to nebude ani na 15. ročníku Punkáči deťom. Vidíme sa pod pódiom.👍🎸</t>
+  </si>
+  <si>
+    <t>1SbwRl6gJdmErpczPTwSDM</t>
+  </si>
+  <si>
+    <t>hoten-toten</t>
+  </si>
+  <si>
+    <t>TOTAL CHAOS</t>
+  </si>
+  <si>
+    <t>Na Punkáči deťom 2026 mieri zaujímavá úderka z USA Total Chaos, čo znamená, že sa môžeš tešiť na rýchly, hlučný a drsný hardcore punk, ktorý sa nezastavuje pred ničím. Energická a bezohľadná hudba, provokujúce texty, žiadne kompromisy. Príď sa presvedčiť.🤘😉</t>
+  </si>
+  <si>
+    <t>1KFz81eR4ZcTBqDQjwkgDP</t>
+  </si>
+  <si>
+    <t>hardcore punk</t>
+  </si>
+  <si>
+    <t>total-chaos</t>
+  </si>
+  <si>
+    <t>THE RUMKICKS</t>
+  </si>
+  <si>
+    <t>Tri (v tom najlepšom zmysle) bláznivé baby z Južnej Kórey prídu na Punkáči deťom 2026, aby so svojou kapelou Rumkicks priniesli množstvo nespútanej energie a vlastný pohľad na punk rock. 🤘 
+Formácia z ďalekého Soulu je známa tým, že rada vystupuje po celom svete, my sa tešíme na jej premiéru na našom festivale. 🖤🎸</t>
+  </si>
+  <si>
+    <t>0T5WHtmwuKkqfduvDMnWwt</t>
+  </si>
+  <si>
+    <t>rumkicks</t>
+  </si>
+  <si>
+    <t>AGATA</t>
+  </si>
+  <si>
+    <t>To, že aj na strednom Slovensku sa robí zaujímavý punkrock, potvrdzuje kapela Agata - tá za roky pódiových vystúpení nabrala množstvo skúseností a tie pretavila do zaujímavého koncertného setu, ktorý charakterizujú zvuk, melodický štýl i texty založené na bežných životných situáciách. 👍</t>
+  </si>
+  <si>
+    <t>5fYCdChpBuSm3auI19zcJr</t>
+  </si>
+  <si>
+    <t>agata</t>
+  </si>
+  <si>
+    <t>CYBO</t>
+  </si>
+  <si>
+    <t>Ďalším účastníkom 15. ročníka Punkáči deťom je Cybo, formácia ponúkajúca z pódia myšlienky, skúsenosti i pocity spojené v konkrétnom čase do jedného celku. O zážitok je teda postarané.🎸🎵</t>
+  </si>
+  <si>
+    <t>7crQ7dTH1O7raTTbxiUPMy</t>
+  </si>
+  <si>
+    <t>cybo</t>
+  </si>
+  <si>
+    <t>MÄRNØ</t>
+  </si>
+  <si>
+    <t>MÄRNØ je zástupcom hardcore/punk scény s výrazným podielom crustu, emo HC i post metalu. Kapela z ľavého brehu rieky Morava na Punkáči deťom ukáže, že tento festival má rád presahy a spája aj pridružené subkultúry. 🤘🎸</t>
+  </si>
+  <si>
+    <t>4uc1tTfhjN4YhWTvJJO3Ys</t>
+  </si>
+  <si>
+    <t>crust / black metal</t>
+  </si>
+  <si>
+    <t>marno</t>
+  </si>
+  <si>
+    <t>UPSIDE DOWN!</t>
+  </si>
+  <si>
+    <t>Spoza rieky Morava príde na tento benefičný festival aj kapela Upside Down!CZ, aby pri premiére ukázala poctivý punk s rýchlym tempom a melodickým setom. Formácia z Litomyšlu je činná vyše dekádu a na pódiu ukáže, že ju hudba rozhodne baví.🤘🎸</t>
+  </si>
+  <si>
+    <t>2MWklkepIEuA4uZeB7KHlb</t>
+  </si>
+  <si>
+    <t>upside-down</t>
+  </si>
+  <si>
+    <t>COVERS FOR LOVERS</t>
+  </si>
+  <si>
+    <t>Česká formácia Covers for Lovers (C4L), prinesie sebe vlastný nápaditý, melodický set.🎸 
+Táto pražská kapela je na scéne 15 rokov, pätnástiny oslavuje aj podujatie Punkáči deťom, takže bude party.😋🍻</t>
+  </si>
+  <si>
+    <t>7BdcI3vqGd7a45QZWfxmsf</t>
+  </si>
+  <si>
+    <t>covers-for-lovers</t>
+  </si>
+  <si>
+    <t>SITŇAN</t>
+  </si>
+  <si>
+    <t>Zo stredného Slovenska sa na Punkáči deťom vybrala kapela Sitnan. Vyše 30 rokov na scéne, množstvo odohratých koncertov a stále veľa punku a energie. Príď sa presvedčiť, štandardne to bude veľmi fajn.🎸😎</t>
+  </si>
+  <si>
+    <t>05hEq5XjfjIh2Y0irRmmRI</t>
+  </si>
+  <si>
+    <t>sitnan</t>
+  </si>
+  <si>
+    <t>V.V.Ú</t>
+  </si>
+  <si>
+    <t>Dobre známa kapela V.V.Ú štandardne ponúka melodický punk and roll, ale zároveň aj ostrejšie songy s prvkami hardcoru a to preto, aby bolo pogo pod pódiom čo najvýživnejšie. Buď toho súčasťou, veď parta okolo Štěpánkáča má čo povedať. 🎸🫵🤘</t>
+  </si>
+  <si>
+    <t>7M1cdZ99uob1guIqng2Kka</t>
+  </si>
+  <si>
+    <t>vvu</t>
+  </si>
+  <si>
+    <t>NEŽFALEŠ</t>
+  </si>
+  <si>
+    <t>Formácia Nežfaleš bola druhou potvrdenou kapelou programu 15. ročníka Punkáči deťom a dôvod je zrejmý - parádne texty, známe songy a všeobecne melodický punk and roll, ktorý rozhodne poteší. 🎸🤟 A keby náhodou nie, je tu vodka a lexaurin.🙃</t>
+  </si>
+  <si>
+    <t>72cDnRKentI0gLDMkLGMHN</t>
+  </si>
+  <si>
+    <t>nezfales</t>
+  </si>
+  <si>
+    <t>THE FIALKY</t>
+  </si>
+  <si>
+    <t>Z Prahy prídu na festival starí známi bardi zo 77 punkom ovplyvnenej formácie The Fialky 💥🤟🎸 Bude to vysoko energické, príjemne melodické, bude to plné výkričníkov❗❗❗ a bude to pre teba! A ani nemusíš mať nasadené brejle růžový. 😋</t>
+  </si>
+  <si>
+    <t>2PGAJekhxSzrM9X9ek3vtl</t>
+  </si>
+  <si>
+    <t>fialky</t>
+  </si>
+  <si>
+    <t>PUNK FLOID</t>
+  </si>
+  <si>
+    <t>Rokmi a množstvom vystúpení overená parta okolo Bobbyho Floutka nazvaná Punk Floid si pauzu od Punkáči deťom nedáva ani tento rok. O koncertný zážitok, množstvo dobre známych peciek i náladu máš teda postarané, už sa len stačí zariadiť tak, že to nepremeškáš.🖤😏</t>
+  </si>
+  <si>
+    <t>ZOTRWAČNOSŤ</t>
+  </si>
+  <si>
+    <t>Jeden set, jeden punk, jeden trash. Trnavská formácia Zotrwačnosť ponúkne veľa energie i čo to z nového albumu, ktorý vyšiel na konci minulého roka. Kritické texty, dávka srdu, frustrácie i hnevu, tvrdosť, melanchólia, nadhľad aj prítomný kontrast sú tým, čo túto kapelu charakterizuje. Poď si vystúpenie užiť spoločne s nami. 🎸🤘</t>
+  </si>
+  <si>
+    <t>2zTF1VBdwExv59dW9b5zTE</t>
+  </si>
+  <si>
+    <t>punk / trash</t>
+  </si>
+  <si>
+    <t>zotrwacnost</t>
+  </si>
+  <si>
+    <t>MENTAL TENSION</t>
+  </si>
+  <si>
+    <t>Nekompromisný, surový a zároveň poctivý hardcore sa hrá aj v Trenčíne, parta Mental Tension to teda má do opatovského kempingu na skok. O tom, že tvrdšia hudba na Punkáči deťom patrí, sa môžeš presvedčiť práve pri vystúpení tento party.🤘🎸</t>
+  </si>
+  <si>
+    <t>hardcore / punk</t>
+  </si>
+  <si>
+    <t>mental-tension</t>
+  </si>
+  <si>
+    <t>CROSSCZECH</t>
+  </si>
+  <si>
+    <t>Rýchly, úderný oi! v podaní pražskej kapely Crossczech si môžeš vypočuť aj na opatovských Rybníkoch.🎸👊 Nastavenie hrať to, čo ťa baví, z pódia ponúknuť myšlienky, skúsenosti a pútavý set, je základ - a my sme za. 😉</t>
+  </si>
+  <si>
+    <t>1Jrodi5WbL1r2z1LZN2dkw</t>
+  </si>
+  <si>
+    <t>power oi!</t>
+  </si>
+  <si>
+    <t>crossczech</t>
+  </si>
+  <si>
+    <t>ŠTAMGASTI</t>
+  </si>
+  <si>
+    <t>Hovorí sa, do tretice všetko naj, a tak na Punkáči deťom 2026 vystúpi aj brnenská parta nazvaná Štamgasti. Subcultural beat, srdce a melodický set sú mixom, ktorý baví. 👊🎸</t>
+  </si>
+  <si>
+    <t>subcultural beat</t>
+  </si>
+  <si>
+    <t>VISION DAYS</t>
+  </si>
+  <si>
+    <t>Spoza západných hraníc príde na 15. ročník Punkáči deťom aj dobre známa kapela Vision Days. 🎸🪗 
+Známe, melodické songy, koncertová nálož a priamočiarosť sú devízami tejto punkrockovej formácie, ktorá má fanúšikov od západu Čiech až po východ Slovenska. 🤘</t>
+  </si>
+  <si>
+    <t>TRAGEDIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na Punkáči deťom vystúpi aj početná grupa z Jindřichovho Hradca dobre známa pod menom Tragedis, aby ponúkla obľúbené songy, melodický i jemne nostalgický set, ktorý rozhodne zabaví i poteší ducha. 🎸🪗 
 </t>
   </si>
   <si>
-    <t>0Fi9o8A0CS2JYaEnuWoLAm</t>
-  </si>
-  <si>
-    <t>ŠVINDL (CZ)</t>
-  </si>
-  <si>
-    <t>Punkáči z Litoměřic predvedú, čo je v nich. Kto vie ten vie, že prítomná je svižná, pozitívna hudba podčiarkujúca rýchly melodický rock´n´roll z konca minulého i začiatku tohto storočia, ale aj každodenné skúsenosti s bežným životom zabalené sem-tam do dezilúzií, väčšinou ale do zrejmého entuziazmu.🎸🤘</t>
-  </si>
-  <si>
-    <t>2rMrT5P9Ud0EfWByKWgNjZ</t>
-  </si>
-  <si>
-    <t>ODPAD</t>
-  </si>
-  <si>
-    <t>Z Turca do opatovského campingu zavítala na scéne 30 rokov pôsobiaca kapela, rozhodnutá ponúknuť svoj jasný pohľad à la ostrov slobody vložený do "škatule" Vila la punk musica!🎸👍</t>
-  </si>
-  <si>
-    <t>1pLzB94RzRFGLbc1NFg35b</t>
-  </si>
-  <si>
-    <t>POLEMIC</t>
-  </si>
-  <si>
-    <t>Zrejmý odkaz "Tancuj!" ponúka ska-reaggae legenda Polemic, ktorá zaplní nielen celé pódium ale aj priestor pod ním. 🎷🎸📣 
-Množstvo známych hitov, veľká dávka energie a srdca, skvelá nálada i vyše 35 rokov skúseností s koncertovaním sú mixom dokonalého zážitku. Tak si ho nenechaj ujsť.😉</t>
-  </si>
-  <si>
-    <t>3kIdGWio7imoX74L5EEti4</t>
-  </si>
-  <si>
-    <t>KONFRONT (CZ)</t>
-  </si>
-  <si>
-    <t>Miesto na 14. ročníku Punkáči deťom si uchmatla aj punk-harcorová parta z Prahy KONFRONT a my sme za to radi.👍 Lebo na festival patrí aj tvrdšia hudba, navyše keď ponúknuté žánrové križovatky niekedy zavedú až k metalu. 🎸🎙️</t>
-  </si>
-  <si>
-    <t>0rkS41htYnixneGrMvjlTy</t>
-  </si>
-  <si>
-    <t>hardcore punk rock</t>
-  </si>
-  <si>
-    <t>E!E (CZ)</t>
-  </si>
-  <si>
-    <t>Legenda česko-slovenského punku, ktorá svojho času predskakovala Sex Pistols a zároveň notoricky známa kapela zo stredu Čiech s notoricky známymi songami sa rozhodne postará o parádnu zábavu. Tak len POSLOUCHEJ!😎🎸</t>
-  </si>
-  <si>
-    <t>0n4OWH3G70Pn7HgO9uHfSE</t>
-  </si>
-  <si>
-    <t>NAČO NÁZOV</t>
-  </si>
-  <si>
-    <t>Stálica punkrockovej scény, navyše overená časom i množstvom koncertov. V repertoári poctivý rock´n´roll, príjemný melodický hluk i zrejmý old school smrad, ktorý stále láka. Sedieť len tak na zadku, keď hrá Načo Názov je úplne zbytočný luxus.</t>
-  </si>
-  <si>
-    <t>3d4a7znExBumWnsdPgYVok</t>
-  </si>
-  <si>
-    <t>BREAKOUT (FR)</t>
-  </si>
-  <si>
-    <t>Parížsky hardcore punk, alebo jednoducho len hudobný náklad, ktorý ťa odrovná. Energický set a jasný svetonázor sú dlhoročnou charakteristikou tejto formácie.🤘🎸</t>
-  </si>
-  <si>
-    <t>5ByG0t48AO0z10Cb1bEdeH</t>
-  </si>
-  <si>
-    <t>FEELME</t>
-  </si>
-  <si>
-    <t>Kapela hrajúca inštrumentálny crossover. Medzi najzaujímavejšie koncertné zážitky nepochybne patria hrania pred umelcami ako APOCALYPTICA, GLENN HUGHES (ex-DEEP PURPLE), THE 69 EYES a účasť na množstve festivalov. Ako prezrádza slovná hračka v názve skupiny, orientuje sa výlučne na spracovanie známych i menej známych filmových tém. Nové verzie v podaní FEELME sú plné energie, emócií a experimentu, svoje miesto má aj improvizácia.</t>
-  </si>
-  <si>
-    <t>filmová hudba</t>
-  </si>
-  <si>
-    <t>ŠTAMGASTI (CZ)</t>
-  </si>
-  <si>
-    <t>Subcultural beat, alebo jednoducho povedané mix sympatického smradu, hluku a drsnosti doplnený o romantický náhľad na svet, kamarátstvo, držanie party a množstvo spomienok. Vitaj v rock ´n´ rollovom svete brnenských pardálov.🎸😎</t>
-  </si>
-  <si>
-    <t>punk ´n´ roll</t>
-  </si>
-  <si>
-    <t>Na 14. ročník Punkáči deťom zavítajú aj dobre známi bardi z hlavného mesta Slovenska a, samozrejme, v ružovom.🩷 Bratislavské Dievčatá tradične prinesú 77 punkom ladený set, známe songy i jasný názor.🎸</t>
-  </si>
-  <si>
-    <t>bratislavske-dievcata</t>
-  </si>
-  <si>
-    <t>PREMIETANIE DOKUMENTU KOLÉBKA PUNKU: THE FIALKY</t>
-  </si>
-  <si>
-    <t>punkrockový dokument</t>
-  </si>
-  <si>
-    <t>MIGHTY MAGGOTS (AT)</t>
-  </si>
-  <si>
-    <t>Z Rakúska prišli prítomných roztancovať kapelníci zoskupení pod názvom Mighty Maggots a s nimi aj boky, nohy, ruky i hlavy do pohybu nútiaci set plný ska. Sedieť sa fakt neoplatí. 🎸🎷🥳</t>
-  </si>
-  <si>
-    <t>4nOTYbqJrV2w2GWRqN9baX</t>
-  </si>
-  <si>
-    <t>ska punk</t>
-  </si>
-  <si>
-    <t>BERMUDSKEJ KVÁDR (CZ)</t>
-  </si>
-  <si>
-    <t>Z Vysočiny sa na Slovensko presunula kapela Bermudskéj Kvádr. Priprav sa teda na číry punk rock, rázny štýl, uvoľnenie, gitary, k tomu sem-tam harmonika a program je vystarané.🎸🪗</t>
-  </si>
-  <si>
-    <t>7vM3UvlsF8UUHfNeUv44CF</t>
-  </si>
-  <si>
-    <t>NEKULTÚRA</t>
-  </si>
-  <si>
-    <t>Aj v Hlohovci sa hrá energická muzika, čoho dôkazom je Nekultura, rozhodná i rozhodnutá formácia, ktorá toho zažila dosť na to, aby sa s nami o to podelila. 😎🎸 
-Ak máš teda chuť na neprispôsobivý punk, alebo si naopak vzorný občan, prípadne si o sebe myslíš, že nepatríš do davu, máš o program postarané.😉</t>
-  </si>
-  <si>
-    <t>0MOQRwDXdbbRnxsuNtpPRA</t>
-  </si>
-  <si>
-    <t>BARIKÁDY Z POPELNIC (CZ)</t>
-  </si>
-  <si>
-    <t>Kúsok za hranicami na českej strane leží Hodonín a z tohto mesta pochádza miestami viac či menej nahnevaná parta zoskupená pod názvom @barikadyzpopelnic, ktorá prinesie punkrockový set plný názorov i radosti. Doraz.😉🎸</t>
-  </si>
-  <si>
-    <t>UHOL DOPADU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miestna, rozumej trenčianska kapela Uhol Dopadu ti na prvú ponúka nahnevaný set plný odkazov na to, čo sa okolo nás deje, v druhom pláne ale dodá prítomným čas na zamyslenie sa i tonu energie.💥🎸🎷
+    <t>5NRl4lYRw5epN0Uy1VFfGV</t>
+  </si>
+  <si>
+    <t>tragedis</t>
+  </si>
+  <si>
+    <t>SAINTS &amp; SINNERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streetpunkovú scénu na Punkáči deťom vol. 15 zastúpia aj Saints &amp; Sinners. V našich končinách špička Oi! subžánra má množstvo fanúšikov, my sa tešíme, že sa v opatovskom kempingu predstaví práve táto kapela, ktorá je známa nielen v Európe, ale aj za "veľkou mlákou". 👊🤘 
 </t>
   </si>
   <si>
-    <t>0Tn93NgQ9UGL6PN0JwyxaM</t>
-  </si>
-  <si>
-    <t>BEAUTIFUL BASTARDS</t>
-  </si>
-  <si>
-    <t>Topoľčianska parta Beautiful Bastards ponúka z pódia melodický punk i typický rock´n´rollový príjemný smrad, ležérnosť a istú dávku frivolnosti. 🎸🎙️</t>
-  </si>
-  <si>
-    <t>5PMCmrxaYfVO30KlUOYmOB</t>
-  </si>
-  <si>
-    <t>SOUR BITCH (CZ)</t>
-  </si>
-  <si>
-    <t>Nestrojený rock´n´roll v podaní dievčat z kapely Sour Bitch ti rozhodne ponúkne zaujímavý zážitok.🎸🎙️
-Veľavravný odkaz priamo z textov i pódiového setu v podaní tohto femme fatale bandu si po krajinách západnej Európy vypočuje tentoraz aj Slovensko.</t>
-  </si>
-  <si>
-    <t>19Tp4WoYZu2tyZiblsZype</t>
-  </si>
-  <si>
-    <t>rock ´n´ roll</t>
-  </si>
-  <si>
-    <t>EXNI!TO (CZ)</t>
-  </si>
-  <si>
-    <t>Česká punkrocková stálica Exni!to ponúka príležitosť si zaspomínať. Cez rytmy tzv. South Bohemian punk coru na časy, kedy sa svet zdal omnoho krajší. 😉🎸</t>
-  </si>
-  <si>
-    <t>2n3xDIcnuC8AmJNi3uIS2F</t>
-  </si>
-  <si>
-    <t>PUNK FLOID (CZ)</t>
-  </si>
-  <si>
-    <t>Spája nás aj číslo 25. Presne toľko rokov je na scéne Punk Floid. A keďže z aktuálneho storočia je už ukrojených 25 rokov, máme tu zhodu. A to ani nemusíš piť líh ze slív či čuchať k princeznám. 🙃 
-Známa partia tradične ponúkne skvelú show podporenú songami, ktoré už dávno zľudoveli.🎸🤘</t>
-  </si>
-  <si>
-    <t>TOTÁLNÍ NASAZENÍ (CZ)</t>
-  </si>
-  <si>
-    <t>Prvá zverejnená kapela 14. ročníka Punkáči deťom si to na opatovské Rybníky zamierila z českého Slaného. A nie je to len parta kdejakých nazdárkov, ale naopak - legenda česko-slovenskej scény Totální nasazení. Tradične sa teda môžeš tešiť na pútavú hudbu, ktorá poteší i roztancuje. 👍🎸</t>
-  </si>
-  <si>
-    <t>28B7Oh3NiOx2PCCAo7wcGL</t>
-  </si>
-  <si>
-    <t>THE CARBURETORS (NO)</t>
-  </si>
-  <si>
-    <t>Rýchly rock´n´roll prichádza na festival Punkáči deťom 2025 zo Škandinávie pod hlavičkou The Carburetors. 🤘🎸 
-Charizmatická nórska parta, ktorej začiatky siahajú ešte do roku 2001, ponúkne nezabudnuteľný set plný známych songov a tiež aj zvuk pripomínajúci Motörhead i štart hardrockovej hudby.😍</t>
-  </si>
-  <si>
-    <t>7KQDCEtQTBAtcTJNgezwCD</t>
-  </si>
-  <si>
-    <t>rock</t>
-  </si>
-  <si>
-    <t>PIRATES OF THE PUBS (CZ)</t>
-  </si>
-  <si>
-    <t>Gitary, bicie, husle, akordeón aj flauta. K tomu pre celtic punk tradičný výstavný zvuk a to všetko pod názvom Pirates of the Pubs.🏴‍☠️😎
-⛵ Parta, ktorá sa zdarne plaví nielen po českých moriach, ponúka vo svojej tvorbe nádych Írska i Škótska podporený skúsenosťami z českobudějovických barov. Poď si po nie zasa až taký obvyklý zážitok.🎸🎻</t>
-  </si>
-  <si>
-    <t>4TdCxuJIWjWIoMTwqlnUBK</t>
-  </si>
-  <si>
-    <t>celtic punk</t>
-  </si>
-  <si>
-    <t>PREMIETANIE DOKUMENTU KOLÉBKA PUNKU: TOTÁLNÍ NASAZENÍ</t>
-  </si>
-  <si>
-    <t>CESTOVATEĽSKÁ PREDNÁŠKA: TOMÁŠ PASTIERIK - Stopom cez Irán zo severu na juh a späť</t>
-  </si>
-  <si>
-    <t>Šialený mesiac v Iráne tým najpunkovejším spôsobom. Stopom zo severu na juh a späť. Bez veľkých plánov, zato so silným pocitom slobody v nie práve najslobodnejšej krajine plnej kontrastov a kontroverzií. Hory, púšte, historické mestá a dedinky, ale najme neuveriteľné zážitky s ľuďmi, kde bola v hlavnej úlohe pohostinnosť... Aj o tom bude prednáška Spomienky na Irán aneb trochu punku v Perzii.</t>
-  </si>
-  <si>
-    <t>cestovanie je láska</t>
-  </si>
-  <si>
-    <t>STAND-UP: MATEJ MAKOVICKÝ + VLADO MIKULÁŠ</t>
-  </si>
-  <si>
-    <t>komici v akcii</t>
-  </si>
-  <si>
-    <t>KOHOUT PLAŠÍ SMRT (CZ)</t>
-  </si>
-  <si>
-    <t>Liberecká partia Kohout plaší smrt je na scéne takmer 30 rokov, a tak na pódiu presne vie, čo a ako a ako a čo. 🎸🎙️ 
-Teba teda čaká zrejmý punkový set, kapela sa však nevyhýba ani prechodom do iných žánrov. A mimochodom, každý dobre vie, že najlepšie by bolo mať tučniaka vo vani. Ale o tom už počas koncertu KPS.</t>
-  </si>
-  <si>
-    <t>16vGSIqRkGQhL0LOhgUbFi</t>
-  </si>
-  <si>
-    <t>STREETMACHINE (CZ)</t>
-  </si>
-  <si>
-    <t>Festival Punkáči deťom je tiež multižánrovým podujatím, ktoré zgrupuje aj vyznávačov tvrdšej hudby. Potvrdením tohto je potom účasť hardcorovej party Streetmachine, ktorá prináša zaujímavý playlist i vystúpenie. 🎸🤘</t>
-  </si>
-  <si>
-    <t>6zEBdLkHY9EQeowQbBIZSl</t>
-  </si>
-  <si>
-    <t>hardccore metal</t>
-  </si>
-  <si>
-    <t>THE ROCKET DOGZ (CZ)</t>
-  </si>
-  <si>
-    <t>Pražská parta The Rocket Dogz ponúkne tradične našliapaný set s prvkami psychobilly a punku, resp. dôrazné predstavenie, pri ktorom nezostaneš len tak postávať. 🎸🎻🥁</t>
-  </si>
-  <si>
-    <t>3Hg2fMTZlxQWG8xEBjBXCm</t>
-  </si>
-  <si>
-    <t>punkabilly</t>
-  </si>
-  <si>
-    <t>VOLANT (CZ)</t>
-  </si>
-  <si>
-    <t>Pardubický Volant sa hudbou baví (a všetkých naokolo) už nejaký ten piatok. Ak ti je po vôli melodický punk rock, chytľavé refrény, ale aj zveličovanie a sranda všeho druhu, túto partiu si rozhodne vychutnáš. 😎</t>
-  </si>
-  <si>
-    <t>6rPwkqIhsHQuhIEatC6cL4</t>
-  </si>
-  <si>
-    <t>AFTERPARTY: TRSNISI!</t>
-  </si>
-  <si>
-    <t>Punk rock dídžejs in da hauz. A k tomu new wave, množstvo známych songov = o zábavu je postarané. Večer sa končí až keď dohrá Trsnisi!</t>
-  </si>
-  <si>
-    <t>punk rock, new wave z platní</t>
-  </si>
-  <si>
-    <t>ŽÁDNEJ STRES (CZ)</t>
-  </si>
-  <si>
-    <t>Ska-punkové "združenie" Žádnej Stres ponúka z pódia úsmevy, dobrú náladu i melódie, ktoré roztancúvajú. Východočeská partička veci nehrotí, neberie príliš vážne a je to aj na jej vystúpeniach vidieť. 😎🎸</t>
-  </si>
-  <si>
-    <t>3lx6VXgIRiLkIVyQA2PX5c</t>
-  </si>
-  <si>
-    <t>P.U.M (CZ)</t>
-  </si>
-  <si>
-    <t>Z Prahy si na najväčší punk, ska, oi!, hardcore festival zašli aj chalani z kapely P.U.M, aby nám v textoch pripomenuli, kde je sever a hudobným setom dodali ešte väčšiu chuť na ten či onen drink. 😎🎸 
-Ak teda máš chuť na dávku reality, ktorá nie je zrovna mäkká, prídeš si na svoje. 😉</t>
-  </si>
-  <si>
-    <t>0qi2LoXZB4ytCeIc42lW03</t>
-  </si>
-  <si>
-    <t>SEX DEVIANTS (CZ)</t>
-  </si>
-  <si>
-    <t>Už takmer tri desaťročia môžeme na koncertoch vídavať kapelu Sex deviants, ktorá na Punkáči deťom 2025 zastupuje Plzenský kraj. No a ponúka set preložený melodickosťou i presahmi, ktoré sa miestami jemne odkláňajú od surovosti a tvrdosti punk rocku ako takého. Do toho príjemne zvládnuté texty a máš po ruke fajn zážitok. 🎸🎙️</t>
-  </si>
-  <si>
-    <t>5m8rQZIZtxgg20ni9qf5eF</t>
-  </si>
-  <si>
-    <t>THE CHOICES (FR)</t>
-  </si>
-  <si>
-    <t>Na Punkáči deťom 2025 dorazí aj francúzska formácia The Choices, ktorá ponúkne energický a zároveň melodický punk rock. Spojenie skúsených hudobníkov a charizmatickej Jenny Wooo sa rozhodne oplatí vidieť.😉🎸</t>
-  </si>
-  <si>
-    <t>6AUO0GOTTZG5fnNmvDhiVN</t>
-  </si>
-  <si>
-    <t>DRIÁK (CZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Srdciari z kapely Driák, ktorá dobre pozná krkonošské končiare, sú v ostatných rokoch stálicou tohto podujatia, takže sa aj tentoraz môžeš tešiť na známe songy, dobrú náladu a veľa dôvodov na tanec i drink. 🪗🎸 A splnenie priania, aby si aspoň na chvíľu mal hudobný sluch. 😎 
+    <t>6vfTBFSl2Cf9e3c74pjum2</t>
+  </si>
+  <si>
+    <t>saints-sinners</t>
+  </si>
+  <si>
+    <t>BOOZE AND GLORY</t>
+  </si>
+  <si>
+    <t>Ľahko rozpoznateľný zvuk ulice, silné refrény a hudba ovplyvnená klasickým britským oi! a street punkom, ktorý máme tak radi. To je Booze &amp; Glory, to je jeden z headlinerov 15. ročníka Punkáči deťom. A úprimne, bude parádna jazda. 👊🎸 
+Kapela sa na tomto benefičnom festival predstaví po štyroch rokoch a my si veľmi radi zopakujeme skvelý koncert, veď ako s nadsázkou hovorí klasik "cause we got nothing else to do ..."😉</t>
+  </si>
+  <si>
+    <t>4gVommn6B9vUqdsfSwVaiv</t>
+  </si>
+  <si>
+    <t>street punk / oi!</t>
+  </si>
+  <si>
+    <t>booze-glory</t>
+  </si>
+  <si>
+    <t>PERKELE</t>
+  </si>
+  <si>
+    <t>Perkele sa vracajú s novým silným albumom Theater a na naše potešenie svoje songy premietnu do vystúpenia aj na Punkáči deťom.💥🔝 
+Punk rock? Heavy metal? Rock? Perkele vznikli v roku 1993 ako punkrocková kapela, no už od začiatku radi experimentovali so svojím zvukom. Vyrastali na punk rocku, rôznych štýloch heavy metalu, folku aj progresívnej hudby - všetky tieto vplyvy sú v ich tvorbe viac či menej prítomné od samých začiatkov a ty sa o tom môžeš presvedčiť na vlastné uši🎸🥁</t>
+  </si>
+  <si>
+    <t>6tchRzwnjHlOGnFt1Dh9cF</t>
+  </si>
+  <si>
+    <t>perkele</t>
+  </si>
+  <si>
+    <t>GREEN MONSTER</t>
+  </si>
+  <si>
+    <t>Legenda štýlu psychobilly Green Monster zamierila na Slovensko a na Punkáči deťom ponúkne skvelú show. 🎸🎶🎻Poď si zobrať z dávky energie, charizmy a pokojne sa za pomoci melodických liniek nechaj preniesť napr. do 50. rokov minulého storočia. Alebo sa len opantaj old school štýlom, hororovými prvkami i temným humorom.😎⚰️</t>
+  </si>
+  <si>
+    <t>1NNKHpORNnDbjOiI2hf4Do</t>
+  </si>
+  <si>
+    <t>psychobilly</t>
+  </si>
+  <si>
+    <t>green-monster</t>
+  </si>
+  <si>
+    <t>BILBO (MARHULE)</t>
+  </si>
+  <si>
+    <t>Bilbo, známy z viacerých projektov, si tentoraz hodí koncertný set sám, resp. bez zvyšných členov kapely Marhule. Prítomné teda bude invenčné hovorené slovo, texty rovnako tak, pričom netreba zabúdať na zrejmý odkaz - Šír lásku, ty ...🖤🎸</t>
+  </si>
+  <si>
+    <t>2cTDthazuaQez0gRNP9fIe</t>
+  </si>
+  <si>
+    <t>antipunk</t>
+  </si>
+  <si>
+    <t>bilbo</t>
+  </si>
+  <si>
+    <t>DAFY &amp; THE RAFTERS</t>
+  </si>
+  <si>
+    <t>Jen růžová to může být, hovorí sa v istých kruhoch. A tak si na Punkáči deťom 2026 dajme aj takto sfarbený punk v podaní Dafy and the Rafters. Viacero lovesongov v 77 šate, rýchle tempo a párty až na prvom mieste. Však uvidíš. 🎸😉</t>
+  </si>
+  <si>
+    <t>1FEhgbSVVmmIqeptz60WFZ</t>
+  </si>
+  <si>
+    <t>dafy-the-rafters</t>
+  </si>
+  <si>
+    <t>SPRINGLESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z hlavného mesta Česka mieria do opatovského areálu skatepunkoví, česko-americkí Springless a bude to, samozrejme, jazda. Poď si ju užiť s nami.🤘 
 </t>
   </si>
   <si>
-    <t>DUKLA VOZOVNA (CZ)</t>
-  </si>
-  <si>
-    <t>Punk rock doplnený o prvky ska, zvuk podporený harmonikou (a nie jednou). K tou stovky koncertov, veľa spokojných ľudí pod pódiom. Táto pardubická parta ti navyše z pódia rada na všeličo odpovie. Prípadne poteší krásou svou. 🙃😎</t>
-  </si>
-  <si>
-    <t>4bDVwlWNaxn5syR7Si1DEa</t>
-  </si>
-  <si>
-    <t>VISION DAYS (CZ)</t>
-  </si>
-  <si>
-    <t>Don't worry be punk. A to stačí. Východočeskí Vision Days ti spoza rieky Moravy prinášajú známe songy, punk rock i ska. O program i náladu je postarané. 😉</t>
-  </si>
-  <si>
-    <t>THE OFFENDERS (IT)</t>
-  </si>
-  <si>
-    <t>Hlasná hudba, folkové prvky prelínajúce sa s punk rockom, k tomu ska feeling, mandolína, buzuki a gitarové riffy. 🎸Aj o tom je produkcia The Offenders, talianskej kapely, ktorá sa pred rokmi presťahovala do Berlína, lenže za miesto pôsobenia má prednostne starý kontinent ako taký. 🎙️🎶</t>
-  </si>
-  <si>
-    <t>3S1FzJNl5DweiBE4UE0uob</t>
-  </si>
-  <si>
-    <t>HOUBA (CZ)</t>
-  </si>
-  <si>
-    <t>Ostrieľaná a dobre známa Houba je všade tam, kde sa hrá melodický punk rock, kde hudbu počuť, navyše má zrejmý názor. Večírek s chalanmi z Ústí nad Labem si poď užiť na konci leta 2025, kedy sa v opatovskom campingu koná 14. ročník Punkáči deťom.</t>
-  </si>
-  <si>
-    <t>1fYPVGnjtbTutjBMtI03FJ</t>
-  </si>
-  <si>
-    <t>CATASTROFY</t>
-  </si>
-  <si>
-    <t>Na Punkáči deťom 2025 sa predstaví ešte jedna chuťovka.🤩Ak obľubuješ zbojníkov, trash metal, jednoznačné názorové ukotvenie, satiru, trochu hnevu, pódiovú energiu a máš rád aj melodický rámus, tak vedz, že na záver festivalu ti parádny set pripravia chalani z kapely Catastrofy.🪓🎸🔥</t>
-  </si>
-  <si>
-    <t>2jGzHS5xW03K3Nl4avwxJh</t>
-  </si>
-  <si>
-    <t>trash metal</t>
-  </si>
-  <si>
-    <t>EVIL CONDUCT (NL)</t>
-  </si>
-  <si>
-    <t>Holandská oi! legenda celoeurópskeho dosahu, ktorá je na scéne od roku 1984 je jedným z ťahákov Punkáči deťom 2025. 🖤🎸 Známe pecky, ktoré preveril čas, zuniace nástroje i skvelý koncertný set je len zlomkom, na čo sa môžeš tešiť. Takže skins, Boots on Our Feet a ide sa na to!🤘</t>
-  </si>
-  <si>
-    <t>2fFRHacdj6NyxkPnL8W3Tp</t>
-  </si>
-  <si>
-    <t>PREMIETANIE DOKUMENTU KOLÉBKA PUNKU: ZNOUZECTNOST</t>
-  </si>
-  <si>
-    <t>SLAM POETRY</t>
-  </si>
-  <si>
-    <t>permormatívna súťažná poézia</t>
-  </si>
-  <si>
-    <t>TALKSHOW u HOLA: Podzemné klebety o kluboch (hostia: Vajgel / Collosseum, Richťo / Mariatchi)</t>
-  </si>
-  <si>
-    <t>diskusia</t>
-  </si>
-  <si>
-    <t>ADACTA</t>
-  </si>
-  <si>
-    <t>Hudba zavše spája a ADACTA spája rovnako tak. Napríklad vyznávačov crustu, metalu, hardcoru i punku, tých, čo sa neberú zasa až tak vážne, na druhej strane ale vážne berú veci, na ktorých záleží. 🎸🤘☠️ 
-Tvrdšia hudba mala a má na Punkáči deťom svoje zastúpenie, táto bratislavská kapela navyše ponúka množstvo prvkov, silných hesiel, odkazov, ale aj melodické pasáže. 😎</t>
-  </si>
-  <si>
-    <t>3tKYQbYmSiPHAB80JpLhLS</t>
-  </si>
-  <si>
-    <t>hardcore/crust</t>
-  </si>
-  <si>
-    <t>LENIWIEC (PL)</t>
-  </si>
-  <si>
-    <t>Poriadnu dávku tanečnej hudby založenej na punk rocku, ska a reggae ti na Punkáči deťom prinesie poľská kapela Leniwiec (official), ktorá je na scéne takmer 20 rokov. Priprav si teda končatiny, bude to veľkolepé. 🙃😎</t>
-  </si>
-  <si>
-    <t>1tThntK2T0oDsBTCnBI6im</t>
-  </si>
-  <si>
-    <t>DEGRADACE (CZ)</t>
-  </si>
-  <si>
-    <t>Poď si po poriadny punk´n´roll. Táto ostravská formácia ti ponúkne známe pecky, rokmi overené skúsenosti z pódií, ktoré je dobre rozoznať a hlavne parádnu muziku.🎸👍</t>
-  </si>
-  <si>
-    <t>74rKCPdFckL9YutMRNdlrz</t>
-  </si>
-  <si>
-    <t>JENNY WOO (CA)</t>
-  </si>
-  <si>
-    <t>Z Kanady na festival Punkáči deťom zamieri aj charizmatická Jenny Woo so svojím Oi! Projectom. 🎸Sympatická muzikantka ponúkne štandardne punkom a rock ´n´ rollom nabitý set, do toho ľudskosť a pohodu. Navyše sa objaví aj (samozrejme) v kapele The Choices i na pódiu počas koncertu kamarátov Evil Conduct.🖤</t>
-  </si>
-  <si>
-    <t>5v0cYJxObirCG3XaWNv3og</t>
-  </si>
-  <si>
-    <t>AFTER PARTY: VIKTORR</t>
-  </si>
-  <si>
-    <t>DJ set</t>
+    <t>6dSFJPT69fYPatJtNwNt9M</t>
+  </si>
+  <si>
+    <t>springless</t>
+  </si>
+  <si>
+    <t>Na 15. ročníku Punkáči deťom nechýba ani do ružova sfarbená parta z hlavného mesta nazvaná Bratislavské Dievčatá. Tá prinesie tradičný punk 77 set plný energie, rovnako tak veľa pohody, aby platilo, že každý každého má rád. 🎸🖤🩷</t>
+  </si>
+  <si>
+    <t>SKA PETARDA</t>
+  </si>
+  <si>
+    <t>Tanečná smrť od našich severných susedov má názov SKA Petarda a na opatovských Rybníkoch roztancuje celý camping. Príď sa presvedčiť, príď zavrtieť bokmi, zaskákať.🎵😎</t>
+  </si>
+  <si>
+    <t>1R5rm2uE9X3dRRZ1cBywJc</t>
+  </si>
+  <si>
+    <t>ska-petarda</t>
+  </si>
+  <si>
+    <t>BRAŇO JOBUS spieva a rozpráva o svojich knihách</t>
+  </si>
+  <si>
+    <t>Majster irónie aj invenčnosti, majster absurdných situácií, autor kníh. Braňo Jobus známy z hudobných telies ako sú napr. Karpatské Chrbáty či Vrbovskí víťazi porozpráva i zaspieva na Punkáči deťom o svojich knihách.</t>
+  </si>
+  <si>
+    <t>Punkové rozhovory: HOLO spovedá VAJGLA (Colloseum) + RICHŤA (Mariatchi) + RASŤA (Smer klub 77)</t>
+  </si>
+  <si>
+    <t>Otvorená diskusia s prevádzkarmi punkových klubov. Od Nitry cez Žilinu až do Košíc prerozprávané skúsenosti, zážitky, úplne opačný pohľad na vec, akú majú návštevníci, dišputa o tom, aké je to v aktuálnej dobe viesť podniky takéhoto typu. Bude to rozhodne zaujímavé.</t>
+  </si>
+  <si>
+    <t>Dokumentárny cyklus: Kolébka punku - Pája Junek alias dlhoročný dokumentarista punku</t>
+  </si>
+  <si>
+    <t>PROTI SMĚRU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Po dvoch rokoch si na Punkáči deťom zahrajú aj clockwork punk vyznávajúci Opaváci Proti směru, ktorí slávia 25 rokov na scéne a z pódia ti odkáže, že "ty v tom jedeš s náma". 🤝🤛
+</t>
+  </si>
+  <si>
+    <t>3Eq6Zbu3EIRKrxPJLcNELI</t>
+  </si>
+  <si>
+    <t>proti-smeru</t>
+  </si>
+  <si>
+    <t>DIMENZIA X</t>
+  </si>
+  <si>
+    <t>Kapela, ktorá má čo povedať. Dimenzia X príde na Punkáči deťom, aby sčasti nastavila zrkadlo - spoločnosti i sebe. A to všetko v energickom sete plnom odkazov a kritiky. 👊🎸</t>
+  </si>
+  <si>
+    <t>3fX6bmv2pJAPO12cG4X4o9</t>
+  </si>
+  <si>
+    <t>dimenzia-x</t>
+  </si>
+  <si>
+    <t>CURLIES</t>
+  </si>
+  <si>
+    <t>Nádych Škótska, dynamický punk-rock doplnený o gajdy a hlavne výborný zážitok. Z Česka prichádza na 15. ročník Punkáči deťom aj kapela Curlies, a to s jasným odkazom.</t>
+  </si>
+  <si>
+    <t>01IWtpV4mPTvdVx44kLlI6</t>
+  </si>
+  <si>
+    <t>curlies</t>
+  </si>
+  <si>
+    <t>FAIL TOGETHER</t>
+  </si>
+  <si>
+    <t>Čo takto kapela, ktorá dáva folk a punk dokopy? A tiež pátos táborových ohňov mieša so smradom írskych pubov?🤔 
+Fail Together bude v Opatoviach zaujímavým zjavom, navyše ponúkne veľa energie, pozitívnej nálady a dôvodov len tak nepostávať a radšej sa rozhýbať.💪👯‍♀️</t>
+  </si>
+  <si>
+    <t>55x0gFFuoOgjSexGGYGKux</t>
+  </si>
+  <si>
+    <t>folk punk</t>
+  </si>
+  <si>
+    <t>fail-together</t>
+  </si>
+  <si>
+    <t>AFTERPÁRTY: Viktorr</t>
+  </si>
+  <si>
+    <t>Ako mi Nepál zmenil život - TOMÁŠ PASTIERIK (cestovateľská prednáška)</t>
+  </si>
+  <si>
+    <t>Pred jedenástimi rokmi sa ocitol v Nepále len týždeň po ničivom zemetrasení. Netušil, že táto cesta mu navždy zmení život. Poď si vypočuť inšpiratívny príbeh o odvahe, Himalájach a krajine, ktorá sa stala jeho druhým domovom.🏔️✈️🚗🧳🧭</t>
+  </si>
+  <si>
+    <t>Duševné zdravie s IPčkom (odborná prednáška s diskusiou)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ako rozpoznať, že psychická pohoda už nie je samozrejmosťou? Kedy vyhľadať pomoc a ako sa starať o svoje duševné zdravie? Príď na odbornú prednášku s diskusiou Duševné zdravie s IPčkom a získaj praktické rady od odborníkov, ktorí pomáhajú ľuďom zvládať náročné životné situácie. 
+</t>
+  </si>
+  <si>
+    <t>Dokumentárny cyklus: Kolébka punku - Petr Hošek bez strihu</t>
+  </si>
+  <si>
+    <t>STARÁ PUŠKA</t>
+  </si>
+  <si>
+    <t>Známe hity zahrá na 15. ročníku Punkáči deťom "starý" známy Sid zo Starých Pušiek, tentoraz v jednotnom čísle pod projektom Stará Puška.🎸 
+Tradične vydarený hudobný set, atmosféra i hovorené slovo sú garanciou veľmi dobrého zážitku.</t>
+  </si>
+  <si>
+    <t>5r7VUq5OPwusmuMQxtWSDv</t>
+  </si>
+  <si>
+    <t>punk / folk</t>
+  </si>
+  <si>
+    <t>stara-puska</t>
+  </si>
+  <si>
+    <t>48bNhCBEDL8fse3pKb3jnl</t>
+  </si>
+  <si>
+    <t>SUPERTESLA</t>
+  </si>
+  <si>
+    <t>Po takmer troch rokoch sa na pódiá vracia Supertesla, parta veľkých srdciarov na trase Brno - Praha. Špeciálny comeback si môžeš užiť práve na 15. ročníku Punkáči deťom, zaspievať si, zabaviť sa, zaspomínať a tiež si nabrať za igelitku romantiky.🎸</t>
+  </si>
+  <si>
+    <t>2dRz5TJJV7ZDnvDr8dkDLu</t>
+  </si>
+  <si>
+    <t>heartland punk</t>
+  </si>
+  <si>
+    <t>supertesla</t>
+  </si>
+  <si>
+    <t>DRIÁK</t>
+  </si>
+  <si>
+    <t>Na 15. ročníku Punkáči deťom uvidíš aj Driák a od týchto krkonošských bardov a zároveň srdciarov, samozrejme, dobre známe i songy z nového albumu. 🎸🪗 A možno sa ti aj splní prianie o tom mať hudobný sluch.😉</t>
+  </si>
+  <si>
+    <t>PLUS MÍNUS</t>
+  </si>
+  <si>
+    <t>Dobre známa formácia Plus Mínus posúva do praxe myšlienku, že punk rock môže výborne znieť aj akusticky. Na 15. ročníku Punkáči deťom teda zaznie aj melodický set tejto bratislavskej kapely, samozrejme plný chytľavých refrénov. 🎶🎸👊</t>
+  </si>
+  <si>
+    <t>7Mvv3CqJw2QzjZElmBmlWw</t>
+  </si>
+  <si>
+    <t>plus-minus</t>
+  </si>
+  <si>
+    <t>AFTERPÁRTY: TrsniSi!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,28 +702,38 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -662,6 +743,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F7FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4A7D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2C4C9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE5CD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -713,18 +830,196 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1082,13 +1377,13 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1120,1896 +1415,1882 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>25001</v>
-      </c>
-      <c r="B2" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="A2" s="8">
+        <v>26001</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C2" s="10">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D2" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E2" s="10">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="14">
+        <v>550</v>
+      </c>
+      <c r="L2" s="13"/>
+      <c r="M2" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>26002</v>
+      </c>
+      <c r="B3" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D3" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E3" s="10">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="14">
+        <v>560</v>
+      </c>
+      <c r="L3" s="13"/>
+      <c r="M3" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>26003</v>
+      </c>
+      <c r="B4" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D4" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="14">
+        <v>600</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>26004</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.78125</v>
+      </c>
+      <c r="D5" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.8125</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="14">
+        <v>300</v>
+      </c>
+      <c r="L5" s="13"/>
+      <c r="M5" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>26005</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D6" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" s="14">
+        <v>110</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>26006</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46261</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0.9375</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="14">
+        <v>40</v>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>26007</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46261</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.96527777777777779</v>
+      </c>
+      <c r="D8" s="9">
+        <v>46262</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="14">
+        <v>50</v>
+      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>26008</v>
+      </c>
+      <c r="B9" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C9" s="19">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D9" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E9" s="19">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K9" s="24">
+        <v>630</v>
+      </c>
+      <c r="L9" s="23"/>
+      <c r="M9" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>26009</v>
+      </c>
+      <c r="B10" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D10" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E10" s="19">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K10" s="24">
+        <v>580</v>
+      </c>
+      <c r="L10" s="23"/>
+      <c r="M10" s="26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
+        <v>26010</v>
+      </c>
+      <c r="B11" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C11" s="19">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D11" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E11" s="19">
         <v>0.625</v>
       </c>
-      <c r="D2" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="F11" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="24">
+        <v>590</v>
+      </c>
+      <c r="L11" s="23"/>
+      <c r="M11" s="25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
+        <v>26011</v>
+      </c>
+      <c r="B12" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D12" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E12" s="19">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="24">
+        <v>610</v>
+      </c>
+      <c r="L12" s="23"/>
+      <c r="M12" s="25" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
+        <v>26012</v>
+      </c>
+      <c r="B13" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C13" s="19">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D13" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E13" s="19">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="24">
+        <v>540</v>
+      </c>
+      <c r="L13" s="23"/>
+      <c r="M13" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>26013</v>
+      </c>
+      <c r="B14" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C14" s="19">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D14" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E14" s="19">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="24">
+        <v>300</v>
+      </c>
+      <c r="L14" s="23"/>
+      <c r="M14" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
+        <v>26014</v>
+      </c>
+      <c r="B15" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0.78125</v>
+      </c>
+      <c r="D15" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E15" s="19">
+        <v>0.8125</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="24">
+        <v>510</v>
+      </c>
+      <c r="L15" s="23"/>
+      <c r="M15" s="26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17">
+        <v>26015</v>
+      </c>
+      <c r="B16" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D16" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" s="24">
+        <v>130</v>
+      </c>
+      <c r="L16" s="23"/>
+      <c r="M16" s="25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17">
+        <v>26016</v>
+      </c>
+      <c r="B17" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C17" s="19">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D17" s="18">
+        <v>46262</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0.9375</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="24">
+        <v>120</v>
+      </c>
+      <c r="L17" s="23"/>
+      <c r="M17" s="26" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
+        <v>26017</v>
+      </c>
+      <c r="B18" s="18">
+        <v>46262</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0.96527777777777779</v>
+      </c>
+      <c r="D18" s="18">
+        <v>46263</v>
+      </c>
+      <c r="E18" s="19">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="24">
+        <v>140</v>
+      </c>
+      <c r="L18" s="23"/>
+      <c r="M18" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>26018</v>
+      </c>
+      <c r="B19" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C19" s="29">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="D19" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E19" s="29">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="K19" s="33">
+        <v>660</v>
+      </c>
+      <c r="L19" s="32"/>
+      <c r="M19" s="34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>26019</v>
+      </c>
+      <c r="B20" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C20" s="29">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="D20" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E20" s="29">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" s="33">
+        <v>570</v>
+      </c>
+      <c r="L20" s="32"/>
+      <c r="M20" s="34" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27">
+        <v>26020</v>
+      </c>
+      <c r="B21" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C21" s="29">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="D21" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E21" s="29">
+        <v>0.625</v>
+      </c>
+      <c r="F21" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J21" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="K21" s="33">
+        <v>300</v>
+      </c>
+      <c r="L21" s="32"/>
+      <c r="M21" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="27">
+        <v>26021</v>
+      </c>
+      <c r="B22" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C22" s="29">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D22" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F22" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" s="33">
+        <v>300</v>
+      </c>
+      <c r="L22" s="32"/>
+      <c r="M22" s="36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
+        <v>26022</v>
+      </c>
+      <c r="B23" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C23" s="29">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D23" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E23" s="29">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K23" s="33">
+        <v>300</v>
+      </c>
+      <c r="L23" s="32"/>
+      <c r="M23" s="34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
+        <v>26023</v>
+      </c>
+      <c r="B24" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C24" s="29">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D24" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E24" s="29">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="33">
+        <v>300</v>
+      </c>
+      <c r="L24" s="32"/>
+      <c r="M24" s="34" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27">
+        <v>26024</v>
+      </c>
+      <c r="B25" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C25" s="29">
+        <v>0.78125</v>
+      </c>
+      <c r="D25" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E25" s="29">
+        <v>0.8125</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="33">
+        <v>300</v>
+      </c>
+      <c r="L25" s="32"/>
+      <c r="M25" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27">
+        <v>26025</v>
+      </c>
+      <c r="B26" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C26" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D26" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E26" s="37">
+        <v>0.875</v>
+      </c>
+      <c r="F26" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="K26" s="33">
+        <v>20</v>
+      </c>
+      <c r="L26" s="32"/>
+      <c r="M26" s="34" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="27">
+        <v>26026</v>
+      </c>
+      <c r="B27" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C27" s="37">
+        <v>0.89930555555555558</v>
+      </c>
+      <c r="D27" s="28">
+        <v>46263</v>
+      </c>
+      <c r="E27" s="37">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="F27" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="K27" s="33">
+        <v>10</v>
+      </c>
+      <c r="L27" s="32"/>
+      <c r="M27" s="34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27">
+        <v>26027</v>
+      </c>
+      <c r="B28" s="28">
+        <v>46263</v>
+      </c>
+      <c r="C28" s="29">
+        <v>0.96875</v>
+      </c>
+      <c r="D28" s="28">
+        <v>46264</v>
+      </c>
+      <c r="E28" s="37">
+        <v>0</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="K28" s="33">
+        <v>300</v>
+      </c>
+      <c r="L28" s="32"/>
+      <c r="M28" s="36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="38">
+        <v>26028</v>
+      </c>
+      <c r="B29" s="39">
+        <v>46261</v>
+      </c>
+      <c r="C29" s="40">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D29" s="39">
+        <v>46261</v>
+      </c>
+      <c r="E29" s="40">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="F29" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J29" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="K29" s="44">
+        <v>650</v>
+      </c>
+      <c r="L29" s="43"/>
+      <c r="M29" s="45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="38">
+        <v>26029</v>
+      </c>
+      <c r="B30" s="39">
+        <v>46261</v>
+      </c>
+      <c r="C30" s="40">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="D30" s="39">
+        <v>46261</v>
+      </c>
+      <c r="E30" s="40">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="J30" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="44">
+        <v>670</v>
+      </c>
+      <c r="L30" s="43"/>
+      <c r="M30" s="47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="38">
+        <v>26030</v>
+      </c>
+      <c r="B31" s="39">
+        <v>46261</v>
+      </c>
+      <c r="C31" s="40">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D31" s="39">
+        <v>46261</v>
+      </c>
+      <c r="E31" s="40">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="J31" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K31" s="44">
+        <v>620</v>
+      </c>
+      <c r="L31" s="43"/>
+      <c r="M31" s="47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="38">
+        <v>26031</v>
+      </c>
+      <c r="B32" s="39">
+        <v>46261</v>
+      </c>
+      <c r="C32" s="40">
+        <v>0.9375</v>
+      </c>
+      <c r="D32" s="39">
+        <v>46261</v>
+      </c>
+      <c r="E32" s="48">
+        <v>0.96527777777777779</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="G32" s="41" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="44">
+        <v>300</v>
+      </c>
+      <c r="L32" s="43"/>
+      <c r="M32" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K2" s="3">
-        <v>100</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>25002</v>
-      </c>
-      <c r="B3" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="2" t="s">
+    </row>
+    <row r="33" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="38">
+        <v>26032</v>
+      </c>
+      <c r="B33" s="39">
+        <v>46262</v>
+      </c>
+      <c r="C33" s="40">
+        <v>0</v>
+      </c>
+      <c r="D33" s="39">
+        <v>46262</v>
+      </c>
+      <c r="E33" s="40">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="J33" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" s="44">
+        <v>150</v>
+      </c>
+      <c r="L33" s="43"/>
+      <c r="M33" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="49">
+        <v>26033</v>
+      </c>
+      <c r="B34" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C34" s="51">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D34" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E34" s="52">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="H34" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
+      <c r="M34" s="55"/>
+    </row>
+    <row r="35" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="49">
+        <v>26034</v>
+      </c>
+      <c r="B35" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C35" s="51">
+        <v>0.625</v>
+      </c>
+      <c r="D35" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E35" s="52">
+        <v>0.65625</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="G35" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="H35" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="55"/>
+      <c r="J35" s="55"/>
+      <c r="K35" s="55"/>
+      <c r="L35" s="55"/>
+      <c r="M35" s="55"/>
+    </row>
+    <row r="36" spans="1:13" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="49">
+        <v>26035</v>
+      </c>
+      <c r="B36" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C36" s="51">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D36" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E36" s="51">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="F36" s="56" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="55"/>
+      <c r="H36" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+    </row>
+    <row r="37" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="49">
+        <v>26036</v>
+      </c>
+      <c r="B37" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C37" s="51">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="D37" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E37" s="51">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>162</v>
+      </c>
+      <c r="G37" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="J37" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3">
-        <v>100</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <v>25003</v>
-      </c>
-      <c r="B4" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D4" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K37" s="57">
+        <v>300</v>
+      </c>
+      <c r="L37" s="55"/>
+      <c r="M37" s="58" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="49">
+        <v>26037</v>
+      </c>
+      <c r="B38" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C38" s="51">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="D38" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E38" s="51">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>166</v>
+      </c>
+      <c r="G38" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="H38" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="J38" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="3">
-        <v>100</v>
-      </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>25004</v>
-      </c>
-      <c r="B5" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.75</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K38" s="57">
+        <v>300</v>
+      </c>
+      <c r="L38" s="55"/>
+      <c r="M38" s="58" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="49">
+        <v>26038</v>
+      </c>
+      <c r="B39" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C39" s="51">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D39" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E39" s="51">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="59" t="s">
+        <v>172</v>
+      </c>
+      <c r="J39" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="3">
-        <v>100</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>25005</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D6" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.82638888888888884</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="3">
-        <v>100</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>25006</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.84027777777777779</v>
-      </c>
-      <c r="D7" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="K39" s="57">
+        <v>530</v>
+      </c>
+      <c r="L39" s="55"/>
+      <c r="M39" s="60" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="49">
+        <v>26039</v>
+      </c>
+      <c r="B40" s="50">
+        <v>46262</v>
+      </c>
+      <c r="C40" s="51">
+        <v>0.9375</v>
+      </c>
+      <c r="D40" s="50">
+        <v>46262</v>
+      </c>
+      <c r="E40" s="51">
+        <v>0.96527777777777779</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="K40" s="57">
+        <v>640</v>
+      </c>
+      <c r="L40" s="55"/>
+      <c r="M40" s="58" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="49">
+        <v>26040</v>
+      </c>
+      <c r="B41" s="50">
+        <v>46263</v>
+      </c>
+      <c r="C41" s="51">
+        <v>0</v>
+      </c>
+      <c r="D41" s="50">
+        <v>46263</v>
+      </c>
+      <c r="E41" s="51">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="55"/>
+      <c r="H41" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+    </row>
+    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="61">
+        <v>26041</v>
+      </c>
+      <c r="B42" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C42" s="63">
+        <v>0.5</v>
+      </c>
+      <c r="D42" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E42" s="64">
+        <v>0.5625</v>
+      </c>
+      <c r="F42" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="G42" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="H42" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="67"/>
+      <c r="M42" s="67"/>
+    </row>
+    <row r="43" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="61">
+        <v>26042</v>
+      </c>
+      <c r="B43" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C43" s="63">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D43" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E43" s="64">
+        <v>0.625</v>
+      </c>
+      <c r="F43" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="G43" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="H43" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="67"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="67"/>
+      <c r="M43" s="67"/>
+    </row>
+    <row r="44" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="61">
+        <v>26043</v>
+      </c>
+      <c r="B44" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C44" s="63">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D44" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E44" s="63">
+        <v>0.6875</v>
+      </c>
+      <c r="F44" s="68" t="s">
+        <v>184</v>
+      </c>
+      <c r="G44" s="67"/>
+      <c r="H44" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="67"/>
+      <c r="J44" s="67"/>
+      <c r="K44" s="67"/>
+      <c r="L44" s="67"/>
+      <c r="M44" s="67"/>
+    </row>
+    <row r="45" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="61">
+        <v>26044</v>
+      </c>
+      <c r="B45" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C45" s="63">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="D45" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E45" s="64">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="F45" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="H45" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="67" t="s">
+        <v>187</v>
+      </c>
+      <c r="J45" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="K45" s="69">
+        <v>300</v>
+      </c>
+      <c r="L45" s="67"/>
+      <c r="M45" s="70" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="61">
+        <v>26045</v>
+      </c>
+      <c r="B46" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C46" s="64">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="D46" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E46" s="63">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="F46" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="G46" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="H46" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="67" t="s">
+        <v>190</v>
+      </c>
+      <c r="J46" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="K46" s="67"/>
+      <c r="L46" s="67"/>
+      <c r="M46" s="70" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="61">
+        <v>26046</v>
+      </c>
+      <c r="B47" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C47" s="63">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="D47" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E47" s="63">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F47" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="G47" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="H47" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="67" t="s">
+        <v>193</v>
+      </c>
+      <c r="J47" s="67" t="s">
+        <v>194</v>
+      </c>
+      <c r="K47" s="69">
+        <v>300</v>
+      </c>
+      <c r="L47" s="67"/>
+      <c r="M47" s="70" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="61">
+        <v>26047</v>
+      </c>
+      <c r="B48" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C48" s="63">
         <v>0.86805555555555558</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="3">
-        <v>100</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>25007</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.88194444444444442</v>
-      </c>
-      <c r="D8" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.90972222222222221</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="D48" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E48" s="63">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F48" s="66" t="s">
+        <v>196</v>
+      </c>
+      <c r="G48" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="3">
-        <v>100</v>
-      </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>25008</v>
-      </c>
-      <c r="B9" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.92708333333333337</v>
-      </c>
-      <c r="D9" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.96527777777777779</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K48" s="69">
+        <v>300</v>
+      </c>
+      <c r="L48" s="67"/>
+      <c r="M48" s="70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="61">
+        <v>26048</v>
+      </c>
+      <c r="B49" s="62">
+        <v>46263</v>
+      </c>
+      <c r="C49" s="63">
+        <v>0.94097222222222221</v>
+      </c>
+      <c r="D49" s="62">
+        <v>46263</v>
+      </c>
+      <c r="E49" s="63">
+        <v>0.96875</v>
+      </c>
+      <c r="F49" s="66" t="s">
+        <v>198</v>
+      </c>
+      <c r="G49" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="H49" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="67" t="s">
+        <v>200</v>
+      </c>
+      <c r="J49" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <v>25009</v>
-      </c>
-      <c r="B10" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C10" s="4">
-        <v>0.97222222222222221</v>
-      </c>
-      <c r="D10" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="K49" s="69">
+        <v>520</v>
+      </c>
+      <c r="L49" s="67"/>
+      <c r="M49" s="70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="61">
+        <v>26049</v>
+      </c>
+      <c r="B50" s="62">
+        <v>46264</v>
+      </c>
+      <c r="C50" s="63">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="3">
-        <v>60</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <v>25010</v>
-      </c>
-      <c r="B11" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C11" s="4">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="D11" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0.79861111111111116</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="2" t="s">
+      <c r="D50" s="62">
+        <v>46264</v>
+      </c>
+      <c r="E50" s="63">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F50" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="G50" s="67"/>
+      <c r="H50" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="3">
-        <v>100</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <v>25011</v>
-      </c>
-      <c r="B12" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C12" s="4">
-        <v>0.81944444444444442</v>
-      </c>
-      <c r="D12" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.84722222222222221</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <v>25012</v>
-      </c>
-      <c r="B13" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0.90277777777777779</v>
-      </c>
-      <c r="D13" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.93055555555555558</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="3">
-        <v>100</v>
-      </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <v>25013</v>
-      </c>
-      <c r="B14" s="11">
-        <v>46239</v>
-      </c>
-      <c r="C14" s="4">
-        <v>0.95138888888888884</v>
-      </c>
-      <c r="D14" s="11">
-        <v>46239</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0.97916666666666663</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="5"/>
-    </row>
-    <row r="15" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <v>25014</v>
-      </c>
-      <c r="B15" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E15" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K15" s="3">
-        <v>70</v>
-      </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="5"/>
-    </row>
-    <row r="16" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <v>25015</v>
-      </c>
-      <c r="B16" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="3">
-        <v>100</v>
-      </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="5"/>
-    </row>
-    <row r="17" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <v>25016</v>
-      </c>
-      <c r="B17" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C17" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D17" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="3">
-        <v>100</v>
-      </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="5"/>
-    </row>
-    <row r="18" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <v>25017</v>
-      </c>
-      <c r="B18" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C18" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D18" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E18" s="4">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="5"/>
-    </row>
-    <row r="19" spans="1:13" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <v>25018</v>
-      </c>
-      <c r="B19" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C19" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="D19" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E19" s="4">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="3">
-        <v>100</v>
-      </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="5"/>
-    </row>
-    <row r="20" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <v>25019</v>
-      </c>
-      <c r="B20" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C20" s="4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D20" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E20" s="4">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="5"/>
-    </row>
-    <row r="21" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <v>25020</v>
-      </c>
-      <c r="B21" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C21" s="4">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D21" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E21" s="4">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="3">
-        <v>100</v>
-      </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="5"/>
-    </row>
-    <row r="22" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>25021</v>
-      </c>
-      <c r="B22" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C22" s="4">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="D22" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E22" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="5"/>
-    </row>
-    <row r="23" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <v>25022</v>
-      </c>
-      <c r="B23" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="D23" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E23" s="4">
-        <v>0.83680555555555558</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>25023</v>
-      </c>
-      <c r="B24" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C24" s="4">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D24" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E24" s="4">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
-      </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="5"/>
-    </row>
-    <row r="25" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <v>25024</v>
-      </c>
-      <c r="B25" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C25" s="4">
-        <v>0.90972222222222221</v>
-      </c>
-      <c r="D25" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E25" s="4">
-        <v>0.94444444444444442</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K25" s="3">
-        <v>10</v>
-      </c>
-      <c r="L25" s="2"/>
-      <c r="M25" s="5"/>
-    </row>
-    <row r="26" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>25025</v>
-      </c>
-      <c r="B26" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C26" s="4">
-        <v>0.96527777777777779</v>
-      </c>
-      <c r="D26" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E26" s="4">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
-      <c r="L26" s="2"/>
-      <c r="M26" s="5"/>
-    </row>
-    <row r="27" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <v>25026</v>
-      </c>
-      <c r="B27" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C27" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D27" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E27" s="4">
-        <v>0.56597222222222221</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L27" s="2"/>
-      <c r="M27" s="5"/>
-    </row>
-    <row r="28" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>25027</v>
-      </c>
-      <c r="B28" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="D28" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E28" s="4">
-        <v>0.65972222222222221</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K28" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L28" s="2"/>
-      <c r="M28" s="5"/>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <v>25028</v>
-      </c>
-      <c r="B29" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C29" s="4">
-        <v>0.68055555555555558</v>
-      </c>
-      <c r="D29" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0.71527777777777779</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K29" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L29" s="2"/>
-      <c r="M29" s="5"/>
-    </row>
-    <row r="30" spans="1:13" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <v>25029</v>
-      </c>
-      <c r="B30" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C30" s="4">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="D30" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E30" s="4">
-        <v>0.76388888888888884</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="3">
-        <v>100</v>
-      </c>
-      <c r="L30" s="2"/>
-      <c r="M30" s="5"/>
-    </row>
-    <row r="31" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <v>25030</v>
-      </c>
-      <c r="B31" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C31" s="4">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="D31" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E31" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K31" s="3">
-        <v>100</v>
-      </c>
-      <c r="L31" s="2"/>
-      <c r="M31" s="5"/>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <v>25031</v>
-      </c>
-      <c r="B32" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C32" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D32" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E32" s="4">
-        <v>0.86111111111111116</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="2"/>
-      <c r="M32" s="5"/>
-    </row>
-    <row r="33" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>25032</v>
-      </c>
-      <c r="B33" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C33" s="4">
-        <v>0.88541666666666663</v>
-      </c>
-      <c r="D33" s="11">
-        <v>46240</v>
-      </c>
-      <c r="E33" s="4">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="3">
-        <v>100</v>
-      </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="5"/>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <v>25033</v>
-      </c>
-      <c r="B34" s="11">
-        <v>46240</v>
-      </c>
-      <c r="C34" s="4">
-        <v>0.94444444444444442</v>
-      </c>
-      <c r="D34" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E34" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K34" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" s="5"/>
-    </row>
-    <row r="35" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
-        <v>25034</v>
-      </c>
-      <c r="B35" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C35" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D35" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E35" s="4">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K35" s="3">
-        <v>100</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="5"/>
-    </row>
-    <row r="36" spans="1:13" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
-        <v>25035</v>
-      </c>
-      <c r="B36" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C36" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D36" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E36" s="4">
-        <v>0.56944444444444442</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="3">
-        <v>100</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="5"/>
-    </row>
-    <row r="37" spans="1:13" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
-        <v>25036</v>
-      </c>
-      <c r="B37" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C37" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="D37" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E37" s="4">
-        <v>0.61111111111111116</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="3">
-        <v>100</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="5"/>
-    </row>
-    <row r="38" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
-        <v>25037</v>
-      </c>
-      <c r="B38" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C38" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="D38" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E38" s="4">
-        <v>0.65277777777777779</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" s="3">
-        <v>40</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="1:13" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
-        <v>25038</v>
-      </c>
-      <c r="B39" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C39" s="4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="D39" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E39" s="4">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="3">
-        <v>100</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <v>25039</v>
-      </c>
-      <c r="B40" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C40" s="4">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="D40" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E40" s="4">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" s="3">
-        <v>100</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="5"/>
-    </row>
-    <row r="41" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
-        <v>25040</v>
-      </c>
-      <c r="B41" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C41" s="4">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="D41" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E41" s="4">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" s="3">
-        <v>100</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
-        <v>25041</v>
-      </c>
-      <c r="B42" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C42" s="4">
-        <v>0.80555555555555558</v>
-      </c>
-      <c r="D42" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E42" s="4">
-        <v>0.83680555555555558</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" s="3">
-        <v>30</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="5"/>
-    </row>
-    <row r="43" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
-        <v>25042</v>
-      </c>
-      <c r="B43" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C43" s="4">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D43" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E43" s="4">
-        <v>0.88541666666666663</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" s="3">
-        <v>100</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="5"/>
-    </row>
-    <row r="44" spans="1:13" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
-        <v>25043</v>
-      </c>
-      <c r="B44" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C44" s="4">
-        <v>0.90625</v>
-      </c>
-      <c r="D44" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E44" s="4">
-        <v>0.94097222222222221</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="K44" s="3">
-        <v>100</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="5"/>
-    </row>
-    <row r="45" spans="1:13" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
-        <v>25044</v>
-      </c>
-      <c r="B45" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C45" s="4">
-        <v>0.96180555555555558</v>
-      </c>
-      <c r="D45" s="11">
-        <v>46242</v>
-      </c>
-      <c r="E45" s="4">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K45" s="3">
-        <v>20</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="5"/>
-    </row>
-    <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
-        <v>25045</v>
-      </c>
-      <c r="B46" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C46" s="4">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="D46" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E46" s="4">
-        <v>0.57638888888888884</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K46" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="5"/>
-    </row>
-    <row r="47" spans="1:13" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
-        <v>25046</v>
-      </c>
-      <c r="B47" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C47" s="4">
-        <v>0.59375</v>
-      </c>
-      <c r="D47" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E47" s="4">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K47" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="5"/>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
-        <v>25047</v>
-      </c>
-      <c r="B48" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C48" s="4">
-        <v>0.69444444444444442</v>
-      </c>
-      <c r="D48" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E48" s="4">
-        <v>0.72569444444444442</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K48" s="3">
-        <v>9999</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="5"/>
-    </row>
-    <row r="49" spans="1:13" ht="78" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
-        <v>25048</v>
-      </c>
-      <c r="B49" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C49" s="4">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="D49" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E49" s="4">
-        <v>0.76388888888888884</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="K49" s="3">
-        <v>100</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="5"/>
-    </row>
-    <row r="50" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
-        <v>25049</v>
-      </c>
-      <c r="B50" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C50" s="4">
-        <v>0.78472222222222221</v>
-      </c>
-      <c r="D50" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E50" s="4">
-        <v>0.8125</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="K50" s="3">
-        <v>100</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="5"/>
-    </row>
-    <row r="51" spans="1:13" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
-        <v>25050</v>
-      </c>
-      <c r="B51" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C51" s="4">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D51" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E51" s="4">
-        <v>0.86111111111111116</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K51" s="3">
-        <v>100</v>
-      </c>
+      <c r="I50" s="67"/>
+      <c r="J50" s="67"/>
+      <c r="K50" s="67"/>
+      <c r="L50" s="67"/>
+      <c r="M50" s="67"/>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="3"/>
       <c r="L51" s="2"/>
       <c r="M51" s="5"/>
     </row>
-    <row r="52" spans="1:13" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
-        <v>25051</v>
-      </c>
-      <c r="B52" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C52" s="4">
-        <v>0.88541666666666663</v>
-      </c>
-      <c r="D52" s="11">
-        <v>46241</v>
-      </c>
-      <c r="E52" s="4">
-        <v>0.91319444444444442</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K52" s="3">
-        <v>50</v>
-      </c>
+    <row r="52" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="3"/>
       <c r="L52" s="2"/>
       <c r="M52" s="5"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
-        <v>25052</v>
-      </c>
-      <c r="B53" s="11">
-        <v>46241</v>
-      </c>
-      <c r="C53" s="4">
-        <v>0.94444444444444442</v>
-      </c>
-      <c r="D53" s="11">
-        <v>46242</v>
-      </c>
-      <c r="E53" s="4">
-        <v>7.9861111111111105E-2</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>177</v>
-      </c>
+      <c r="A53" s="3"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-      <c r="H53" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="H53" s="2"/>
       <c r="I53" s="2"/>
-      <c r="J53" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K53" s="3">
-        <v>9999</v>
-      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="3"/>
       <c r="L53" s="2"/>
       <c r="M53" s="5"/>
     </row>
